--- a/New Microsoft Excel Worksheet.xlsx
+++ b/New Microsoft Excel Worksheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696165D7-3355-426F-BC0E-AECE6F603F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708B4B88-7CA8-446F-AB58-A8FE1D30A08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="for check" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'for check'!$A$1:$AC$93</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -319,7 +322,7 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-Asadh grade bridhhi</t>
+Asadh grade bridhhi mistaken by lekha</t>
         </r>
       </text>
     </comment>
@@ -379,7 +382,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>User</author>
-    <author>DELL</author>
   </authors>
   <commentList>
     <comment ref="D3" authorId="0" shapeId="0" xr:uid="{B868339A-E22D-43B4-B7DD-A5CCA0F0A9F2}">
@@ -1024,7 +1026,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{AB12CF4D-CD25-494A-BB9C-AF11A084B26F}">
+    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{B6C5563C-478D-47C6-AE6E-42F6B0801AB6}">
       <text>
         <r>
           <rPr>
@@ -1044,11 +1046,11 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-Asadh</t>
+Asadh supposed to be</t>
         </r>
       </text>
     </comment>
-    <comment ref="E81" authorId="0" shapeId="0" xr:uid="{3834E43B-C7B9-403D-9AB6-404396A32B80}">
+    <comment ref="D82" authorId="0" shapeId="0" xr:uid="{AB71EC1D-DF05-4D0B-9379-E7DCF797F2C1}">
       <text>
         <r>
           <rPr>
@@ -1068,11 +1070,35 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-Asadh grade bridhhi</t>
+Asadh actual</t>
         </r>
       </text>
     </comment>
-    <comment ref="M82" authorId="0" shapeId="0" xr:uid="{DF0DAF17-9556-4E92-8611-A136E25F8C2E}">
+    <comment ref="E82" authorId="0" shapeId="0" xr:uid="{3834E43B-C7B9-403D-9AB6-404396A32B80}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Asadh grade bridhhi mistaken by lekha</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M83" authorId="0" shapeId="0" xr:uid="{DF0DAF17-9556-4E92-8611-A136E25F8C2E}">
       <text>
         <r>
           <rPr>
@@ -1096,7 +1122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D84" authorId="1" shapeId="0" xr:uid="{77C76E6E-8187-405C-85F2-C4B071248F14}">
+    <comment ref="D87" authorId="0" shapeId="0" xr:uid="{07C2709F-ED6A-4DB9-B52E-7EB2FDB18058}">
       <text>
         <r>
           <rPr>
@@ -1106,7 +1132,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>DELL:</t>
+          <t>User:</t>
         </r>
         <r>
           <rPr>
@@ -1116,7 +1142,79 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-From shrawan</t>
+shrawan supposed to be</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D88" authorId="0" shapeId="0" xr:uid="{DF1371C2-8627-4678-9826-92127D3A143E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+shrawan actual</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D89" authorId="0" shapeId="0" xr:uid="{4D3A85A8-F648-4993-AC85-A778145CF8C4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+shrawan actual</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D90" authorId="0" shapeId="0" xr:uid="{6B6B2DA6-B027-410A-949D-5FF619044C8D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Bhadra</t>
         </r>
       </text>
     </comment>
@@ -1125,7 +1223,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="39">
   <si>
     <t>l;= g+=</t>
   </si>
@@ -1219,6 +1317,130 @@
   <si>
     <t>Asadh</t>
   </si>
+  <si>
+    <t>k|wfgdGqL /fxt sf]if s§L</t>
+  </si>
+  <si>
+    <r>
+      <t>Shrawan (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t>x'g'kg]{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Shrawan (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t>c;f/df a9L uPsf] s§L ubf{ x'g'kg]{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Shrawan actual (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t>ePsf]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Asadh (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.499984740745262"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t>x'g'kg]{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Asadh (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t>ePsf]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>3f6f</t>
+  </si>
+  <si>
+    <t>km/s -c;f/df a9L uPsf] s§L x'g'kg]{_</t>
+  </si>
 </sst>
 </file>
 
@@ -1227,7 +1449,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1278,8 +1500,88 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF2F2F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
+      <color rgb="FFC00000"/>
+      <name val="Preeti"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Preeti"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.499984740745262"/>
+      <name val="Preeti"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1289,6 +1591,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1320,7 +1628,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1340,21 +1648,63 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF2F2F"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1634,7 +1984,7 @@
   <cols>
     <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.140625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="6" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.140625" bestFit="1" customWidth="1"/>
@@ -1661,67 +2011,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14" t="s">
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14" t="s">
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="15" t="s">
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="13" t="s">
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="X1" s="15" t="s">
+      <c r="X1" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="13" t="s">
+      <c r="Y1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="13" t="s">
+      <c r="Z1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="13" t="s">
+      <c r="AA1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="AB1" s="13" t="s">
+      <c r="AB1" s="16" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:28" s="6" customFormat="1" ht="71.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
       <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
@@ -1758,7 +2108,7 @@
       <c r="O2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="15"/>
+      <c r="P2" s="17"/>
       <c r="Q2" s="3" t="s">
         <v>14</v>
       </c>
@@ -1777,12 +2127,12 @@
       <c r="V2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="W2" s="13"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="13"/>
-      <c r="Z2" s="13"/>
-      <c r="AA2" s="13"/>
-      <c r="AB2" s="13"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="17"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -3398,16 +3748,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AC65475-327E-4983-B60B-CF7593014FA5}">
-  <dimension ref="A1:AB96"/>
+  <dimension ref="A1:AC101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.140625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="4" width="6" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.85546875" customWidth="1"/>
     <col min="9" max="9" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
@@ -3421,76 +3771,78 @@
     <col min="18" max="18" width="7" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9" style="5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8" customWidth="1"/>
-    <col min="24" max="24" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.85546875" customWidth="1"/>
-    <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.140625" customWidth="1"/>
+    <col min="22" max="22" width="14" customWidth="1"/>
+    <col min="23" max="23" width="9" style="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8" customWidth="1"/>
+    <col min="25" max="25" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.140625" customWidth="1"/>
+    <col min="28" max="28" width="6" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="16.140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
+    <row r="1" spans="1:29" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14" t="s">
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14" t="s">
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="15" t="s">
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="13" t="s">
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="X1" s="15" t="s">
+      <c r="Y1" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="13" t="s">
+      <c r="Z1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="13" t="s">
+      <c r="AA1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="13" t="s">
+      <c r="AB1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="AB1" s="13" t="s">
+      <c r="AC1" s="16" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:28" s="6" customFormat="1" ht="71.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
+    <row r="2" spans="1:29" s="6" customFormat="1" ht="71.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
       <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
@@ -3527,7 +3879,7 @@
       <c r="O2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="15"/>
+      <c r="P2" s="17"/>
       <c r="Q2" s="3" t="s">
         <v>14</v>
       </c>
@@ -3544,16 +3896,19 @@
         <v>28</v>
       </c>
       <c r="V2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="W2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="W2" s="13"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="13"/>
-      <c r="Z2" s="13"/>
-      <c r="AA2" s="13"/>
-      <c r="AB2" s="13"/>
-    </row>
-    <row r="3" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="X2" s="16"/>
+      <c r="Y2" s="17"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+    </row>
+    <row r="3" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -3615,30 +3970,31 @@
         <f t="shared" ref="U3" si="6">J3*2</f>
         <v>3193.2</v>
       </c>
-      <c r="V3" s="4">
-        <f t="shared" ref="V3" si="7">SUM(Q3:U3)</f>
+      <c r="V3" s="2"/>
+      <c r="W3" s="4">
+        <f t="shared" ref="W3" si="7">SUM(Q3:U3)</f>
         <v>14315.2</v>
       </c>
-      <c r="W3" s="2">
-        <f t="shared" ref="W3" si="8">X3+U3</f>
+      <c r="X3" s="2">
+        <f>Y3+U3</f>
         <v>22806.6</v>
       </c>
-      <c r="X3" s="10">
-        <f t="shared" ref="X3" si="9">P3-V3</f>
+      <c r="Y3" s="10">
+        <f>P3-W3</f>
         <v>19613.399999999998</v>
       </c>
-      <c r="Y3" s="2">
-        <f t="shared" ref="Y3:Y66" si="10">IF(X3*13&gt;600000,1%*X3,0)</f>
-        <v>0</v>
-      </c>
       <c r="Z3" s="2">
-        <f t="shared" ref="Z3" si="11">X3-Y3</f>
+        <f t="shared" ref="Z3:Z66" si="8">IF(Y3*13&gt;600000,1%*Y3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2">
+        <f t="shared" ref="AA3" si="9">Y3-Z3</f>
         <v>19613.399999999998</v>
       </c>
-      <c r="AA3" s="2"/>
       <c r="AB3" s="2"/>
-    </row>
-    <row r="4" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC3" s="2"/>
+    </row>
+    <row r="4" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -3660,15 +4016,16 @@
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="10"/>
-      <c r="Y4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="10"/>
       <c r="Z4" s="2"/>
       <c r="AA4" s="2"/>
       <c r="AB4" s="2"/>
-    </row>
-    <row r="5" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC4" s="2"/>
+    </row>
+    <row r="5" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3681,7 +4038,7 @@
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="8">
-        <f t="shared" ref="G5:G16" si="12">SUM(D5:F5)</f>
+        <f t="shared" ref="G5:G16" si="10">SUM(D5:F5)</f>
         <v>26610</v>
       </c>
       <c r="H5" s="2">
@@ -3693,11 +4050,11 @@
         <v>400</v>
       </c>
       <c r="J5" s="2">
-        <f t="shared" ref="J5:J16" si="13">6%*G5</f>
+        <f t="shared" ref="J5:J16" si="11">6%*G5</f>
         <v>1596.6</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" ref="K5:K16" si="14">SUM(G5:J5)</f>
+        <f t="shared" ref="K5:K16" si="12">SUM(G5:J5)</f>
         <v>31267.599999999999</v>
       </c>
       <c r="L5" s="2">
@@ -3709,18 +4066,18 @@
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="4">
-        <f t="shared" ref="O5:O16" si="15">SUM(L5:N5)</f>
+        <f t="shared" ref="O5:O16" si="13">SUM(L5:N5)</f>
         <v>2661</v>
       </c>
       <c r="P5" s="8">
-        <f t="shared" ref="P5:P16" si="16">K5+O5</f>
+        <f t="shared" ref="P5:P16" si="14">K5+O5</f>
         <v>33928.6</v>
       </c>
       <c r="Q5" s="2">
         <v>800</v>
       </c>
       <c r="R5" s="2">
-        <f t="shared" ref="R5:R16" si="17">H5*2</f>
+        <f t="shared" ref="R5:R16" si="15">H5*2</f>
         <v>5322</v>
       </c>
       <c r="S5" s="2">
@@ -3728,33 +4085,34 @@
       </c>
       <c r="T5" s="2"/>
       <c r="U5" s="2">
-        <f t="shared" ref="U5:U16" si="18">J5*2</f>
+        <f t="shared" ref="U5:U16" si="16">J5*2</f>
         <v>3193.2</v>
       </c>
-      <c r="V5" s="4">
-        <f t="shared" ref="V5:V16" si="19">SUM(Q5:U5)</f>
+      <c r="V5" s="2"/>
+      <c r="W5" s="4">
+        <f t="shared" ref="W5:W16" si="17">SUM(Q5:U5)</f>
         <v>14315.2</v>
       </c>
-      <c r="W5" s="2">
-        <f t="shared" ref="W5:W16" si="20">X5+U5</f>
+      <c r="X5" s="2">
+        <f>Y5+U5</f>
         <v>22806.6</v>
       </c>
-      <c r="X5" s="10">
-        <f t="shared" ref="X5:X16" si="21">P5-V5</f>
+      <c r="Y5" s="10">
+        <f>P5-W5</f>
         <v>19613.399999999998</v>
       </c>
-      <c r="Y5" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z5" s="2">
-        <f t="shared" ref="Z5:Z16" si="22">X5-Y5</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA5" s="2">
+        <f t="shared" ref="AA5:AA16" si="18">Y5-Z5</f>
         <v>19613.399999999998</v>
       </c>
-      <c r="AA5" s="2"/>
       <c r="AB5" s="2"/>
-    </row>
-    <row r="6" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC5" s="2"/>
+    </row>
+    <row r="6" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -3762,12 +4120,12 @@
         <v>26610</v>
       </c>
       <c r="E6" s="4">
-        <f t="shared" ref="E6:E15" si="23">ROUNDUP(D6/30,0)*0</f>
+        <f t="shared" ref="E6:E15" si="19">ROUNDUP(D6/30,0)*0</f>
         <v>0</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>26610</v>
       </c>
       <c r="H6" s="2">
@@ -3779,11 +4137,11 @@
         <v>400</v>
       </c>
       <c r="J6" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1596.6</v>
       </c>
       <c r="K6" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>31267.599999999999</v>
       </c>
       <c r="L6" s="2">
@@ -3795,18 +4153,18 @@
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>2661</v>
       </c>
       <c r="P6" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>33928.6</v>
       </c>
       <c r="Q6" s="2">
         <v>800</v>
       </c>
       <c r="R6" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>5322</v>
       </c>
       <c r="S6" s="2">
@@ -3814,33 +4172,34 @@
       </c>
       <c r="T6" s="2"/>
       <c r="U6" s="2">
+        <f t="shared" si="16"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V6" s="2"/>
+      <c r="W6" s="4">
+        <f t="shared" si="17"/>
+        <v>14315.2</v>
+      </c>
+      <c r="X6" s="2">
+        <f>Y6+U6</f>
+        <v>22806.6</v>
+      </c>
+      <c r="Y6" s="10">
+        <f>P6-W6</f>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="Z6" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="2">
         <f t="shared" si="18"/>
-        <v>3193.2</v>
-      </c>
-      <c r="V6" s="4">
-        <f t="shared" si="19"/>
-        <v>14315.2</v>
-      </c>
-      <c r="W6" s="2">
-        <f t="shared" si="20"/>
-        <v>22806.6</v>
-      </c>
-      <c r="X6" s="10">
-        <f t="shared" si="21"/>
         <v>19613.399999999998</v>
       </c>
-      <c r="Y6" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Z6" s="2">
-        <f t="shared" si="22"/>
-        <v>19613.399999999998</v>
-      </c>
-      <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
-    </row>
-    <row r="7" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC6" s="2"/>
+    </row>
+    <row r="7" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -3848,12 +4207,12 @@
         <v>26610</v>
       </c>
       <c r="E7" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>26610</v>
       </c>
       <c r="H7" s="2">
@@ -3865,11 +4224,11 @@
         <v>400</v>
       </c>
       <c r="J7" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1596.6</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>31267.599999999999</v>
       </c>
       <c r="L7" s="2">
@@ -3881,18 +4240,18 @@
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>29271</v>
       </c>
       <c r="P7" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>60538.6</v>
       </c>
       <c r="Q7" s="2">
         <v>800</v>
       </c>
       <c r="R7" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>5322</v>
       </c>
       <c r="S7" s="2">
@@ -3900,30 +4259,31 @@
       </c>
       <c r="T7" s="2"/>
       <c r="U7" s="2">
+        <f t="shared" si="16"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V7" s="2"/>
+      <c r="W7" s="4">
+        <f t="shared" si="17"/>
+        <v>14315.2</v>
+      </c>
+      <c r="X7" s="2">
+        <f>Y7+U7</f>
+        <v>49416.599999999991</v>
+      </c>
+      <c r="Y7" s="10">
+        <f>P7-W7</f>
+        <v>46223.399999999994</v>
+      </c>
+      <c r="Z7" s="2"/>
+      <c r="AA7" s="2">
         <f t="shared" si="18"/>
-        <v>3193.2</v>
-      </c>
-      <c r="V7" s="4">
-        <f t="shared" si="19"/>
-        <v>14315.2</v>
-      </c>
-      <c r="W7" s="2">
-        <f t="shared" si="20"/>
-        <v>49416.599999999991</v>
-      </c>
-      <c r="X7" s="10">
-        <f t="shared" si="21"/>
         <v>46223.399999999994</v>
       </c>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2">
-        <f t="shared" si="22"/>
-        <v>46223.399999999994</v>
-      </c>
-      <c r="AA7" s="2"/>
       <c r="AB7" s="2"/>
-    </row>
-    <row r="8" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC7" s="2"/>
+    </row>
+    <row r="8" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -3931,12 +4291,12 @@
         <v>26610</v>
       </c>
       <c r="E8" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>26610</v>
       </c>
       <c r="H8" s="2">
@@ -3948,34 +4308,34 @@
         <v>400</v>
       </c>
       <c r="J8" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1596.6</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>31267.599999999999</v>
       </c>
       <c r="L8" s="2">
         <v>0</v>
       </c>
       <c r="M8" s="2">
-        <f>10%*D8</f>
+        <f t="shared" ref="M8:M16" si="20">10%*D8</f>
         <v>2661</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>2661</v>
       </c>
       <c r="P8" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>33928.6</v>
       </c>
       <c r="Q8" s="2">
         <v>800</v>
       </c>
       <c r="R8" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>5322</v>
       </c>
       <c r="S8" s="2">
@@ -3983,33 +4343,34 @@
       </c>
       <c r="T8" s="2"/>
       <c r="U8" s="2">
+        <f t="shared" si="16"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V8" s="2"/>
+      <c r="W8" s="4">
+        <f t="shared" si="17"/>
+        <v>14315.2</v>
+      </c>
+      <c r="X8" s="2">
+        <f>Y8+U8</f>
+        <v>22806.6</v>
+      </c>
+      <c r="Y8" s="10">
+        <f>P8-W8</f>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="Z8" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA8" s="2">
         <f t="shared" si="18"/>
-        <v>3193.2</v>
-      </c>
-      <c r="V8" s="4">
-        <f t="shared" si="19"/>
-        <v>14315.2</v>
-      </c>
-      <c r="W8" s="2">
-        <f t="shared" si="20"/>
-        <v>22806.6</v>
-      </c>
-      <c r="X8" s="10">
-        <f t="shared" si="21"/>
         <v>19613.399999999998</v>
       </c>
-      <c r="Y8" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Z8" s="2">
-        <f t="shared" si="22"/>
-        <v>19613.399999999998</v>
-      </c>
-      <c r="AA8" s="2"/>
       <c r="AB8" s="2"/>
-    </row>
-    <row r="9" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC8" s="2"/>
+    </row>
+    <row r="9" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -4017,12 +4378,12 @@
         <v>26610</v>
       </c>
       <c r="E9" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>26610</v>
       </c>
       <c r="H9" s="2">
@@ -4034,34 +4395,34 @@
         <v>400</v>
       </c>
       <c r="J9" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1596.6</v>
       </c>
       <c r="K9" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>31267.599999999999</v>
       </c>
       <c r="L9" s="2">
         <v>0</v>
       </c>
       <c r="M9" s="2">
-        <f>10%*D9</f>
+        <f t="shared" si="20"/>
         <v>2661</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>2661</v>
       </c>
       <c r="P9" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>33928.6</v>
       </c>
       <c r="Q9" s="2">
         <v>800</v>
       </c>
       <c r="R9" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>5322</v>
       </c>
       <c r="S9" s="2">
@@ -4069,33 +4430,34 @@
       </c>
       <c r="T9" s="2"/>
       <c r="U9" s="2">
+        <f t="shared" si="16"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V9" s="2"/>
+      <c r="W9" s="4">
+        <f t="shared" si="17"/>
+        <v>14315.2</v>
+      </c>
+      <c r="X9" s="2">
+        <f>Y9+U9</f>
+        <v>22806.6</v>
+      </c>
+      <c r="Y9" s="10">
+        <f>P9-W9</f>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="Z9" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA9" s="2">
         <f t="shared" si="18"/>
-        <v>3193.2</v>
-      </c>
-      <c r="V9" s="4">
-        <f t="shared" si="19"/>
-        <v>14315.2</v>
-      </c>
-      <c r="W9" s="2">
-        <f t="shared" si="20"/>
-        <v>22806.6</v>
-      </c>
-      <c r="X9" s="10">
-        <f t="shared" si="21"/>
         <v>19613.399999999998</v>
       </c>
-      <c r="Y9" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Z9" s="2">
-        <f t="shared" si="22"/>
-        <v>19613.399999999998</v>
-      </c>
-      <c r="AA9" s="2"/>
       <c r="AB9" s="2"/>
-    </row>
-    <row r="10" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC9" s="2"/>
+    </row>
+    <row r="10" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -4103,12 +4465,12 @@
         <v>26610</v>
       </c>
       <c r="E10" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>26610</v>
       </c>
       <c r="H10" s="2">
@@ -4120,34 +4482,34 @@
         <v>400</v>
       </c>
       <c r="J10" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1596.6</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>31267.599999999999</v>
       </c>
       <c r="L10" s="2">
         <v>0</v>
       </c>
       <c r="M10" s="2">
-        <f>10%*D10</f>
+        <f t="shared" si="20"/>
         <v>2661</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>2661</v>
       </c>
       <c r="P10" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>33928.6</v>
       </c>
       <c r="Q10" s="2">
         <v>800</v>
       </c>
       <c r="R10" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>5322</v>
       </c>
       <c r="S10" s="2">
@@ -4155,33 +4517,34 @@
       </c>
       <c r="T10" s="2"/>
       <c r="U10" s="2">
+        <f t="shared" si="16"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V10" s="2"/>
+      <c r="W10" s="4">
+        <f t="shared" si="17"/>
+        <v>14315.2</v>
+      </c>
+      <c r="X10" s="2">
+        <f>Y10+U10</f>
+        <v>22806.6</v>
+      </c>
+      <c r="Y10" s="10">
+        <f>P10-W10</f>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="Z10" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA10" s="2">
         <f t="shared" si="18"/>
-        <v>3193.2</v>
-      </c>
-      <c r="V10" s="4">
-        <f t="shared" si="19"/>
-        <v>14315.2</v>
-      </c>
-      <c r="W10" s="2">
-        <f t="shared" si="20"/>
-        <v>22806.6</v>
-      </c>
-      <c r="X10" s="10">
-        <f t="shared" si="21"/>
         <v>19613.399999999998</v>
       </c>
-      <c r="Y10" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Z10" s="2">
-        <f t="shared" si="22"/>
-        <v>19613.399999999998</v>
-      </c>
-      <c r="AA10" s="2"/>
       <c r="AB10" s="2"/>
-    </row>
-    <row r="11" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC10" s="2"/>
+    </row>
+    <row r="11" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -4189,12 +4552,12 @@
         <v>26610</v>
       </c>
       <c r="E11" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>26610</v>
       </c>
       <c r="H11" s="2">
@@ -4206,34 +4569,34 @@
         <v>400</v>
       </c>
       <c r="J11" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1596.6</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>31267.599999999999</v>
       </c>
       <c r="L11" s="2">
         <v>0</v>
       </c>
       <c r="M11" s="2">
-        <f>10%*D11</f>
+        <f t="shared" si="20"/>
         <v>2661</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>2661</v>
       </c>
       <c r="P11" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>33928.6</v>
       </c>
       <c r="Q11" s="2">
         <v>800</v>
       </c>
       <c r="R11" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>5322</v>
       </c>
       <c r="S11" s="2">
@@ -4241,33 +4604,34 @@
       </c>
       <c r="T11" s="2"/>
       <c r="U11" s="2">
+        <f t="shared" si="16"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V11" s="2"/>
+      <c r="W11" s="4">
+        <f t="shared" si="17"/>
+        <v>14315.2</v>
+      </c>
+      <c r="X11" s="2">
+        <f>Y11+U11</f>
+        <v>22806.6</v>
+      </c>
+      <c r="Y11" s="10">
+        <f>P11-W11</f>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="Z11" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA11" s="2">
         <f t="shared" si="18"/>
-        <v>3193.2</v>
-      </c>
-      <c r="V11" s="4">
-        <f t="shared" si="19"/>
-        <v>14315.2</v>
-      </c>
-      <c r="W11" s="2">
-        <f t="shared" si="20"/>
-        <v>22806.6</v>
-      </c>
-      <c r="X11" s="10">
-        <f t="shared" si="21"/>
         <v>19613.399999999998</v>
       </c>
-      <c r="Y11" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Z11" s="2">
-        <f t="shared" si="22"/>
-        <v>19613.399999999998</v>
-      </c>
-      <c r="AA11" s="2"/>
       <c r="AB11" s="2"/>
-    </row>
-    <row r="12" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC11" s="2"/>
+    </row>
+    <row r="12" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -4275,12 +4639,12 @@
         <v>26610</v>
       </c>
       <c r="E12" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>26610</v>
       </c>
       <c r="H12" s="2">
@@ -4292,34 +4656,34 @@
         <v>400</v>
       </c>
       <c r="J12" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1596.6</v>
       </c>
       <c r="K12" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>31267.599999999999</v>
       </c>
       <c r="L12" s="2">
         <v>0</v>
       </c>
       <c r="M12" s="2">
-        <f>10%*D12</f>
+        <f t="shared" si="20"/>
         <v>2661</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>2661</v>
       </c>
       <c r="P12" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>33928.6</v>
       </c>
       <c r="Q12" s="2">
         <v>800</v>
       </c>
       <c r="R12" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>5322</v>
       </c>
       <c r="S12" s="2">
@@ -4327,33 +4691,34 @@
       </c>
       <c r="T12" s="2"/>
       <c r="U12" s="2">
+        <f t="shared" si="16"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V12" s="2"/>
+      <c r="W12" s="4">
+        <f t="shared" si="17"/>
+        <v>14315.2</v>
+      </c>
+      <c r="X12" s="2">
+        <f>Y12+U12</f>
+        <v>22806.6</v>
+      </c>
+      <c r="Y12" s="10">
+        <f>P12-W12</f>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="Z12" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA12" s="2">
         <f t="shared" si="18"/>
-        <v>3193.2</v>
-      </c>
-      <c r="V12" s="4">
-        <f t="shared" si="19"/>
-        <v>14315.2</v>
-      </c>
-      <c r="W12" s="2">
-        <f t="shared" si="20"/>
-        <v>22806.6</v>
-      </c>
-      <c r="X12" s="10">
-        <f t="shared" si="21"/>
         <v>19613.399999999998</v>
       </c>
-      <c r="Y12" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Z12" s="2">
-        <f t="shared" si="22"/>
-        <v>19613.399999999998</v>
-      </c>
-      <c r="AA12" s="2"/>
       <c r="AB12" s="2"/>
-    </row>
-    <row r="13" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC12" s="2"/>
+    </row>
+    <row r="13" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -4361,12 +4726,12 @@
         <v>26610</v>
       </c>
       <c r="E13" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>26610</v>
       </c>
       <c r="H13" s="2">
@@ -4378,36 +4743,36 @@
         <v>400</v>
       </c>
       <c r="J13" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1596.6</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>31267.599999999999</v>
       </c>
       <c r="L13" s="2">
         <v>0</v>
       </c>
       <c r="M13" s="2">
-        <f>10%*D13</f>
+        <f t="shared" si="20"/>
         <v>2661</v>
       </c>
       <c r="N13" s="2">
         <v>10000</v>
       </c>
       <c r="O13" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>12661</v>
       </c>
       <c r="P13" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>43928.6</v>
       </c>
       <c r="Q13" s="2">
         <v>800</v>
       </c>
       <c r="R13" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>5322</v>
       </c>
       <c r="S13" s="2">
@@ -4415,33 +4780,34 @@
       </c>
       <c r="T13" s="2"/>
       <c r="U13" s="2">
+        <f t="shared" si="16"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V13" s="2"/>
+      <c r="W13" s="4">
+        <f t="shared" si="17"/>
+        <v>14315.2</v>
+      </c>
+      <c r="X13" s="2">
+        <f>Y13+U13</f>
+        <v>32806.6</v>
+      </c>
+      <c r="Y13" s="10">
+        <f>P13-W13</f>
+        <v>29613.399999999998</v>
+      </c>
+      <c r="Z13" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA13" s="2">
         <f t="shared" si="18"/>
-        <v>3193.2</v>
-      </c>
-      <c r="V13" s="4">
-        <f t="shared" si="19"/>
-        <v>14315.2</v>
-      </c>
-      <c r="W13" s="2">
-        <f t="shared" si="20"/>
-        <v>32806.6</v>
-      </c>
-      <c r="X13" s="10">
-        <f t="shared" si="21"/>
         <v>29613.399999999998</v>
       </c>
-      <c r="Y13" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Z13" s="2">
-        <f t="shared" si="22"/>
-        <v>29613.399999999998</v>
-      </c>
-      <c r="AA13" s="2"/>
       <c r="AB13" s="2"/>
-    </row>
-    <row r="14" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC13" s="2"/>
+    </row>
+    <row r="14" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -4449,12 +4815,12 @@
         <v>26610</v>
       </c>
       <c r="E14" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>26610</v>
       </c>
       <c r="H14" s="2">
@@ -4466,34 +4832,34 @@
         <v>400</v>
       </c>
       <c r="J14" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1596.6</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>31267.599999999999</v>
       </c>
       <c r="L14" s="2">
         <v>0</v>
       </c>
       <c r="M14" s="2">
-        <f>10%*D14</f>
+        <f t="shared" si="20"/>
         <v>2661</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>2661</v>
       </c>
       <c r="P14" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>33928.6</v>
       </c>
       <c r="Q14" s="2">
         <v>800</v>
       </c>
       <c r="R14" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>5322</v>
       </c>
       <c r="S14" s="2">
@@ -4501,33 +4867,34 @@
       </c>
       <c r="T14" s="2"/>
       <c r="U14" s="2">
+        <f t="shared" si="16"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V14" s="2"/>
+      <c r="W14" s="4">
+        <f t="shared" si="17"/>
+        <v>14315.2</v>
+      </c>
+      <c r="X14" s="2">
+        <f>Y14+U14</f>
+        <v>22806.6</v>
+      </c>
+      <c r="Y14" s="10">
+        <f>P14-W14</f>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="Z14" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA14" s="2">
         <f t="shared" si="18"/>
-        <v>3193.2</v>
-      </c>
-      <c r="V14" s="4">
-        <f t="shared" si="19"/>
-        <v>14315.2</v>
-      </c>
-      <c r="W14" s="2">
-        <f t="shared" si="20"/>
-        <v>22806.6</v>
-      </c>
-      <c r="X14" s="10">
-        <f t="shared" si="21"/>
         <v>19613.399999999998</v>
       </c>
-      <c r="Y14" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Z14" s="2">
-        <f t="shared" si="22"/>
-        <v>19613.399999999998</v>
-      </c>
-      <c r="AA14" s="2"/>
       <c r="AB14" s="2"/>
-    </row>
-    <row r="15" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC14" s="2"/>
+    </row>
+    <row r="15" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -4535,12 +4902,12 @@
         <v>26610</v>
       </c>
       <c r="E15" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>26610</v>
       </c>
       <c r="H15" s="2">
@@ -4552,34 +4919,34 @@
         <v>400</v>
       </c>
       <c r="J15" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1596.6</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>31267.599999999999</v>
       </c>
       <c r="L15" s="2">
         <v>0</v>
       </c>
       <c r="M15" s="2">
-        <f>10%*D15</f>
+        <f t="shared" si="20"/>
         <v>2661</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>2661</v>
       </c>
       <c r="P15" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>33928.6</v>
       </c>
       <c r="Q15" s="2">
         <v>800</v>
       </c>
       <c r="R15" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>5322</v>
       </c>
       <c r="S15" s="2">
@@ -4587,33 +4954,34 @@
       </c>
       <c r="T15" s="2"/>
       <c r="U15" s="2">
+        <f t="shared" si="16"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V15" s="2"/>
+      <c r="W15" s="4">
+        <f t="shared" si="17"/>
+        <v>14315.2</v>
+      </c>
+      <c r="X15" s="2">
+        <f>Y15+U15</f>
+        <v>22806.6</v>
+      </c>
+      <c r="Y15" s="10">
+        <f>P15-W15</f>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="Z15" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA15" s="2">
         <f t="shared" si="18"/>
-        <v>3193.2</v>
-      </c>
-      <c r="V15" s="4">
-        <f t="shared" si="19"/>
-        <v>14315.2</v>
-      </c>
-      <c r="W15" s="2">
-        <f t="shared" si="20"/>
-        <v>22806.6</v>
-      </c>
-      <c r="X15" s="10">
-        <f t="shared" si="21"/>
         <v>19613.399999999998</v>
       </c>
-      <c r="Y15" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="2">
-        <f t="shared" si="22"/>
-        <v>19613.399999999998</v>
-      </c>
-      <c r="AA15" s="2"/>
       <c r="AB15" s="2"/>
-    </row>
-    <row r="16" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC15" s="2"/>
+    </row>
+    <row r="16" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -4621,12 +4989,12 @@
         <v>26610</v>
       </c>
       <c r="E16" s="4">
-        <f t="shared" ref="E6:E18" si="24">ROUNDUP(D16/30,0)</f>
+        <f t="shared" ref="E16" si="21">ROUNDUP(D16/30,0)</f>
         <v>887</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>27497</v>
       </c>
       <c r="H16" s="2">
@@ -4638,34 +5006,34 @@
         <v>400</v>
       </c>
       <c r="J16" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1649.82</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>32296.52</v>
       </c>
       <c r="L16" s="2">
         <v>0</v>
       </c>
       <c r="M16" s="2">
-        <f>10%*D16</f>
+        <f t="shared" si="20"/>
         <v>2661</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>2661</v>
       </c>
       <c r="P16" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>34957.520000000004</v>
       </c>
       <c r="Q16" s="2">
         <v>800</v>
       </c>
       <c r="R16" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>5499.4000000000005</v>
       </c>
       <c r="S16" s="2">
@@ -4673,33 +5041,34 @@
       </c>
       <c r="T16" s="2"/>
       <c r="U16" s="2">
+        <f t="shared" si="16"/>
+        <v>3299.64</v>
+      </c>
+      <c r="V16" s="2"/>
+      <c r="W16" s="4">
+        <f t="shared" si="17"/>
+        <v>14599.04</v>
+      </c>
+      <c r="X16" s="2">
+        <f>Y16+U16</f>
+        <v>23658.120000000003</v>
+      </c>
+      <c r="Y16" s="10">
+        <f>P16-W16</f>
+        <v>20358.480000000003</v>
+      </c>
+      <c r="Z16" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="2">
         <f t="shared" si="18"/>
-        <v>3299.64</v>
-      </c>
-      <c r="V16" s="4">
-        <f t="shared" si="19"/>
-        <v>14599.04</v>
-      </c>
-      <c r="W16" s="2">
-        <f t="shared" si="20"/>
-        <v>23658.120000000003</v>
-      </c>
-      <c r="X16" s="10">
-        <f t="shared" si="21"/>
         <v>20358.480000000003</v>
       </c>
-      <c r="Y16" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Z16" s="2">
-        <f t="shared" si="22"/>
-        <v>20358.480000000003</v>
-      </c>
-      <c r="AA16" s="2"/>
       <c r="AB16" s="2"/>
-    </row>
-    <row r="17" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC16" s="2"/>
+    </row>
+    <row r="17" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -4721,15 +5090,16 @@
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
-      <c r="V17" s="4"/>
-      <c r="W17" s="2"/>
-      <c r="X17" s="10"/>
-      <c r="Y17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="10"/>
       <c r="Z17" s="2"/>
       <c r="AA17" s="2"/>
       <c r="AB17" s="2"/>
-    </row>
-    <row r="18" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC17" s="2"/>
+    </row>
+    <row r="18" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -4742,7 +5112,7 @@
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="8">
-        <f t="shared" ref="G18:G29" si="25">SUM(D18:F18)</f>
+        <f t="shared" ref="G18:G29" si="22">SUM(D18:F18)</f>
         <v>29564</v>
       </c>
       <c r="H18" s="2">
@@ -4754,11 +5124,11 @@
         <v>400</v>
       </c>
       <c r="J18" s="2">
-        <f t="shared" ref="J18:J29" si="26">6%*G18</f>
+        <f t="shared" ref="J18:J29" si="23">6%*G18</f>
         <v>1773.84</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" ref="K18:K29" si="27">SUM(G18:J18)</f>
+        <f t="shared" ref="K18:K29" si="24">SUM(G18:J18)</f>
         <v>34694.239999999998</v>
       </c>
       <c r="L18" s="2">
@@ -4770,18 +5140,18 @@
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="4">
-        <f t="shared" ref="O18:O29" si="28">SUM(L18:N18)</f>
+        <f t="shared" ref="O18:O29" si="25">SUM(L18:N18)</f>
         <v>2861</v>
       </c>
       <c r="P18" s="8">
-        <f t="shared" ref="P18:P29" si="29">K18+O18</f>
+        <f t="shared" ref="P18:P29" si="26">K18+O18</f>
         <v>37555.24</v>
       </c>
       <c r="Q18" s="2">
         <v>800</v>
       </c>
       <c r="R18" s="2">
-        <f t="shared" ref="R18:R29" si="30">H18*2</f>
+        <f t="shared" ref="R18:R29" si="27">H18*2</f>
         <v>5912.8</v>
       </c>
       <c r="S18" s="2">
@@ -4789,33 +5159,34 @@
       </c>
       <c r="T18" s="2"/>
       <c r="U18" s="2">
-        <f t="shared" ref="U18:U29" si="31">J18*2</f>
+        <f t="shared" ref="U18:U29" si="28">J18*2</f>
         <v>3547.68</v>
       </c>
-      <c r="V18" s="4">
-        <f t="shared" ref="V18:V29" si="32">SUM(Q18:U18)</f>
+      <c r="V18" s="2"/>
+      <c r="W18" s="4">
+        <f t="shared" ref="W18:W29" si="29">SUM(Q18:U18)</f>
         <v>15260.48</v>
       </c>
-      <c r="W18" s="2">
-        <f t="shared" ref="W18:W29" si="33">X18+U18</f>
+      <c r="X18" s="2">
+        <f>Y18+U18</f>
         <v>25842.44</v>
       </c>
-      <c r="X18" s="10">
-        <f t="shared" ref="X18:X29" si="34">P18-V18</f>
+      <c r="Y18" s="10">
+        <f>P18-W18</f>
         <v>22294.76</v>
       </c>
-      <c r="Y18" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z18" s="2">
-        <f t="shared" ref="Z18:Z29" si="35">X18-Y18</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA18" s="2">
+        <f t="shared" ref="AA18:AA29" si="30">Y18-Z18</f>
         <v>22294.76</v>
       </c>
-      <c r="AA18" s="2"/>
       <c r="AB18" s="2"/>
-    </row>
-    <row r="19" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC18" s="2"/>
+    </row>
+    <row r="19" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -4823,12 +5194,12 @@
         <v>28610</v>
       </c>
       <c r="E19" s="4">
-        <f t="shared" ref="E19:E28" si="36">ROUNDUP(D19/30,0)*1</f>
+        <f t="shared" ref="E19:E28" si="31">ROUNDUP(D19/30,0)*1</f>
         <v>954</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>29564</v>
       </c>
       <c r="H19" s="2">
@@ -4840,11 +5211,11 @@
         <v>400</v>
       </c>
       <c r="J19" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>1773.84</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L19" s="2">
@@ -4856,18 +5227,18 @@
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2861</v>
       </c>
       <c r="P19" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>37555.24</v>
       </c>
       <c r="Q19" s="2">
         <v>800</v>
       </c>
       <c r="R19" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>5912.8</v>
       </c>
       <c r="S19" s="2">
@@ -4875,33 +5246,34 @@
       </c>
       <c r="T19" s="2"/>
       <c r="U19" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>3547.68</v>
       </c>
-      <c r="V19" s="4">
-        <f t="shared" si="32"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="4">
+        <f t="shared" si="29"/>
         <v>15260.48</v>
       </c>
-      <c r="W19" s="2">
-        <f t="shared" si="33"/>
+      <c r="X19" s="2">
+        <f>Y19+U19</f>
         <v>25842.44</v>
       </c>
-      <c r="X19" s="10">
-        <f t="shared" si="34"/>
+      <c r="Y19" s="10">
+        <f>P19-W19</f>
         <v>22294.76</v>
       </c>
-      <c r="Y19" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z19" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA19" s="2">
+        <f t="shared" si="30"/>
         <v>22294.76</v>
       </c>
-      <c r="AA19" s="2"/>
       <c r="AB19" s="2"/>
-    </row>
-    <row r="20" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC19" s="2"/>
+    </row>
+    <row r="20" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -4909,12 +5281,12 @@
         <v>28610</v>
       </c>
       <c r="E20" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>954</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>29564</v>
       </c>
       <c r="H20" s="2">
@@ -4926,11 +5298,11 @@
         <v>400</v>
       </c>
       <c r="J20" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>1773.84</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L20" s="2">
@@ -4942,18 +5314,18 @@
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>31471</v>
       </c>
       <c r="P20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>66165.239999999991</v>
       </c>
       <c r="Q20" s="2">
         <v>800</v>
       </c>
       <c r="R20" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>5912.8</v>
       </c>
       <c r="S20" s="2">
@@ -4961,30 +5333,31 @@
       </c>
       <c r="T20" s="2"/>
       <c r="U20" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>3547.68</v>
       </c>
-      <c r="V20" s="4">
-        <f t="shared" si="32"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="4">
+        <f t="shared" si="29"/>
         <v>15260.48</v>
       </c>
-      <c r="W20" s="2">
-        <f t="shared" si="33"/>
+      <c r="X20" s="2">
+        <f>Y20+U20</f>
         <v>54452.439999999995</v>
       </c>
-      <c r="X20" s="10">
-        <f t="shared" si="34"/>
+      <c r="Y20" s="10">
+        <f>P20-W20</f>
         <v>50904.759999999995</v>
       </c>
-      <c r="Y20" s="2"/>
-      <c r="Z20" s="2">
-        <f t="shared" si="35"/>
+      <c r="Z20" s="2"/>
+      <c r="AA20" s="2">
+        <f t="shared" si="30"/>
         <v>50904.759999999995</v>
       </c>
-      <c r="AA20" s="2"/>
       <c r="AB20" s="2"/>
-    </row>
-    <row r="21" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC20" s="2"/>
+    </row>
+    <row r="21" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -4992,12 +5365,12 @@
         <v>28610</v>
       </c>
       <c r="E21" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>954</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>29564</v>
       </c>
       <c r="H21" s="2">
@@ -5009,34 +5382,34 @@
         <v>400</v>
       </c>
       <c r="J21" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>1773.84</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L21" s="2">
         <v>0</v>
       </c>
       <c r="M21" s="2">
-        <f>10%*D21</f>
+        <f t="shared" ref="M21:M29" si="32">10%*D21</f>
         <v>2861</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2861</v>
       </c>
       <c r="P21" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>37555.24</v>
       </c>
       <c r="Q21" s="2">
         <v>800</v>
       </c>
       <c r="R21" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>5912.8</v>
       </c>
       <c r="S21" s="2">
@@ -5044,33 +5417,34 @@
       </c>
       <c r="T21" s="2"/>
       <c r="U21" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>3547.68</v>
       </c>
-      <c r="V21" s="4">
-        <f t="shared" si="32"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="4">
+        <f t="shared" si="29"/>
         <v>15260.48</v>
       </c>
-      <c r="W21" s="2">
-        <f t="shared" si="33"/>
+      <c r="X21" s="2">
+        <f>Y21+U21</f>
         <v>25842.44</v>
       </c>
-      <c r="X21" s="10">
-        <f t="shared" si="34"/>
+      <c r="Y21" s="10">
+        <f>P21-W21</f>
         <v>22294.76</v>
       </c>
-      <c r="Y21" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z21" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA21" s="2">
+        <f t="shared" si="30"/>
         <v>22294.76</v>
       </c>
-      <c r="AA21" s="2"/>
       <c r="AB21" s="2"/>
-    </row>
-    <row r="22" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC21" s="2"/>
+    </row>
+    <row r="22" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -5078,12 +5452,12 @@
         <v>28610</v>
       </c>
       <c r="E22" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>954</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>29564</v>
       </c>
       <c r="H22" s="2">
@@ -5095,34 +5469,34 @@
         <v>400</v>
       </c>
       <c r="J22" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>1773.84</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L22" s="2">
         <v>0</v>
       </c>
       <c r="M22" s="2">
-        <f>10%*D22</f>
+        <f t="shared" si="32"/>
         <v>2861</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2861</v>
       </c>
       <c r="P22" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>37555.24</v>
       </c>
       <c r="Q22" s="2">
         <v>800</v>
       </c>
       <c r="R22" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>5912.8</v>
       </c>
       <c r="S22" s="2">
@@ -5130,33 +5504,34 @@
       </c>
       <c r="T22" s="2"/>
       <c r="U22" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>3547.68</v>
       </c>
-      <c r="V22" s="4">
-        <f t="shared" si="32"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="4">
+        <f t="shared" si="29"/>
         <v>15260.48</v>
       </c>
-      <c r="W22" s="2">
-        <f t="shared" si="33"/>
+      <c r="X22" s="2">
+        <f>Y22+U22</f>
         <v>25842.44</v>
       </c>
-      <c r="X22" s="10">
-        <f t="shared" si="34"/>
+      <c r="Y22" s="10">
+        <f>P22-W22</f>
         <v>22294.76</v>
       </c>
-      <c r="Y22" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z22" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA22" s="2">
+        <f t="shared" si="30"/>
         <v>22294.76</v>
       </c>
-      <c r="AA22" s="2"/>
       <c r="AB22" s="2"/>
-    </row>
-    <row r="23" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC22" s="2"/>
+    </row>
+    <row r="23" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -5164,12 +5539,12 @@
         <v>28610</v>
       </c>
       <c r="E23" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>954</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>29564</v>
       </c>
       <c r="H23" s="2">
@@ -5181,34 +5556,34 @@
         <v>400</v>
       </c>
       <c r="J23" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>1773.84</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L23" s="2">
         <v>0</v>
       </c>
       <c r="M23" s="2">
-        <f>10%*D23</f>
+        <f t="shared" si="32"/>
         <v>2861</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2861</v>
       </c>
       <c r="P23" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>37555.24</v>
       </c>
       <c r="Q23" s="2">
         <v>800</v>
       </c>
       <c r="R23" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>5912.8</v>
       </c>
       <c r="S23" s="2">
@@ -5216,33 +5591,34 @@
       </c>
       <c r="T23" s="2"/>
       <c r="U23" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>3547.68</v>
       </c>
-      <c r="V23" s="4">
-        <f t="shared" si="32"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="4">
+        <f t="shared" si="29"/>
         <v>15260.48</v>
       </c>
-      <c r="W23" s="2">
-        <f t="shared" si="33"/>
+      <c r="X23" s="2">
+        <f>Y23+U23</f>
         <v>25842.44</v>
       </c>
-      <c r="X23" s="10">
-        <f t="shared" si="34"/>
+      <c r="Y23" s="10">
+        <f>P23-W23</f>
         <v>22294.76</v>
       </c>
-      <c r="Y23" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z23" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA23" s="2">
+        <f t="shared" si="30"/>
         <v>22294.76</v>
       </c>
-      <c r="AA23" s="2"/>
       <c r="AB23" s="2"/>
-    </row>
-    <row r="24" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC23" s="2"/>
+    </row>
+    <row r="24" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -5250,12 +5626,12 @@
         <v>28610</v>
       </c>
       <c r="E24" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>954</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>29564</v>
       </c>
       <c r="H24" s="2">
@@ -5267,34 +5643,34 @@
         <v>400</v>
       </c>
       <c r="J24" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>1773.84</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L24" s="2">
         <v>0</v>
       </c>
       <c r="M24" s="2">
-        <f>10%*D24</f>
+        <f t="shared" si="32"/>
         <v>2861</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2861</v>
       </c>
       <c r="P24" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>37555.24</v>
       </c>
       <c r="Q24" s="2">
         <v>800</v>
       </c>
       <c r="R24" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>5912.8</v>
       </c>
       <c r="S24" s="2">
@@ -5302,33 +5678,34 @@
       </c>
       <c r="T24" s="2"/>
       <c r="U24" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>3547.68</v>
       </c>
-      <c r="V24" s="4">
-        <f t="shared" si="32"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="4">
+        <f t="shared" si="29"/>
         <v>15260.48</v>
       </c>
-      <c r="W24" s="2">
-        <f t="shared" si="33"/>
+      <c r="X24" s="2">
+        <f>Y24+U24</f>
         <v>25842.44</v>
       </c>
-      <c r="X24" s="10">
-        <f t="shared" si="34"/>
+      <c r="Y24" s="10">
+        <f>P24-W24</f>
         <v>22294.76</v>
       </c>
-      <c r="Y24" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z24" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA24" s="2">
+        <f t="shared" si="30"/>
         <v>22294.76</v>
       </c>
-      <c r="AA24" s="2"/>
       <c r="AB24" s="2"/>
-    </row>
-    <row r="25" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC24" s="2"/>
+    </row>
+    <row r="25" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -5336,12 +5713,12 @@
         <v>28610</v>
       </c>
       <c r="E25" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>954</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>29564</v>
       </c>
       <c r="H25" s="2">
@@ -5353,34 +5730,34 @@
         <v>400</v>
       </c>
       <c r="J25" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>1773.84</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L25" s="2">
         <v>0</v>
       </c>
       <c r="M25" s="2">
-        <f>10%*D25</f>
+        <f t="shared" si="32"/>
         <v>2861</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2861</v>
       </c>
       <c r="P25" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>37555.24</v>
       </c>
       <c r="Q25" s="2">
         <v>800</v>
       </c>
       <c r="R25" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>5912.8</v>
       </c>
       <c r="S25" s="2">
@@ -5388,33 +5765,34 @@
       </c>
       <c r="T25" s="2"/>
       <c r="U25" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>3547.68</v>
       </c>
-      <c r="V25" s="4">
-        <f t="shared" si="32"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="4">
+        <f t="shared" si="29"/>
         <v>15260.48</v>
       </c>
-      <c r="W25" s="2">
-        <f t="shared" si="33"/>
+      <c r="X25" s="2">
+        <f>Y25+U25</f>
         <v>25842.44</v>
       </c>
-      <c r="X25" s="10">
-        <f t="shared" si="34"/>
+      <c r="Y25" s="10">
+        <f>P25-W25</f>
         <v>22294.76</v>
       </c>
-      <c r="Y25" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z25" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA25" s="2">
+        <f t="shared" si="30"/>
         <v>22294.76</v>
       </c>
-      <c r="AA25" s="2"/>
       <c r="AB25" s="2"/>
-    </row>
-    <row r="26" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC25" s="2"/>
+    </row>
+    <row r="26" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -5422,12 +5800,12 @@
         <v>28610</v>
       </c>
       <c r="E26" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>954</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>29564</v>
       </c>
       <c r="H26" s="2">
@@ -5439,36 +5817,36 @@
         <v>400</v>
       </c>
       <c r="J26" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>1773.84</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L26" s="2">
         <v>0</v>
       </c>
       <c r="M26" s="2">
-        <f>10%*D26</f>
+        <f t="shared" si="32"/>
         <v>2861</v>
       </c>
       <c r="N26" s="2">
         <v>10000</v>
       </c>
       <c r="O26" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>12861</v>
       </c>
       <c r="P26" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>47555.24</v>
       </c>
       <c r="Q26" s="2">
         <v>800</v>
       </c>
       <c r="R26" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>5912.8</v>
       </c>
       <c r="S26" s="2">
@@ -5476,33 +5854,34 @@
       </c>
       <c r="T26" s="2"/>
       <c r="U26" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>3547.68</v>
       </c>
-      <c r="V26" s="4">
-        <f t="shared" si="32"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="4">
+        <f t="shared" si="29"/>
         <v>15260.48</v>
       </c>
-      <c r="W26" s="2">
-        <f t="shared" si="33"/>
+      <c r="X26" s="2">
+        <f>Y26+U26</f>
         <v>35842.439999999995</v>
       </c>
-      <c r="X26" s="10">
-        <f t="shared" si="34"/>
+      <c r="Y26" s="10">
+        <f>P26-W26</f>
         <v>32294.76</v>
       </c>
-      <c r="Y26" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z26" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA26" s="2">
+        <f t="shared" si="30"/>
         <v>32294.76</v>
       </c>
-      <c r="AA26" s="2"/>
       <c r="AB26" s="2"/>
-    </row>
-    <row r="27" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC26" s="2"/>
+    </row>
+    <row r="27" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -5510,12 +5889,12 @@
         <v>28610</v>
       </c>
       <c r="E27" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>954</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>29564</v>
       </c>
       <c r="H27" s="2">
@@ -5527,34 +5906,34 @@
         <v>400</v>
       </c>
       <c r="J27" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>1773.84</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L27" s="2">
         <v>0</v>
       </c>
       <c r="M27" s="2">
-        <f>10%*D27</f>
+        <f t="shared" si="32"/>
         <v>2861</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2861</v>
       </c>
       <c r="P27" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>37555.24</v>
       </c>
       <c r="Q27" s="2">
         <v>800</v>
       </c>
       <c r="R27" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>5912.8</v>
       </c>
       <c r="S27" s="2">
@@ -5562,33 +5941,34 @@
       </c>
       <c r="T27" s="2"/>
       <c r="U27" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>3547.68</v>
       </c>
-      <c r="V27" s="4">
-        <f t="shared" si="32"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="4">
+        <f t="shared" si="29"/>
         <v>15260.48</v>
       </c>
-      <c r="W27" s="2">
-        <f t="shared" si="33"/>
+      <c r="X27" s="2">
+        <f>Y27+U27</f>
         <v>25842.44</v>
       </c>
-      <c r="X27" s="10">
-        <f t="shared" si="34"/>
+      <c r="Y27" s="10">
+        <f>P27-W27</f>
         <v>22294.76</v>
       </c>
-      <c r="Y27" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z27" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA27" s="2">
+        <f t="shared" si="30"/>
         <v>22294.76</v>
       </c>
-      <c r="AA27" s="2"/>
       <c r="AB27" s="2"/>
-    </row>
-    <row r="28" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC27" s="2"/>
+    </row>
+    <row r="28" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -5596,12 +5976,12 @@
         <v>28610</v>
       </c>
       <c r="E28" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>954</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>29564</v>
       </c>
       <c r="H28" s="2">
@@ -5613,34 +5993,34 @@
         <v>400</v>
       </c>
       <c r="J28" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>1773.84</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L28" s="2">
         <v>0</v>
       </c>
       <c r="M28" s="2">
-        <f>10%*D28</f>
+        <f t="shared" si="32"/>
         <v>2861</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2861</v>
       </c>
       <c r="P28" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>37555.24</v>
       </c>
       <c r="Q28" s="2">
         <v>800</v>
       </c>
       <c r="R28" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>5912.8</v>
       </c>
       <c r="S28" s="2">
@@ -5648,33 +6028,34 @@
       </c>
       <c r="T28" s="2"/>
       <c r="U28" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>3547.68</v>
       </c>
-      <c r="V28" s="4">
-        <f t="shared" si="32"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="4">
+        <f t="shared" si="29"/>
         <v>15260.48</v>
       </c>
-      <c r="W28" s="2">
-        <f t="shared" si="33"/>
+      <c r="X28" s="2">
+        <f>Y28+U28</f>
         <v>25842.44</v>
       </c>
-      <c r="X28" s="10">
-        <f t="shared" si="34"/>
+      <c r="Y28" s="10">
+        <f>P28-W28</f>
         <v>22294.76</v>
       </c>
-      <c r="Y28" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z28" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA28" s="2">
+        <f t="shared" si="30"/>
         <v>22294.76</v>
       </c>
-      <c r="AA28" s="2"/>
       <c r="AB28" s="2"/>
-    </row>
-    <row r="29" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC28" s="2"/>
+    </row>
+    <row r="29" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -5687,7 +6068,7 @@
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>30518</v>
       </c>
       <c r="H29" s="2">
@@ -5699,34 +6080,34 @@
         <v>400</v>
       </c>
       <c r="J29" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>1831.08</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>35800.880000000005</v>
       </c>
       <c r="L29" s="2">
         <v>0</v>
       </c>
       <c r="M29" s="2">
-        <f>10%*D29</f>
+        <f t="shared" si="32"/>
         <v>2861</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2861</v>
       </c>
       <c r="P29" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>38661.880000000005</v>
       </c>
       <c r="Q29" s="2">
         <v>800</v>
       </c>
       <c r="R29" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>6103.6</v>
       </c>
       <c r="S29" s="2">
@@ -5734,33 +6115,34 @@
       </c>
       <c r="T29" s="2"/>
       <c r="U29" s="2">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>3662.16</v>
       </c>
-      <c r="V29" s="4">
-        <f t="shared" si="32"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="4">
+        <f t="shared" si="29"/>
         <v>15565.76</v>
       </c>
-      <c r="W29" s="2">
-        <f t="shared" si="33"/>
+      <c r="X29" s="2">
+        <f>Y29+U29</f>
         <v>26758.280000000002</v>
       </c>
-      <c r="X29" s="10">
-        <f t="shared" si="34"/>
+      <c r="Y29" s="10">
+        <f>P29-W29</f>
         <v>23096.120000000003</v>
       </c>
-      <c r="Y29" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z29" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA29" s="2">
+        <f t="shared" si="30"/>
         <v>23096.120000000003</v>
       </c>
-      <c r="AA29" s="2"/>
       <c r="AB29" s="2"/>
-    </row>
-    <row r="30" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC29" s="2"/>
+    </row>
+    <row r="30" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -5782,15 +6164,16 @@
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
-      <c r="V30" s="4"/>
-      <c r="W30" s="2"/>
-      <c r="X30" s="10"/>
-      <c r="Y30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="4"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="10"/>
       <c r="Z30" s="2"/>
       <c r="AA30" s="2"/>
       <c r="AB30" s="2"/>
-    </row>
-    <row r="31" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC30" s="2"/>
+    </row>
+    <row r="31" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -5803,7 +6186,7 @@
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="8">
-        <f t="shared" ref="G31:G42" si="37">SUM(D31:F31)</f>
+        <f t="shared" ref="G31:G42" si="33">SUM(D31:F31)</f>
         <v>35096</v>
       </c>
       <c r="H31" s="2">
@@ -5815,11 +6198,11 @@
         <v>400</v>
       </c>
       <c r="J31" s="2">
-        <f t="shared" ref="J31:J42" si="38">6%*G31</f>
+        <f t="shared" ref="J31:J42" si="34">6%*G31</f>
         <v>2105.7599999999998</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" ref="K31:K42" si="39">SUM(G31:J31)</f>
+        <f t="shared" ref="K31:K42" si="35">SUM(G31:J31)</f>
         <v>41111.360000000001</v>
       </c>
       <c r="L31" s="2">
@@ -5831,18 +6214,18 @@
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="4">
-        <f t="shared" ref="O31:O42" si="40">SUM(L31:N31)</f>
+        <f t="shared" ref="O31:O42" si="36">SUM(L31:N31)</f>
         <v>3290.2000000000003</v>
       </c>
       <c r="P31" s="8">
-        <f t="shared" ref="P31:P42" si="41">K31+O31</f>
+        <f t="shared" ref="P31:P42" si="37">K31+O31</f>
         <v>44401.56</v>
       </c>
       <c r="Q31" s="2">
         <v>800</v>
       </c>
       <c r="R31" s="2">
-        <f t="shared" ref="R31:R42" si="42">H31*2</f>
+        <f t="shared" ref="R31:R42" si="38">H31*2</f>
         <v>7019.2000000000007</v>
       </c>
       <c r="S31" s="2">
@@ -5850,33 +6233,34 @@
       </c>
       <c r="T31" s="2"/>
       <c r="U31" s="2">
-        <f t="shared" ref="U31:U42" si="43">J31*2</f>
+        <f t="shared" ref="U31:U42" si="39">J31*2</f>
         <v>4211.5199999999995</v>
       </c>
-      <c r="V31" s="4">
-        <f t="shared" ref="V31:V42" si="44">SUM(Q31:U31)</f>
+      <c r="V31" s="2"/>
+      <c r="W31" s="4">
+        <f t="shared" ref="W31:W42" si="40">SUM(Q31:U31)</f>
         <v>17030.72</v>
       </c>
-      <c r="W31" s="2">
-        <f t="shared" ref="W31:W42" si="45">X31+U31</f>
+      <c r="X31" s="2">
+        <f>Y31+U31</f>
         <v>31582.359999999997</v>
       </c>
-      <c r="X31" s="10">
-        <f t="shared" ref="X31:X42" si="46">P31-V31</f>
+      <c r="Y31" s="10">
+        <f>P31-W31</f>
         <v>27370.839999999997</v>
       </c>
-      <c r="Y31" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z31" s="2">
-        <f t="shared" ref="Z31:Z42" si="47">X31-Y31</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA31" s="2">
+        <f t="shared" ref="AA31:AA42" si="41">Y31-Z31</f>
         <v>27370.839999999997</v>
       </c>
-      <c r="AA31" s="2"/>
       <c r="AB31" s="2"/>
-    </row>
-    <row r="32" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC31" s="2"/>
+    </row>
+    <row r="32" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -5884,12 +6268,12 @@
         <v>32902</v>
       </c>
       <c r="E32" s="4">
-        <f t="shared" ref="E32:E41" si="48">ROUNDUP(D32/30,0)*2</f>
+        <f t="shared" ref="E32:E41" si="42">ROUNDUP(D32/30,0)*2</f>
         <v>2194</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>35096</v>
       </c>
       <c r="H32" s="2">
@@ -5901,11 +6285,11 @@
         <v>400</v>
       </c>
       <c r="J32" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K32" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L32" s="2">
@@ -5917,18 +6301,18 @@
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P32" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>44401.56</v>
       </c>
       <c r="Q32" s="2">
         <v>800</v>
       </c>
       <c r="R32" s="2">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S32" s="2">
@@ -5936,33 +6320,34 @@
       </c>
       <c r="T32" s="2"/>
       <c r="U32" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="39"/>
         <v>4211.5199999999995</v>
       </c>
-      <c r="V32" s="4">
-        <f t="shared" si="44"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="4">
+        <f t="shared" si="40"/>
         <v>17030.72</v>
       </c>
-      <c r="W32" s="2">
-        <f t="shared" si="45"/>
+      <c r="X32" s="2">
+        <f>Y32+U32</f>
         <v>31582.359999999997</v>
       </c>
-      <c r="X32" s="10">
-        <f t="shared" si="46"/>
+      <c r="Y32" s="10">
+        <f>P32-W32</f>
         <v>27370.839999999997</v>
       </c>
-      <c r="Y32" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z32" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA32" s="2">
+        <f t="shared" si="41"/>
         <v>27370.839999999997</v>
       </c>
-      <c r="AA32" s="2"/>
       <c r="AB32" s="2"/>
-    </row>
-    <row r="33" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC32" s="2"/>
+    </row>
+    <row r="33" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -5970,12 +6355,12 @@
         <v>32902</v>
       </c>
       <c r="E33" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="42"/>
         <v>2194</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>35096</v>
       </c>
       <c r="H33" s="2">
@@ -5987,11 +6372,11 @@
         <v>400</v>
       </c>
       <c r="J33" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K33" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L33" s="2">
@@ -6003,18 +6388,18 @@
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>36192.199999999997</v>
       </c>
       <c r="P33" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>77303.56</v>
       </c>
       <c r="Q33" s="2">
         <v>800</v>
       </c>
       <c r="R33" s="2">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S33" s="2">
@@ -6022,30 +6407,31 @@
       </c>
       <c r="T33" s="2"/>
       <c r="U33" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="39"/>
         <v>4211.5199999999995</v>
       </c>
-      <c r="V33" s="4">
-        <f t="shared" si="44"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="4">
+        <f t="shared" si="40"/>
         <v>17030.72</v>
       </c>
-      <c r="W33" s="2">
-        <f t="shared" si="45"/>
+      <c r="X33" s="2">
+        <f>Y33+U33</f>
         <v>64484.359999999993</v>
       </c>
-      <c r="X33" s="10">
-        <f t="shared" si="46"/>
+      <c r="Y33" s="10">
+        <f>P33-W33</f>
         <v>60272.84</v>
       </c>
-      <c r="Y33" s="2"/>
-      <c r="Z33" s="2">
-        <f t="shared" si="47"/>
+      <c r="Z33" s="2"/>
+      <c r="AA33" s="2">
+        <f t="shared" si="41"/>
         <v>60272.84</v>
       </c>
-      <c r="AA33" s="2"/>
       <c r="AB33" s="2"/>
-    </row>
-    <row r="34" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC33" s="2"/>
+    </row>
+    <row r="34" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -6053,12 +6439,12 @@
         <v>32902</v>
       </c>
       <c r="E34" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="42"/>
         <v>2194</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>35096</v>
       </c>
       <c r="H34" s="2">
@@ -6070,34 +6456,34 @@
         <v>400</v>
       </c>
       <c r="J34" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K34" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L34" s="2">
         <v>0</v>
       </c>
       <c r="M34" s="2">
-        <f>10%*D34</f>
+        <f t="shared" ref="M34:M42" si="43">10%*D34</f>
         <v>3290.2000000000003</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P34" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>44401.56</v>
       </c>
       <c r="Q34" s="2">
         <v>800</v>
       </c>
       <c r="R34" s="2">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S34" s="2">
@@ -6105,33 +6491,34 @@
       </c>
       <c r="T34" s="2"/>
       <c r="U34" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="39"/>
         <v>4211.5199999999995</v>
       </c>
-      <c r="V34" s="4">
-        <f t="shared" si="44"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="4">
+        <f t="shared" si="40"/>
         <v>17030.72</v>
       </c>
-      <c r="W34" s="2">
-        <f t="shared" si="45"/>
+      <c r="X34" s="2">
+        <f>Y34+U34</f>
         <v>31582.359999999997</v>
       </c>
-      <c r="X34" s="10">
-        <f t="shared" si="46"/>
+      <c r="Y34" s="10">
+        <f>P34-W34</f>
         <v>27370.839999999997</v>
       </c>
-      <c r="Y34" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z34" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA34" s="2">
+        <f t="shared" si="41"/>
         <v>27370.839999999997</v>
       </c>
-      <c r="AA34" s="2"/>
       <c r="AB34" s="2"/>
-    </row>
-    <row r="35" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC34" s="2"/>
+    </row>
+    <row r="35" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -6139,12 +6526,12 @@
         <v>32902</v>
       </c>
       <c r="E35" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="42"/>
         <v>2194</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>35096</v>
       </c>
       <c r="H35" s="2">
@@ -6156,34 +6543,34 @@
         <v>400</v>
       </c>
       <c r="J35" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K35" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L35" s="2">
         <v>0</v>
       </c>
       <c r="M35" s="2">
-        <f>10%*D35</f>
+        <f t="shared" si="43"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P35" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>44401.56</v>
       </c>
       <c r="Q35" s="2">
         <v>800</v>
       </c>
       <c r="R35" s="2">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S35" s="2">
@@ -6191,33 +6578,34 @@
       </c>
       <c r="T35" s="2"/>
       <c r="U35" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="39"/>
         <v>4211.5199999999995</v>
       </c>
-      <c r="V35" s="4">
-        <f t="shared" si="44"/>
+      <c r="V35" s="2"/>
+      <c r="W35" s="4">
+        <f t="shared" si="40"/>
         <v>17030.72</v>
       </c>
-      <c r="W35" s="2">
-        <f t="shared" si="45"/>
+      <c r="X35" s="2">
+        <f>Y35+U35</f>
         <v>31582.359999999997</v>
       </c>
-      <c r="X35" s="10">
-        <f t="shared" si="46"/>
+      <c r="Y35" s="10">
+        <f>P35-W35</f>
         <v>27370.839999999997</v>
       </c>
-      <c r="Y35" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z35" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA35" s="2">
+        <f t="shared" si="41"/>
         <v>27370.839999999997</v>
       </c>
-      <c r="AA35" s="2"/>
       <c r="AB35" s="2"/>
-    </row>
-    <row r="36" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC35" s="2"/>
+    </row>
+    <row r="36" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -6225,12 +6613,12 @@
         <v>32902</v>
       </c>
       <c r="E36" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="42"/>
         <v>2194</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>35096</v>
       </c>
       <c r="H36" s="2">
@@ -6242,34 +6630,34 @@
         <v>400</v>
       </c>
       <c r="J36" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K36" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L36" s="2">
         <v>0</v>
       </c>
       <c r="M36" s="2">
-        <f>10%*D36</f>
+        <f t="shared" si="43"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P36" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>44401.56</v>
       </c>
       <c r="Q36" s="2">
         <v>800</v>
       </c>
       <c r="R36" s="2">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S36" s="2">
@@ -6277,33 +6665,34 @@
       </c>
       <c r="T36" s="2"/>
       <c r="U36" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="39"/>
         <v>4211.5199999999995</v>
       </c>
-      <c r="V36" s="4">
-        <f t="shared" si="44"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="4">
+        <f t="shared" si="40"/>
         <v>17030.72</v>
       </c>
-      <c r="W36" s="2">
-        <f t="shared" si="45"/>
+      <c r="X36" s="2">
+        <f>Y36+U36</f>
         <v>31582.359999999997</v>
       </c>
-      <c r="X36" s="10">
-        <f t="shared" si="46"/>
+      <c r="Y36" s="10">
+        <f>P36-W36</f>
         <v>27370.839999999997</v>
       </c>
-      <c r="Y36" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z36" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA36" s="2">
+        <f t="shared" si="41"/>
         <v>27370.839999999997</v>
       </c>
-      <c r="AA36" s="2"/>
       <c r="AB36" s="2"/>
-    </row>
-    <row r="37" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC36" s="2"/>
+    </row>
+    <row r="37" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -6311,12 +6700,12 @@
         <v>32902</v>
       </c>
       <c r="E37" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="42"/>
         <v>2194</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>35096</v>
       </c>
       <c r="H37" s="2">
@@ -6328,34 +6717,34 @@
         <v>400</v>
       </c>
       <c r="J37" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K37" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L37" s="2">
         <v>0</v>
       </c>
       <c r="M37" s="2">
-        <f>10%*D37</f>
+        <f t="shared" si="43"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P37" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>44401.56</v>
       </c>
       <c r="Q37" s="2">
         <v>800</v>
       </c>
       <c r="R37" s="2">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S37" s="2">
@@ -6363,33 +6752,34 @@
       </c>
       <c r="T37" s="2"/>
       <c r="U37" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="39"/>
         <v>4211.5199999999995</v>
       </c>
-      <c r="V37" s="4">
-        <f t="shared" si="44"/>
+      <c r="V37" s="2"/>
+      <c r="W37" s="4">
+        <f t="shared" si="40"/>
         <v>17030.72</v>
       </c>
-      <c r="W37" s="2">
-        <f t="shared" si="45"/>
+      <c r="X37" s="2">
+        <f>Y37+U37</f>
         <v>31582.359999999997</v>
       </c>
-      <c r="X37" s="10">
-        <f t="shared" si="46"/>
+      <c r="Y37" s="10">
+        <f>P37-W37</f>
         <v>27370.839999999997</v>
       </c>
-      <c r="Y37" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z37" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA37" s="2">
+        <f t="shared" si="41"/>
         <v>27370.839999999997</v>
       </c>
-      <c r="AA37" s="2"/>
       <c r="AB37" s="2"/>
-    </row>
-    <row r="38" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC37" s="2"/>
+    </row>
+    <row r="38" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -6397,12 +6787,12 @@
         <v>32902</v>
       </c>
       <c r="E38" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="42"/>
         <v>2194</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>35096</v>
       </c>
       <c r="H38" s="2">
@@ -6414,34 +6804,34 @@
         <v>400</v>
       </c>
       <c r="J38" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K38" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L38" s="2">
         <v>0</v>
       </c>
       <c r="M38" s="2">
-        <f>10%*D38</f>
+        <f t="shared" si="43"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P38" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>44401.56</v>
       </c>
       <c r="Q38" s="2">
         <v>800</v>
       </c>
       <c r="R38" s="2">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S38" s="2">
@@ -6449,33 +6839,34 @@
       </c>
       <c r="T38" s="2"/>
       <c r="U38" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="39"/>
         <v>4211.5199999999995</v>
       </c>
-      <c r="V38" s="4">
-        <f t="shared" si="44"/>
+      <c r="V38" s="2"/>
+      <c r="W38" s="4">
+        <f t="shared" si="40"/>
         <v>17030.72</v>
       </c>
-      <c r="W38" s="2">
-        <f t="shared" si="45"/>
+      <c r="X38" s="2">
+        <f>Y38+U38</f>
         <v>31582.359999999997</v>
       </c>
-      <c r="X38" s="10">
-        <f t="shared" si="46"/>
+      <c r="Y38" s="10">
+        <f>P38-W38</f>
         <v>27370.839999999997</v>
       </c>
-      <c r="Y38" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z38" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA38" s="2">
+        <f t="shared" si="41"/>
         <v>27370.839999999997</v>
       </c>
-      <c r="AA38" s="2"/>
       <c r="AB38" s="2"/>
-    </row>
-    <row r="39" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC38" s="2"/>
+    </row>
+    <row r="39" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -6483,12 +6874,12 @@
         <v>32902</v>
       </c>
       <c r="E39" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="42"/>
         <v>2194</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>35096</v>
       </c>
       <c r="H39" s="2">
@@ -6500,36 +6891,36 @@
         <v>400</v>
       </c>
       <c r="J39" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K39" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L39" s="2">
         <v>0</v>
       </c>
       <c r="M39" s="2">
-        <f>10%*D39</f>
+        <f t="shared" si="43"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N39" s="2">
         <v>10000</v>
       </c>
       <c r="O39" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>13290.2</v>
       </c>
       <c r="P39" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>54401.56</v>
       </c>
       <c r="Q39" s="2">
         <v>800</v>
       </c>
       <c r="R39" s="2">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S39" s="2">
@@ -6537,33 +6928,34 @@
       </c>
       <c r="T39" s="2"/>
       <c r="U39" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="39"/>
         <v>4211.5199999999995</v>
       </c>
-      <c r="V39" s="4">
-        <f t="shared" si="44"/>
+      <c r="V39" s="2"/>
+      <c r="W39" s="4">
+        <f t="shared" si="40"/>
         <v>17030.72</v>
       </c>
-      <c r="W39" s="2">
-        <f t="shared" si="45"/>
+      <c r="X39" s="2">
+        <f>Y39+U39</f>
         <v>41582.359999999993</v>
       </c>
-      <c r="X39" s="10">
-        <f t="shared" si="46"/>
+      <c r="Y39" s="10">
+        <f>P39-W39</f>
         <v>37370.839999999997</v>
       </c>
-      <c r="Y39" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z39" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA39" s="2">
+        <f t="shared" si="41"/>
         <v>37370.839999999997</v>
       </c>
-      <c r="AA39" s="2"/>
       <c r="AB39" s="2"/>
-    </row>
-    <row r="40" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC39" s="2"/>
+    </row>
+    <row r="40" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -6571,12 +6963,12 @@
         <v>32902</v>
       </c>
       <c r="E40" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="42"/>
         <v>2194</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>35096</v>
       </c>
       <c r="H40" s="2">
@@ -6588,34 +6980,34 @@
         <v>400</v>
       </c>
       <c r="J40" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K40" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L40" s="2">
         <v>0</v>
       </c>
       <c r="M40" s="2">
-        <f>10%*D40</f>
+        <f t="shared" si="43"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P40" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>44401.56</v>
       </c>
       <c r="Q40" s="2">
         <v>800</v>
       </c>
       <c r="R40" s="2">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S40" s="2">
@@ -6623,33 +7015,34 @@
       </c>
       <c r="T40" s="2"/>
       <c r="U40" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="39"/>
         <v>4211.5199999999995</v>
       </c>
-      <c r="V40" s="4">
-        <f t="shared" si="44"/>
+      <c r="V40" s="2"/>
+      <c r="W40" s="4">
+        <f t="shared" si="40"/>
         <v>17030.72</v>
       </c>
-      <c r="W40" s="2">
-        <f t="shared" si="45"/>
+      <c r="X40" s="2">
+        <f>Y40+U40</f>
         <v>31582.359999999997</v>
       </c>
-      <c r="X40" s="10">
-        <f t="shared" si="46"/>
+      <c r="Y40" s="10">
+        <f>P40-W40</f>
         <v>27370.839999999997</v>
       </c>
-      <c r="Y40" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z40" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA40" s="2">
+        <f t="shared" si="41"/>
         <v>27370.839999999997</v>
       </c>
-      <c r="AA40" s="2"/>
       <c r="AB40" s="2"/>
-    </row>
-    <row r="41" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC40" s="2"/>
+    </row>
+    <row r="41" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -6657,12 +7050,12 @@
         <v>32902</v>
       </c>
       <c r="E41" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="42"/>
         <v>2194</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>35096</v>
       </c>
       <c r="H41" s="2">
@@ -6674,34 +7067,34 @@
         <v>400</v>
       </c>
       <c r="J41" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K41" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L41" s="2">
         <v>0</v>
       </c>
       <c r="M41" s="2">
-        <f>10%*D41</f>
+        <f t="shared" si="43"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P41" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>44401.56</v>
       </c>
       <c r="Q41" s="2">
         <v>800</v>
       </c>
       <c r="R41" s="2">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S41" s="2">
@@ -6709,33 +7102,34 @@
       </c>
       <c r="T41" s="2"/>
       <c r="U41" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="39"/>
         <v>4211.5199999999995</v>
       </c>
-      <c r="V41" s="4">
-        <f t="shared" si="44"/>
+      <c r="V41" s="2"/>
+      <c r="W41" s="4">
+        <f t="shared" si="40"/>
         <v>17030.72</v>
       </c>
-      <c r="W41" s="2">
-        <f t="shared" si="45"/>
+      <c r="X41" s="2">
+        <f>Y41+U41</f>
         <v>31582.359999999997</v>
       </c>
-      <c r="X41" s="10">
-        <f t="shared" si="46"/>
+      <c r="Y41" s="10">
+        <f>P41-W41</f>
         <v>27370.839999999997</v>
       </c>
-      <c r="Y41" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z41" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA41" s="2">
+        <f t="shared" si="41"/>
         <v>27370.839999999997</v>
       </c>
-      <c r="AA41" s="2"/>
       <c r="AB41" s="2"/>
-    </row>
-    <row r="42" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC41" s="2"/>
+    </row>
+    <row r="42" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -6748,7 +7142,7 @@
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>36193</v>
       </c>
       <c r="H42" s="2">
@@ -6760,34 +7154,34 @@
         <v>400</v>
       </c>
       <c r="J42" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>2171.58</v>
       </c>
       <c r="K42" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="35"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L42" s="2">
         <v>0</v>
       </c>
       <c r="M42" s="2">
-        <f>10%*D42</f>
+        <f t="shared" si="43"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P42" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>45674.080000000002</v>
       </c>
       <c r="Q42" s="2">
         <v>800</v>
       </c>
       <c r="R42" s="2">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>7238.6</v>
       </c>
       <c r="S42" s="2">
@@ -6795,33 +7189,34 @@
       </c>
       <c r="T42" s="2"/>
       <c r="U42" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="39"/>
         <v>4343.16</v>
       </c>
-      <c r="V42" s="4">
-        <f t="shared" si="44"/>
+      <c r="V42" s="2"/>
+      <c r="W42" s="4">
+        <f t="shared" si="40"/>
         <v>17381.760000000002</v>
       </c>
-      <c r="W42" s="2">
-        <f t="shared" si="45"/>
+      <c r="X42" s="2">
+        <f>Y42+U42</f>
         <v>32635.48</v>
       </c>
-      <c r="X42" s="10">
-        <f t="shared" si="46"/>
+      <c r="Y42" s="10">
+        <f>P42-W42</f>
         <v>28292.32</v>
       </c>
-      <c r="Y42" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z42" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA42" s="2">
+        <f t="shared" si="41"/>
         <v>28292.32</v>
       </c>
-      <c r="AA42" s="2"/>
       <c r="AB42" s="2"/>
-    </row>
-    <row r="43" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC42" s="2"/>
+    </row>
+    <row r="43" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -6843,15 +7238,16 @@
       <c r="S43" s="2"/>
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
-      <c r="V43" s="4"/>
-      <c r="W43" s="2"/>
-      <c r="X43" s="10"/>
-      <c r="Y43" s="2"/>
+      <c r="V43" s="2"/>
+      <c r="W43" s="4"/>
+      <c r="X43" s="2"/>
+      <c r="Y43" s="10"/>
       <c r="Z43" s="2"/>
       <c r="AA43" s="2"/>
       <c r="AB43" s="2"/>
-    </row>
-    <row r="44" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC43" s="2"/>
+    </row>
+    <row r="44" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -6864,7 +7260,7 @@
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="8">
-        <f t="shared" ref="G44:G55" si="49">SUM(D44:F44)</f>
+        <f t="shared" ref="G44:G55" si="44">SUM(D44:F44)</f>
         <v>36193</v>
       </c>
       <c r="H44" s="2">
@@ -6876,11 +7272,11 @@
         <v>400</v>
       </c>
       <c r="J44" s="2">
-        <f t="shared" ref="J44:J55" si="50">6%*G44</f>
+        <f t="shared" ref="J44:J55" si="45">6%*G44</f>
         <v>2171.58</v>
       </c>
       <c r="K44" s="8">
-        <f t="shared" ref="K44:K55" si="51">SUM(G44:J44)</f>
+        <f t="shared" ref="K44:K55" si="46">SUM(G44:J44)</f>
         <v>42383.880000000005</v>
       </c>
       <c r="L44" s="2">
@@ -6892,18 +7288,18 @@
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="4">
-        <f t="shared" ref="O44:O55" si="52">SUM(L44:N44)</f>
+        <f t="shared" ref="O44:O55" si="47">SUM(L44:N44)</f>
         <v>3290.2000000000003</v>
       </c>
       <c r="P44" s="8">
-        <f t="shared" ref="P44:P55" si="53">K44+O44</f>
+        <f t="shared" ref="P44:P55" si="48">K44+O44</f>
         <v>45674.080000000002</v>
       </c>
       <c r="Q44" s="2">
         <v>800</v>
       </c>
       <c r="R44" s="2">
-        <f t="shared" ref="R44:R55" si="54">H44*2</f>
+        <f t="shared" ref="R44:R55" si="49">H44*2</f>
         <v>7238.6</v>
       </c>
       <c r="S44" s="2">
@@ -6911,33 +7307,34 @@
       </c>
       <c r="T44" s="2"/>
       <c r="U44" s="2">
-        <f t="shared" ref="U44:U55" si="55">J44*2</f>
+        <f t="shared" ref="U44:U55" si="50">J44*2</f>
         <v>4343.16</v>
       </c>
-      <c r="V44" s="4">
-        <f t="shared" ref="V44:V55" si="56">SUM(Q44:U44)</f>
+      <c r="V44" s="2"/>
+      <c r="W44" s="4">
+        <f t="shared" ref="W44:W55" si="51">SUM(Q44:U44)</f>
         <v>17381.760000000002</v>
       </c>
-      <c r="W44" s="2">
-        <f t="shared" ref="W44:W55" si="57">X44+U44</f>
+      <c r="X44" s="2">
+        <f>Y44+U44</f>
         <v>32635.48</v>
       </c>
-      <c r="X44" s="10">
-        <f t="shared" ref="X44:X55" si="58">P44-V44</f>
+      <c r="Y44" s="10">
+        <f>P44-W44</f>
         <v>28292.32</v>
       </c>
-      <c r="Y44" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z44" s="2">
-        <f t="shared" ref="Z44:Z55" si="59">X44-Y44</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA44" s="2">
+        <f t="shared" ref="AA44:AA55" si="52">Y44-Z44</f>
         <v>28292.32</v>
       </c>
-      <c r="AA44" s="2"/>
       <c r="AB44" s="2"/>
-    </row>
-    <row r="45" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC44" s="2"/>
+    </row>
+    <row r="45" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -6945,12 +7342,12 @@
         <v>32902</v>
       </c>
       <c r="E45" s="4">
-        <f t="shared" ref="E45:E54" si="60">ROUNDUP(D45/30,0)*3</f>
+        <f t="shared" ref="E45:E54" si="53">ROUNDUP(D45/30,0)*3</f>
         <v>3291</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="44"/>
         <v>36193</v>
       </c>
       <c r="H45" s="2">
@@ -6962,11 +7359,11 @@
         <v>400</v>
       </c>
       <c r="J45" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="45"/>
         <v>2171.58</v>
       </c>
       <c r="K45" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L45" s="2">
@@ -6978,18 +7375,18 @@
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P45" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>45674.080000000002</v>
       </c>
       <c r="Q45" s="2">
         <v>800</v>
       </c>
       <c r="R45" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>7238.6</v>
       </c>
       <c r="S45" s="2">
@@ -6997,33 +7394,34 @@
       </c>
       <c r="T45" s="2"/>
       <c r="U45" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="50"/>
         <v>4343.16</v>
       </c>
-      <c r="V45" s="4">
-        <f t="shared" si="56"/>
+      <c r="V45" s="2"/>
+      <c r="W45" s="4">
+        <f t="shared" si="51"/>
         <v>17381.760000000002</v>
       </c>
-      <c r="W45" s="2">
-        <f t="shared" si="57"/>
+      <c r="X45" s="2">
+        <f>Y45+U45</f>
         <v>32635.48</v>
       </c>
-      <c r="X45" s="10">
-        <f t="shared" si="58"/>
+      <c r="Y45" s="10">
+        <f>P45-W45</f>
         <v>28292.32</v>
       </c>
-      <c r="Y45" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z45" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA45" s="2">
+        <f t="shared" si="52"/>
         <v>28292.32</v>
       </c>
-      <c r="AA45" s="2"/>
       <c r="AB45" s="2"/>
-    </row>
-    <row r="46" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC45" s="2"/>
+    </row>
+    <row r="46" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -7031,12 +7429,12 @@
         <v>32902</v>
       </c>
       <c r="E46" s="4">
-        <f t="shared" si="60"/>
+        <f t="shared" si="53"/>
         <v>3291</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="44"/>
         <v>36193</v>
       </c>
       <c r="H46" s="2">
@@ -7048,11 +7446,11 @@
         <v>400</v>
       </c>
       <c r="J46" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="45"/>
         <v>2171.58</v>
       </c>
       <c r="K46" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L46" s="2">
@@ -7064,18 +7462,18 @@
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>36192.199999999997</v>
       </c>
       <c r="P46" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>78576.08</v>
       </c>
       <c r="Q46" s="2">
         <v>800</v>
       </c>
       <c r="R46" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>7238.6</v>
       </c>
       <c r="S46" s="2">
@@ -7083,30 +7481,31 @@
       </c>
       <c r="T46" s="2"/>
       <c r="U46" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="50"/>
         <v>4343.16</v>
       </c>
-      <c r="V46" s="4">
-        <f t="shared" si="56"/>
+      <c r="V46" s="2"/>
+      <c r="W46" s="4">
+        <f t="shared" si="51"/>
         <v>17381.760000000002</v>
       </c>
-      <c r="W46" s="2">
-        <f t="shared" si="57"/>
+      <c r="X46" s="2">
+        <f>Y46+U46</f>
         <v>65537.48</v>
       </c>
-      <c r="X46" s="10">
-        <f t="shared" si="58"/>
+      <c r="Y46" s="10">
+        <f>P46-W46</f>
         <v>61194.32</v>
       </c>
-      <c r="Y46" s="2"/>
-      <c r="Z46" s="2">
-        <f t="shared" si="59"/>
+      <c r="Z46" s="2"/>
+      <c r="AA46" s="2">
+        <f t="shared" si="52"/>
         <v>61194.32</v>
       </c>
-      <c r="AA46" s="2"/>
       <c r="AB46" s="2"/>
-    </row>
-    <row r="47" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC46" s="2"/>
+    </row>
+    <row r="47" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -7114,12 +7513,12 @@
         <v>32902</v>
       </c>
       <c r="E47" s="4">
-        <f t="shared" si="60"/>
+        <f t="shared" si="53"/>
         <v>3291</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="44"/>
         <v>36193</v>
       </c>
       <c r="H47" s="2">
@@ -7131,34 +7530,34 @@
         <v>400</v>
       </c>
       <c r="J47" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="45"/>
         <v>2171.58</v>
       </c>
       <c r="K47" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L47" s="2">
         <v>0</v>
       </c>
       <c r="M47" s="2">
-        <f>10%*D47</f>
+        <f t="shared" ref="M47:M55" si="54">10%*D47</f>
         <v>3290.2000000000003</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P47" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>45674.080000000002</v>
       </c>
       <c r="Q47" s="2">
         <v>800</v>
       </c>
       <c r="R47" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>7238.6</v>
       </c>
       <c r="S47" s="2">
@@ -7166,33 +7565,34 @@
       </c>
       <c r="T47" s="2"/>
       <c r="U47" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="50"/>
         <v>4343.16</v>
       </c>
-      <c r="V47" s="4">
-        <f t="shared" si="56"/>
+      <c r="V47" s="2"/>
+      <c r="W47" s="4">
+        <f t="shared" si="51"/>
         <v>17381.760000000002</v>
       </c>
-      <c r="W47" s="2">
-        <f t="shared" si="57"/>
+      <c r="X47" s="2">
+        <f>Y47+U47</f>
         <v>32635.48</v>
       </c>
-      <c r="X47" s="10">
-        <f t="shared" si="58"/>
+      <c r="Y47" s="10">
+        <f>P47-W47</f>
         <v>28292.32</v>
       </c>
-      <c r="Y47" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z47" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA47" s="2">
+        <f t="shared" si="52"/>
         <v>28292.32</v>
       </c>
-      <c r="AA47" s="2"/>
       <c r="AB47" s="2"/>
-    </row>
-    <row r="48" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC47" s="2"/>
+    </row>
+    <row r="48" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -7200,12 +7600,12 @@
         <v>32902</v>
       </c>
       <c r="E48" s="4">
-        <f t="shared" si="60"/>
+        <f t="shared" si="53"/>
         <v>3291</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="44"/>
         <v>36193</v>
       </c>
       <c r="H48" s="2">
@@ -7217,34 +7617,34 @@
         <v>400</v>
       </c>
       <c r="J48" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="45"/>
         <v>2171.58</v>
       </c>
       <c r="K48" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L48" s="2">
         <v>0</v>
       </c>
       <c r="M48" s="2">
-        <f>10%*D48</f>
+        <f t="shared" si="54"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P48" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>45674.080000000002</v>
       </c>
       <c r="Q48" s="2">
         <v>800</v>
       </c>
       <c r="R48" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>7238.6</v>
       </c>
       <c r="S48" s="2">
@@ -7252,33 +7652,34 @@
       </c>
       <c r="T48" s="2"/>
       <c r="U48" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="50"/>
         <v>4343.16</v>
       </c>
-      <c r="V48" s="4">
-        <f t="shared" si="56"/>
+      <c r="V48" s="2"/>
+      <c r="W48" s="4">
+        <f t="shared" si="51"/>
         <v>17381.760000000002</v>
       </c>
-      <c r="W48" s="2">
-        <f t="shared" si="57"/>
+      <c r="X48" s="2">
+        <f>Y48+U48</f>
         <v>32635.48</v>
       </c>
-      <c r="X48" s="10">
-        <f t="shared" si="58"/>
+      <c r="Y48" s="10">
+        <f>P48-W48</f>
         <v>28292.32</v>
       </c>
-      <c r="Y48" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z48" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA48" s="2">
+        <f t="shared" si="52"/>
         <v>28292.32</v>
       </c>
-      <c r="AA48" s="2"/>
       <c r="AB48" s="2"/>
-    </row>
-    <row r="49" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC48" s="2"/>
+    </row>
+    <row r="49" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -7286,12 +7687,12 @@
         <v>32902</v>
       </c>
       <c r="E49" s="4">
-        <f t="shared" si="60"/>
+        <f t="shared" si="53"/>
         <v>3291</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="44"/>
         <v>36193</v>
       </c>
       <c r="H49" s="2">
@@ -7303,34 +7704,34 @@
         <v>400</v>
       </c>
       <c r="J49" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="45"/>
         <v>2171.58</v>
       </c>
       <c r="K49" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L49" s="2">
         <v>0</v>
       </c>
       <c r="M49" s="2">
-        <f>10%*D49</f>
+        <f t="shared" si="54"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P49" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>45674.080000000002</v>
       </c>
       <c r="Q49" s="2">
         <v>800</v>
       </c>
       <c r="R49" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>7238.6</v>
       </c>
       <c r="S49" s="2">
@@ -7338,33 +7739,34 @@
       </c>
       <c r="T49" s="2"/>
       <c r="U49" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="50"/>
         <v>4343.16</v>
       </c>
-      <c r="V49" s="4">
-        <f t="shared" si="56"/>
+      <c r="V49" s="2"/>
+      <c r="W49" s="4">
+        <f t="shared" si="51"/>
         <v>17381.760000000002</v>
       </c>
-      <c r="W49" s="2">
-        <f t="shared" si="57"/>
+      <c r="X49" s="2">
+        <f>Y49+U49</f>
         <v>32635.48</v>
       </c>
-      <c r="X49" s="10">
-        <f t="shared" si="58"/>
+      <c r="Y49" s="10">
+        <f>P49-W49</f>
         <v>28292.32</v>
       </c>
-      <c r="Y49" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z49" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA49" s="2">
+        <f t="shared" si="52"/>
         <v>28292.32</v>
       </c>
-      <c r="AA49" s="2"/>
       <c r="AB49" s="2"/>
-    </row>
-    <row r="50" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC49" s="2"/>
+    </row>
+    <row r="50" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -7372,12 +7774,12 @@
         <v>32902</v>
       </c>
       <c r="E50" s="4">
-        <f t="shared" si="60"/>
+        <f t="shared" si="53"/>
         <v>3291</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="44"/>
         <v>36193</v>
       </c>
       <c r="H50" s="2">
@@ -7389,34 +7791,34 @@
         <v>400</v>
       </c>
       <c r="J50" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="45"/>
         <v>2171.58</v>
       </c>
       <c r="K50" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L50" s="2">
         <v>0</v>
       </c>
       <c r="M50" s="2">
-        <f>10%*D50</f>
+        <f t="shared" si="54"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P50" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>45674.080000000002</v>
       </c>
       <c r="Q50" s="2">
         <v>800</v>
       </c>
       <c r="R50" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>7238.6</v>
       </c>
       <c r="S50" s="2">
@@ -7424,33 +7826,34 @@
       </c>
       <c r="T50" s="2"/>
       <c r="U50" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="50"/>
         <v>4343.16</v>
       </c>
-      <c r="V50" s="4">
-        <f t="shared" si="56"/>
+      <c r="V50" s="2"/>
+      <c r="W50" s="4">
+        <f t="shared" si="51"/>
         <v>17381.760000000002</v>
       </c>
-      <c r="W50" s="2">
-        <f t="shared" si="57"/>
+      <c r="X50" s="2">
+        <f>Y50+U50</f>
         <v>32635.48</v>
       </c>
-      <c r="X50" s="10">
-        <f t="shared" si="58"/>
+      <c r="Y50" s="10">
+        <f>P50-W50</f>
         <v>28292.32</v>
       </c>
-      <c r="Y50" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z50" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA50" s="2">
+        <f t="shared" si="52"/>
         <v>28292.32</v>
       </c>
-      <c r="AA50" s="2"/>
       <c r="AB50" s="2"/>
-    </row>
-    <row r="51" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC50" s="2"/>
+    </row>
+    <row r="51" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -7458,12 +7861,12 @@
         <v>32902</v>
       </c>
       <c r="E51" s="4">
-        <f t="shared" si="60"/>
+        <f t="shared" si="53"/>
         <v>3291</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="44"/>
         <v>36193</v>
       </c>
       <c r="H51" s="2">
@@ -7475,34 +7878,34 @@
         <v>400</v>
       </c>
       <c r="J51" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="45"/>
         <v>2171.58</v>
       </c>
       <c r="K51" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L51" s="2">
         <v>0</v>
       </c>
       <c r="M51" s="2">
-        <f>10%*D51</f>
+        <f t="shared" si="54"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P51" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>45674.080000000002</v>
       </c>
       <c r="Q51" s="2">
         <v>800</v>
       </c>
       <c r="R51" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>7238.6</v>
       </c>
       <c r="S51" s="2">
@@ -7510,33 +7913,34 @@
       </c>
       <c r="T51" s="2"/>
       <c r="U51" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="50"/>
         <v>4343.16</v>
       </c>
-      <c r="V51" s="4">
-        <f t="shared" si="56"/>
+      <c r="V51" s="2"/>
+      <c r="W51" s="4">
+        <f t="shared" si="51"/>
         <v>17381.760000000002</v>
       </c>
-      <c r="W51" s="2">
-        <f t="shared" si="57"/>
+      <c r="X51" s="2">
+        <f>Y51+U51</f>
         <v>32635.48</v>
       </c>
-      <c r="X51" s="10">
-        <f t="shared" si="58"/>
+      <c r="Y51" s="10">
+        <f>P51-W51</f>
         <v>28292.32</v>
       </c>
-      <c r="Y51" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z51" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA51" s="2">
+        <f t="shared" si="52"/>
         <v>28292.32</v>
       </c>
-      <c r="AA51" s="2"/>
       <c r="AB51" s="2"/>
-    </row>
-    <row r="52" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC51" s="2"/>
+    </row>
+    <row r="52" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -7544,12 +7948,12 @@
         <v>32902</v>
       </c>
       <c r="E52" s="4">
-        <f t="shared" si="60"/>
+        <f t="shared" si="53"/>
         <v>3291</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="44"/>
         <v>36193</v>
       </c>
       <c r="H52" s="2">
@@ -7561,36 +7965,36 @@
         <v>400</v>
       </c>
       <c r="J52" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="45"/>
         <v>2171.58</v>
       </c>
       <c r="K52" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L52" s="2">
         <v>0</v>
       </c>
       <c r="M52" s="2">
-        <f>10%*D52</f>
+        <f t="shared" si="54"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N52" s="2">
         <v>10000</v>
       </c>
       <c r="O52" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>13290.2</v>
       </c>
       <c r="P52" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>55674.080000000002</v>
       </c>
       <c r="Q52" s="2">
         <v>800</v>
       </c>
       <c r="R52" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>7238.6</v>
       </c>
       <c r="S52" s="2">
@@ -7598,33 +8002,34 @@
       </c>
       <c r="T52" s="2"/>
       <c r="U52" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="50"/>
         <v>4343.16</v>
       </c>
-      <c r="V52" s="4">
-        <f t="shared" si="56"/>
+      <c r="V52" s="2"/>
+      <c r="W52" s="4">
+        <f t="shared" si="51"/>
         <v>17381.760000000002</v>
       </c>
-      <c r="W52" s="2">
-        <f t="shared" si="57"/>
+      <c r="X52" s="2">
+        <f>Y52+U52</f>
         <v>42635.479999999996</v>
       </c>
-      <c r="X52" s="10">
-        <f t="shared" si="58"/>
+      <c r="Y52" s="10">
+        <f>P52-W52</f>
         <v>38292.32</v>
       </c>
-      <c r="Y52" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z52" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA52" s="2">
+        <f t="shared" si="52"/>
         <v>38292.32</v>
       </c>
-      <c r="AA52" s="2"/>
       <c r="AB52" s="2"/>
-    </row>
-    <row r="53" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC52" s="2"/>
+    </row>
+    <row r="53" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -7632,12 +8037,12 @@
         <v>32902</v>
       </c>
       <c r="E53" s="4">
-        <f t="shared" si="60"/>
+        <f t="shared" si="53"/>
         <v>3291</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="44"/>
         <v>36193</v>
       </c>
       <c r="H53" s="2">
@@ -7649,34 +8054,34 @@
         <v>400</v>
       </c>
       <c r="J53" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="45"/>
         <v>2171.58</v>
       </c>
       <c r="K53" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L53" s="2">
         <v>0</v>
       </c>
       <c r="M53" s="2">
-        <f>10%*D53</f>
+        <f t="shared" si="54"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P53" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>45674.080000000002</v>
       </c>
       <c r="Q53" s="2">
         <v>800</v>
       </c>
       <c r="R53" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>7238.6</v>
       </c>
       <c r="S53" s="2">
@@ -7684,33 +8089,34 @@
       </c>
       <c r="T53" s="2"/>
       <c r="U53" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="50"/>
         <v>4343.16</v>
       </c>
-      <c r="V53" s="4">
-        <f t="shared" si="56"/>
+      <c r="V53" s="2"/>
+      <c r="W53" s="4">
+        <f t="shared" si="51"/>
         <v>17381.760000000002</v>
       </c>
-      <c r="W53" s="2">
-        <f t="shared" si="57"/>
+      <c r="X53" s="2">
+        <f>Y53+U53</f>
         <v>32635.48</v>
       </c>
-      <c r="X53" s="10">
-        <f t="shared" si="58"/>
+      <c r="Y53" s="10">
+        <f>P53-W53</f>
         <v>28292.32</v>
       </c>
-      <c r="Y53" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z53" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA53" s="2">
+        <f t="shared" si="52"/>
         <v>28292.32</v>
       </c>
-      <c r="AA53" s="2"/>
       <c r="AB53" s="2"/>
-    </row>
-    <row r="54" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC53" s="2"/>
+    </row>
+    <row r="54" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -7718,12 +8124,12 @@
         <v>32902</v>
       </c>
       <c r="E54" s="4">
-        <f t="shared" si="60"/>
+        <f t="shared" si="53"/>
         <v>3291</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="44"/>
         <v>36193</v>
       </c>
       <c r="H54" s="2">
@@ -7735,34 +8141,34 @@
         <v>400</v>
       </c>
       <c r="J54" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="45"/>
         <v>2171.58</v>
       </c>
       <c r="K54" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L54" s="2">
         <v>0</v>
       </c>
       <c r="M54" s="2">
-        <f>10%*D54</f>
+        <f t="shared" si="54"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P54" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>45674.080000000002</v>
       </c>
       <c r="Q54" s="2">
         <v>800</v>
       </c>
       <c r="R54" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>7238.6</v>
       </c>
       <c r="S54" s="2">
@@ -7770,33 +8176,34 @@
       </c>
       <c r="T54" s="2"/>
       <c r="U54" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="50"/>
         <v>4343.16</v>
       </c>
-      <c r="V54" s="4">
-        <f t="shared" si="56"/>
+      <c r="V54" s="2"/>
+      <c r="W54" s="4">
+        <f t="shared" si="51"/>
         <v>17381.760000000002</v>
       </c>
-      <c r="W54" s="2">
-        <f t="shared" si="57"/>
+      <c r="X54" s="2">
+        <f>Y54+U54</f>
         <v>32635.48</v>
       </c>
-      <c r="X54" s="10">
-        <f t="shared" si="58"/>
+      <c r="Y54" s="10">
+        <f>P54-W54</f>
         <v>28292.32</v>
       </c>
-      <c r="Y54" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z54" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA54" s="2">
+        <f t="shared" si="52"/>
         <v>28292.32</v>
       </c>
-      <c r="AA54" s="2"/>
       <c r="AB54" s="2"/>
-    </row>
-    <row r="55" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC54" s="2"/>
+    </row>
+    <row r="55" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -7804,12 +8211,12 @@
         <v>32902</v>
       </c>
       <c r="E55" s="4">
-        <f t="shared" ref="E45:E68" si="61">ROUNDUP(D55/30,0)*4</f>
+        <f t="shared" ref="E55:E67" si="55">ROUNDUP(D55/30,0)*4</f>
         <v>4388</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="44"/>
         <v>37290</v>
       </c>
       <c r="H55" s="2">
@@ -7821,34 +8228,34 @@
         <v>400</v>
       </c>
       <c r="J55" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="45"/>
         <v>2237.4</v>
       </c>
       <c r="K55" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>43656.4</v>
       </c>
       <c r="L55" s="2">
         <v>0</v>
       </c>
       <c r="M55" s="2">
-        <f>10%*D55</f>
+        <f t="shared" si="54"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P55" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>46946.6</v>
       </c>
       <c r="Q55" s="2">
         <v>800</v>
       </c>
       <c r="R55" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>7458</v>
       </c>
       <c r="S55" s="2">
@@ -7856,33 +8263,34 @@
       </c>
       <c r="T55" s="2"/>
       <c r="U55" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="50"/>
         <v>4474.8</v>
       </c>
-      <c r="V55" s="4">
-        <f t="shared" si="56"/>
+      <c r="V55" s="2"/>
+      <c r="W55" s="4">
+        <f t="shared" si="51"/>
         <v>17732.8</v>
       </c>
-      <c r="W55" s="2">
-        <f t="shared" si="57"/>
+      <c r="X55" s="2">
+        <f>Y55+U55</f>
         <v>33688.6</v>
       </c>
-      <c r="X55" s="10">
-        <f t="shared" si="58"/>
+      <c r="Y55" s="10">
+        <f>P55-W55</f>
         <v>29213.8</v>
       </c>
-      <c r="Y55" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z55" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA55" s="2">
+        <f t="shared" si="52"/>
         <v>29213.8</v>
       </c>
-      <c r="AA55" s="2"/>
       <c r="AB55" s="2"/>
-    </row>
-    <row r="56" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC55" s="2"/>
+    </row>
+    <row r="56" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -7904,15 +8312,16 @@
       <c r="S56" s="2"/>
       <c r="T56" s="2"/>
       <c r="U56" s="2"/>
-      <c r="V56" s="4"/>
-      <c r="W56" s="2"/>
-      <c r="X56" s="10"/>
-      <c r="Y56" s="2"/>
+      <c r="V56" s="2"/>
+      <c r="W56" s="4"/>
+      <c r="X56" s="2"/>
+      <c r="Y56" s="10"/>
       <c r="Z56" s="2"/>
       <c r="AA56" s="2"/>
       <c r="AB56" s="2"/>
-    </row>
-    <row r="57" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC56" s="2"/>
+    </row>
+    <row r="57" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -7920,12 +8329,12 @@
         <v>32902</v>
       </c>
       <c r="E57" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="55"/>
         <v>4388</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="8">
-        <f t="shared" ref="G57:G68" si="62">SUM(D57:F57)</f>
+        <f t="shared" ref="G57:G68" si="56">SUM(D57:F57)</f>
         <v>37290</v>
       </c>
       <c r="H57" s="2">
@@ -7937,11 +8346,11 @@
         <v>400</v>
       </c>
       <c r="J57" s="2">
-        <f t="shared" ref="J57:J68" si="63">6%*G57</f>
+        <f t="shared" ref="J57:J68" si="57">6%*G57</f>
         <v>2237.4</v>
       </c>
       <c r="K57" s="8">
-        <f t="shared" ref="K57:K68" si="64">SUM(G57:J57)</f>
+        <f t="shared" ref="K57:K68" si="58">SUM(G57:J57)</f>
         <v>43656.4</v>
       </c>
       <c r="L57" s="2">
@@ -7953,18 +8362,18 @@
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="4">
-        <f t="shared" ref="O57:O68" si="65">SUM(L57:N57)</f>
+        <f t="shared" ref="O57:O68" si="59">SUM(L57:N57)</f>
         <v>3290.2000000000003</v>
       </c>
       <c r="P57" s="8">
-        <f t="shared" ref="P57:P68" si="66">K57+O57</f>
+        <f t="shared" ref="P57:P68" si="60">K57+O57</f>
         <v>46946.6</v>
       </c>
       <c r="Q57" s="2">
         <v>800</v>
       </c>
       <c r="R57" s="2">
-        <f t="shared" ref="R57:R68" si="67">H57*2</f>
+        <f t="shared" ref="R57:R68" si="61">H57*2</f>
         <v>7458</v>
       </c>
       <c r="S57" s="2">
@@ -7972,33 +8381,34 @@
       </c>
       <c r="T57" s="2"/>
       <c r="U57" s="2">
-        <f t="shared" ref="U57:U68" si="68">J57*2</f>
+        <f t="shared" ref="U57:U68" si="62">J57*2</f>
         <v>4474.8</v>
       </c>
-      <c r="V57" s="4">
-        <f t="shared" ref="V57:V68" si="69">SUM(Q57:U57)</f>
+      <c r="V57" s="2"/>
+      <c r="W57" s="4">
+        <f t="shared" ref="W57:W68" si="63">SUM(Q57:U57)</f>
         <v>17732.8</v>
       </c>
-      <c r="W57" s="2">
-        <f t="shared" ref="W57:W68" si="70">X57+U57</f>
+      <c r="X57" s="2">
+        <f>Y57+U57</f>
         <v>33688.6</v>
       </c>
-      <c r="X57" s="10">
-        <f t="shared" ref="X57:X68" si="71">P57-V57</f>
+      <c r="Y57" s="10">
+        <f>P57-W57</f>
         <v>29213.8</v>
       </c>
-      <c r="Y57" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z57" s="2">
-        <f t="shared" ref="Z57:Z68" si="72">X57-Y57</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA57" s="2">
+        <f t="shared" ref="AA57:AA68" si="64">Y57-Z57</f>
         <v>29213.8</v>
       </c>
-      <c r="AA57" s="2"/>
       <c r="AB57" s="2"/>
-    </row>
-    <row r="58" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC57" s="2"/>
+    </row>
+    <row r="58" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -8006,12 +8416,12 @@
         <v>32902</v>
       </c>
       <c r="E58" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="55"/>
         <v>4388</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>37290</v>
       </c>
       <c r="H58" s="2">
@@ -8023,11 +8433,11 @@
         <v>400</v>
       </c>
       <c r="J58" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="57"/>
         <v>2237.4</v>
       </c>
       <c r="K58" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>43656.4</v>
       </c>
       <c r="L58" s="2">
@@ -8039,18 +8449,18 @@
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="59"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P58" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="60"/>
         <v>46946.6</v>
       </c>
       <c r="Q58" s="2">
         <v>800</v>
       </c>
       <c r="R58" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>7458</v>
       </c>
       <c r="S58" s="2">
@@ -8058,33 +8468,34 @@
       </c>
       <c r="T58" s="2"/>
       <c r="U58" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>4474.8</v>
       </c>
-      <c r="V58" s="4">
-        <f t="shared" si="69"/>
+      <c r="V58" s="2"/>
+      <c r="W58" s="4">
+        <f t="shared" si="63"/>
         <v>17732.8</v>
       </c>
-      <c r="W58" s="2">
-        <f t="shared" si="70"/>
+      <c r="X58" s="2">
+        <f>Y58+U58</f>
         <v>33688.6</v>
       </c>
-      <c r="X58" s="10">
-        <f t="shared" si="71"/>
+      <c r="Y58" s="10">
+        <f>P58-W58</f>
         <v>29213.8</v>
       </c>
-      <c r="Y58" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z58" s="2">
-        <f t="shared" si="72"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA58" s="2">
+        <f t="shared" si="64"/>
         <v>29213.8</v>
       </c>
-      <c r="AA58" s="2"/>
       <c r="AB58" s="2"/>
-    </row>
-    <row r="59" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC58" s="2"/>
+    </row>
+    <row r="59" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -8092,12 +8503,12 @@
         <v>32902</v>
       </c>
       <c r="E59" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="55"/>
         <v>4388</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>37290</v>
       </c>
       <c r="H59" s="2">
@@ -8109,11 +8520,11 @@
         <v>400</v>
       </c>
       <c r="J59" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="57"/>
         <v>2237.4</v>
       </c>
       <c r="K59" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>43656.4</v>
       </c>
       <c r="L59" s="2">
@@ -8125,18 +8536,18 @@
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="59"/>
         <v>36192.199999999997</v>
       </c>
       <c r="P59" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="60"/>
         <v>79848.600000000006</v>
       </c>
       <c r="Q59" s="2">
         <v>800</v>
       </c>
       <c r="R59" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>7458</v>
       </c>
       <c r="S59" s="2">
@@ -8144,30 +8555,31 @@
       </c>
       <c r="T59" s="2"/>
       <c r="U59" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>4474.8</v>
       </c>
-      <c r="V59" s="4">
-        <f t="shared" si="69"/>
+      <c r="V59" s="2"/>
+      <c r="W59" s="4">
+        <f t="shared" si="63"/>
         <v>17732.8</v>
       </c>
-      <c r="W59" s="2">
-        <f t="shared" si="70"/>
+      <c r="X59" s="2">
+        <f>Y59+U59</f>
         <v>66590.600000000006</v>
       </c>
-      <c r="X59" s="10">
-        <f t="shared" si="71"/>
+      <c r="Y59" s="10">
+        <f>P59-W59</f>
         <v>62115.8</v>
       </c>
-      <c r="Y59" s="2"/>
-      <c r="Z59" s="2">
-        <f t="shared" si="72"/>
+      <c r="Z59" s="2"/>
+      <c r="AA59" s="2">
+        <f t="shared" si="64"/>
         <v>62115.8</v>
       </c>
-      <c r="AA59" s="2"/>
       <c r="AB59" s="2"/>
-    </row>
-    <row r="60" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC59" s="2"/>
+    </row>
+    <row r="60" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -8175,12 +8587,12 @@
         <v>32902</v>
       </c>
       <c r="E60" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="55"/>
         <v>4388</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>37290</v>
       </c>
       <c r="H60" s="2">
@@ -8192,34 +8604,34 @@
         <v>400</v>
       </c>
       <c r="J60" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="57"/>
         <v>2237.4</v>
       </c>
       <c r="K60" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>43656.4</v>
       </c>
       <c r="L60" s="2">
         <v>0</v>
       </c>
       <c r="M60" s="2">
-        <f>10%*D60</f>
+        <f t="shared" ref="M60:M68" si="65">10%*D60</f>
         <v>3290.2000000000003</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="59"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P60" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="60"/>
         <v>46946.6</v>
       </c>
       <c r="Q60" s="2">
         <v>800</v>
       </c>
       <c r="R60" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>7458</v>
       </c>
       <c r="S60" s="2">
@@ -8227,33 +8639,34 @@
       </c>
       <c r="T60" s="2"/>
       <c r="U60" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>4474.8</v>
       </c>
-      <c r="V60" s="4">
-        <f t="shared" si="69"/>
+      <c r="V60" s="2"/>
+      <c r="W60" s="4">
+        <f t="shared" si="63"/>
         <v>17732.8</v>
       </c>
-      <c r="W60" s="2">
-        <f t="shared" si="70"/>
+      <c r="X60" s="2">
+        <f>Y60+U60</f>
         <v>33688.6</v>
       </c>
-      <c r="X60" s="10">
-        <f t="shared" si="71"/>
+      <c r="Y60" s="10">
+        <f>P60-W60</f>
         <v>29213.8</v>
       </c>
-      <c r="Y60" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z60" s="2">
-        <f t="shared" si="72"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA60" s="2">
+        <f t="shared" si="64"/>
         <v>29213.8</v>
       </c>
-      <c r="AA60" s="2"/>
       <c r="AB60" s="2"/>
-    </row>
-    <row r="61" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC60" s="2"/>
+    </row>
+    <row r="61" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -8261,12 +8674,12 @@
         <v>32902</v>
       </c>
       <c r="E61" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="55"/>
         <v>4388</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>37290</v>
       </c>
       <c r="H61" s="2">
@@ -8278,34 +8691,34 @@
         <v>400</v>
       </c>
       <c r="J61" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="57"/>
         <v>2237.4</v>
       </c>
       <c r="K61" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>43656.4</v>
       </c>
       <c r="L61" s="2">
         <v>0</v>
       </c>
       <c r="M61" s="2">
-        <f>10%*D61</f>
+        <f t="shared" si="65"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="59"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P61" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="60"/>
         <v>46946.6</v>
       </c>
       <c r="Q61" s="2">
         <v>800</v>
       </c>
       <c r="R61" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>7458</v>
       </c>
       <c r="S61" s="2">
@@ -8313,33 +8726,34 @@
       </c>
       <c r="T61" s="2"/>
       <c r="U61" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>4474.8</v>
       </c>
-      <c r="V61" s="4">
-        <f t="shared" si="69"/>
+      <c r="V61" s="2"/>
+      <c r="W61" s="4">
+        <f t="shared" si="63"/>
         <v>17732.8</v>
       </c>
-      <c r="W61" s="2">
-        <f t="shared" si="70"/>
+      <c r="X61" s="2">
+        <f>Y61+U61</f>
         <v>33688.6</v>
       </c>
-      <c r="X61" s="10">
-        <f t="shared" si="71"/>
+      <c r="Y61" s="10">
+        <f>P61-W61</f>
         <v>29213.8</v>
       </c>
-      <c r="Y61" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z61" s="2">
-        <f t="shared" si="72"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA61" s="2">
+        <f t="shared" si="64"/>
         <v>29213.8</v>
       </c>
-      <c r="AA61" s="2"/>
       <c r="AB61" s="2"/>
-    </row>
-    <row r="62" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC61" s="2"/>
+    </row>
+    <row r="62" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -8347,12 +8761,12 @@
         <v>32902</v>
       </c>
       <c r="E62" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="55"/>
         <v>4388</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>37290</v>
       </c>
       <c r="H62" s="2">
@@ -8364,34 +8778,34 @@
         <v>400</v>
       </c>
       <c r="J62" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="57"/>
         <v>2237.4</v>
       </c>
       <c r="K62" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>43656.4</v>
       </c>
       <c r="L62" s="2">
         <v>0</v>
       </c>
       <c r="M62" s="2">
-        <f>10%*D62</f>
+        <f t="shared" si="65"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="59"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P62" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="60"/>
         <v>46946.6</v>
       </c>
       <c r="Q62" s="2">
         <v>800</v>
       </c>
       <c r="R62" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>7458</v>
       </c>
       <c r="S62" s="2">
@@ -8399,33 +8813,34 @@
       </c>
       <c r="T62" s="2"/>
       <c r="U62" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>4474.8</v>
       </c>
-      <c r="V62" s="4">
-        <f t="shared" si="69"/>
+      <c r="V62" s="2"/>
+      <c r="W62" s="4">
+        <f t="shared" si="63"/>
         <v>17732.8</v>
       </c>
-      <c r="W62" s="2">
-        <f t="shared" si="70"/>
+      <c r="X62" s="2">
+        <f>Y62+U62</f>
         <v>33688.6</v>
       </c>
-      <c r="X62" s="10">
-        <f t="shared" si="71"/>
+      <c r="Y62" s="10">
+        <f>P62-W62</f>
         <v>29213.8</v>
       </c>
-      <c r="Y62" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z62" s="2">
-        <f t="shared" si="72"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA62" s="2">
+        <f t="shared" si="64"/>
         <v>29213.8</v>
       </c>
-      <c r="AA62" s="2"/>
       <c r="AB62" s="2"/>
-    </row>
-    <row r="63" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC62" s="2"/>
+    </row>
+    <row r="63" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -8433,12 +8848,12 @@
         <v>32902</v>
       </c>
       <c r="E63" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="55"/>
         <v>4388</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>37290</v>
       </c>
       <c r="H63" s="2">
@@ -8450,34 +8865,34 @@
         <v>400</v>
       </c>
       <c r="J63" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="57"/>
         <v>2237.4</v>
       </c>
       <c r="K63" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>43656.4</v>
       </c>
       <c r="L63" s="2">
         <v>0</v>
       </c>
       <c r="M63" s="2">
-        <f>10%*D63</f>
+        <f t="shared" si="65"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="59"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P63" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="60"/>
         <v>46946.6</v>
       </c>
       <c r="Q63" s="2">
         <v>800</v>
       </c>
       <c r="R63" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>7458</v>
       </c>
       <c r="S63" s="2">
@@ -8485,33 +8900,34 @@
       </c>
       <c r="T63" s="2"/>
       <c r="U63" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>4474.8</v>
       </c>
-      <c r="V63" s="4">
-        <f t="shared" si="69"/>
+      <c r="V63" s="2"/>
+      <c r="W63" s="4">
+        <f t="shared" si="63"/>
         <v>17732.8</v>
       </c>
-      <c r="W63" s="2">
-        <f t="shared" si="70"/>
+      <c r="X63" s="2">
+        <f>Y63+U63</f>
         <v>33688.6</v>
       </c>
-      <c r="X63" s="10">
-        <f t="shared" si="71"/>
+      <c r="Y63" s="10">
+        <f>P63-W63</f>
         <v>29213.8</v>
       </c>
-      <c r="Y63" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z63" s="2">
-        <f t="shared" si="72"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA63" s="2">
+        <f t="shared" si="64"/>
         <v>29213.8</v>
       </c>
-      <c r="AA63" s="2"/>
       <c r="AB63" s="2"/>
-    </row>
-    <row r="64" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC63" s="2"/>
+    </row>
+    <row r="64" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -8519,12 +8935,12 @@
         <v>32902</v>
       </c>
       <c r="E64" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="55"/>
         <v>4388</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>37290</v>
       </c>
       <c r="H64" s="2">
@@ -8536,34 +8952,34 @@
         <v>400</v>
       </c>
       <c r="J64" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="57"/>
         <v>2237.4</v>
       </c>
       <c r="K64" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>43656.4</v>
       </c>
       <c r="L64" s="2">
         <v>0</v>
       </c>
       <c r="M64" s="2">
-        <f>10%*D64</f>
+        <f t="shared" si="65"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="59"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P64" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="60"/>
         <v>46946.6</v>
       </c>
       <c r="Q64" s="2">
         <v>800</v>
       </c>
       <c r="R64" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>7458</v>
       </c>
       <c r="S64" s="2">
@@ -8571,33 +8987,34 @@
       </c>
       <c r="T64" s="2"/>
       <c r="U64" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>4474.8</v>
       </c>
-      <c r="V64" s="4">
-        <f t="shared" si="69"/>
+      <c r="V64" s="2"/>
+      <c r="W64" s="4">
+        <f t="shared" si="63"/>
         <v>17732.8</v>
       </c>
-      <c r="W64" s="2">
-        <f t="shared" si="70"/>
+      <c r="X64" s="2">
+        <f>Y64+U64</f>
         <v>33688.6</v>
       </c>
-      <c r="X64" s="10">
-        <f t="shared" si="71"/>
+      <c r="Y64" s="10">
+        <f>P64-W64</f>
         <v>29213.8</v>
       </c>
-      <c r="Y64" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z64" s="2">
-        <f t="shared" si="72"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA64" s="2">
+        <f t="shared" si="64"/>
         <v>29213.8</v>
       </c>
-      <c r="AA64" s="2"/>
       <c r="AB64" s="2"/>
-    </row>
-    <row r="65" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC64" s="2"/>
+    </row>
+    <row r="65" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -8605,12 +9022,12 @@
         <v>32902</v>
       </c>
       <c r="E65" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="55"/>
         <v>4388</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>37290</v>
       </c>
       <c r="H65" s="2">
@@ -8622,36 +9039,36 @@
         <v>400</v>
       </c>
       <c r="J65" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="57"/>
         <v>2237.4</v>
       </c>
       <c r="K65" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>43656.4</v>
       </c>
       <c r="L65" s="2">
         <v>0</v>
       </c>
       <c r="M65" s="2">
-        <f>10%*D65</f>
+        <f t="shared" si="65"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N65" s="2">
         <v>10000</v>
       </c>
       <c r="O65" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="59"/>
         <v>13290.2</v>
       </c>
       <c r="P65" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="60"/>
         <v>56946.600000000006</v>
       </c>
       <c r="Q65" s="2">
         <v>800</v>
       </c>
       <c r="R65" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>7458</v>
       </c>
       <c r="S65" s="2">
@@ -8659,33 +9076,34 @@
       </c>
       <c r="T65" s="2"/>
       <c r="U65" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>4474.8</v>
       </c>
-      <c r="V65" s="4">
-        <f t="shared" si="69"/>
+      <c r="V65" s="2"/>
+      <c r="W65" s="4">
+        <f t="shared" si="63"/>
         <v>17732.8</v>
       </c>
-      <c r="W65" s="2">
-        <f t="shared" si="70"/>
+      <c r="X65" s="2">
+        <f>Y65+U65</f>
         <v>43688.600000000006</v>
       </c>
-      <c r="X65" s="10">
-        <f t="shared" si="71"/>
+      <c r="Y65" s="10">
+        <f>P65-W65</f>
         <v>39213.800000000003</v>
       </c>
-      <c r="Y65" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z65" s="2">
-        <f t="shared" si="72"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA65" s="2">
+        <f t="shared" si="64"/>
         <v>39213.800000000003</v>
       </c>
-      <c r="AA65" s="2"/>
       <c r="AB65" s="2"/>
-    </row>
-    <row r="66" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC65" s="2"/>
+    </row>
+    <row r="66" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -8693,12 +9111,12 @@
         <v>32902</v>
       </c>
       <c r="E66" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="55"/>
         <v>4388</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>37290</v>
       </c>
       <c r="H66" s="2">
@@ -8710,34 +9128,34 @@
         <v>400</v>
       </c>
       <c r="J66" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="57"/>
         <v>2237.4</v>
       </c>
       <c r="K66" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>43656.4</v>
       </c>
       <c r="L66" s="2">
         <v>0</v>
       </c>
       <c r="M66" s="2">
-        <f>10%*D66</f>
+        <f t="shared" si="65"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="59"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P66" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="60"/>
         <v>46946.6</v>
       </c>
       <c r="Q66" s="2">
         <v>800</v>
       </c>
       <c r="R66" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>7458</v>
       </c>
       <c r="S66" s="2">
@@ -8745,33 +9163,34 @@
       </c>
       <c r="T66" s="2"/>
       <c r="U66" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>4474.8</v>
       </c>
-      <c r="V66" s="4">
-        <f t="shared" si="69"/>
+      <c r="V66" s="2"/>
+      <c r="W66" s="4">
+        <f t="shared" si="63"/>
         <v>17732.8</v>
       </c>
-      <c r="W66" s="2">
-        <f t="shared" si="70"/>
+      <c r="X66" s="2">
+        <f>Y66+U66</f>
         <v>33688.6</v>
       </c>
-      <c r="X66" s="10">
-        <f t="shared" si="71"/>
+      <c r="Y66" s="10">
+        <f>P66-W66</f>
         <v>29213.8</v>
       </c>
-      <c r="Y66" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
       <c r="Z66" s="2">
-        <f t="shared" si="72"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA66" s="2">
+        <f t="shared" si="64"/>
         <v>29213.8</v>
       </c>
-      <c r="AA66" s="2"/>
       <c r="AB66" s="2"/>
-    </row>
-    <row r="67" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC66" s="2"/>
+    </row>
+    <row r="67" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -8779,16 +9198,16 @@
         <v>32902</v>
       </c>
       <c r="E67" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="55"/>
         <v>4388</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>37290</v>
       </c>
       <c r="H67" s="2">
-        <f t="shared" ref="H67:H68" si="73">10%*G67</f>
+        <f t="shared" ref="H67:H68" si="66">10%*G67</f>
         <v>3729</v>
       </c>
       <c r="I67" s="2">
@@ -8796,34 +9215,34 @@
         <v>400</v>
       </c>
       <c r="J67" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="57"/>
         <v>2237.4</v>
       </c>
       <c r="K67" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>43656.4</v>
       </c>
       <c r="L67" s="2">
         <v>0</v>
       </c>
       <c r="M67" s="2">
-        <f>10%*D67</f>
+        <f t="shared" si="65"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="59"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P67" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="60"/>
         <v>46946.6</v>
       </c>
       <c r="Q67" s="2">
         <v>800</v>
       </c>
       <c r="R67" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>7458</v>
       </c>
       <c r="S67" s="2">
@@ -8831,33 +9250,34 @@
       </c>
       <c r="T67" s="2"/>
       <c r="U67" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>4474.8</v>
       </c>
-      <c r="V67" s="4">
-        <f t="shared" si="69"/>
+      <c r="V67" s="2"/>
+      <c r="W67" s="4">
+        <f t="shared" si="63"/>
         <v>17732.8</v>
       </c>
-      <c r="W67" s="2">
-        <f t="shared" si="70"/>
+      <c r="X67" s="2">
+        <f>Y67+U67</f>
         <v>33688.6</v>
       </c>
-      <c r="X67" s="10">
-        <f t="shared" si="71"/>
+      <c r="Y67" s="10">
+        <f>P67-W67</f>
         <v>29213.8</v>
       </c>
-      <c r="Y67" s="2">
-        <f t="shared" ref="Y67:Y68" si="74">IF(X67*13&gt;600000,1%*X67,0)</f>
-        <v>0</v>
-      </c>
       <c r="Z67" s="2">
-        <f t="shared" si="72"/>
+        <f t="shared" ref="Z67:Z68" si="67">IF(Y67*13&gt;600000,1%*Y67,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA67" s="2">
+        <f t="shared" si="64"/>
         <v>29213.8</v>
       </c>
-      <c r="AA67" s="2"/>
       <c r="AB67" s="2"/>
-    </row>
-    <row r="68" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC67" s="2"/>
+    </row>
+    <row r="68" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -8870,11 +9290,11 @@
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>38387</v>
       </c>
       <c r="H68" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="66"/>
         <v>3838.7000000000003</v>
       </c>
       <c r="I68" s="2">
@@ -8882,34 +9302,34 @@
         <v>400</v>
       </c>
       <c r="J68" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="57"/>
         <v>2303.2199999999998</v>
       </c>
       <c r="K68" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>44928.92</v>
       </c>
       <c r="L68" s="2">
         <v>0</v>
       </c>
       <c r="M68" s="2">
-        <f>10%*D68</f>
+        <f t="shared" si="65"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="59"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P68" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="60"/>
         <v>48219.119999999995</v>
       </c>
       <c r="Q68" s="2">
         <v>800</v>
       </c>
       <c r="R68" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>7677.4000000000005</v>
       </c>
       <c r="S68" s="2">
@@ -8917,33 +9337,34 @@
       </c>
       <c r="T68" s="2"/>
       <c r="U68" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>4606.4399999999996</v>
       </c>
-      <c r="V68" s="4">
-        <f t="shared" si="69"/>
+      <c r="V68" s="2"/>
+      <c r="W68" s="4">
+        <f t="shared" si="63"/>
         <v>18083.84</v>
       </c>
-      <c r="W68" s="2">
-        <f t="shared" si="70"/>
+      <c r="X68" s="2">
+        <f>Y68+U68</f>
         <v>34741.719999999994</v>
       </c>
-      <c r="X68" s="10">
-        <f t="shared" si="71"/>
+      <c r="Y68" s="10">
+        <f>P68-W68</f>
         <v>30135.279999999995</v>
       </c>
-      <c r="Y68" s="2">
-        <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
       <c r="Z68" s="2">
-        <f t="shared" si="72"/>
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AA68" s="2">
+        <f t="shared" si="64"/>
         <v>30135.279999999995</v>
       </c>
-      <c r="AA68" s="2"/>
       <c r="AB68" s="2"/>
-    </row>
-    <row r="69" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC68" s="2"/>
+    </row>
+    <row r="69" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -8965,15 +9386,16 @@
       <c r="S69" s="2"/>
       <c r="T69" s="2"/>
       <c r="U69" s="2"/>
-      <c r="V69" s="4"/>
-      <c r="W69" s="2"/>
-      <c r="X69" s="10"/>
-      <c r="Y69" s="2"/>
+      <c r="V69" s="2"/>
+      <c r="W69" s="4"/>
+      <c r="X69" s="2"/>
+      <c r="Y69" s="10"/>
       <c r="Z69" s="2"/>
       <c r="AA69" s="2"/>
       <c r="AB69" s="2"/>
-    </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC69" s="2"/>
+    </row>
+    <row r="70" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -9034,30 +9456,31 @@
         <f>J70*2</f>
         <v>4474.8</v>
       </c>
-      <c r="V70" s="4">
+      <c r="V70" s="2"/>
+      <c r="W70" s="4">
         <f>SUM(Q70:U70)</f>
         <v>17732.8</v>
       </c>
-      <c r="W70" s="2">
-        <f>X70+U70</f>
+      <c r="X70" s="2">
+        <f>Y70+U70</f>
         <v>32398.400000000001</v>
       </c>
-      <c r="X70" s="10">
-        <f>P70-V70</f>
+      <c r="Y70" s="10">
+        <f>P70-W70</f>
         <v>27923.600000000002</v>
       </c>
-      <c r="Y70" s="2">
-        <f>IF(X70*13&gt;600000,1%*X70,0)</f>
-        <v>0</v>
-      </c>
       <c r="Z70" s="2">
-        <f>X70-Y70</f>
+        <f>IF(Y70*13&gt;600000,1%*Y70,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA70" s="2">
+        <f>Y70-Z70</f>
         <v>27923.600000000002</v>
       </c>
-      <c r="AA70" s="2"/>
       <c r="AB70" s="2"/>
-    </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC70" s="2"/>
+    </row>
+    <row r="71" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -9120,30 +9543,31 @@
         <f>J71*2</f>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V71" s="4">
+      <c r="V71" s="2"/>
+      <c r="W71" s="4">
         <f>SUM(Q71:U71)</f>
         <v>18395.84</v>
       </c>
-      <c r="W71" s="2">
-        <f>X71+U71</f>
+      <c r="X71" s="2">
+        <f>Y71+U71</f>
         <v>76749.52</v>
       </c>
-      <c r="X71" s="10">
-        <f>P71-V71</f>
+      <c r="Y71" s="10">
+        <f>P71-W71</f>
         <v>72026.080000000002</v>
       </c>
-      <c r="Y71" s="12">
-        <f>IF(X71*13&gt;600000,1%*X71,0)</f>
+      <c r="Z71" s="12">
+        <f>IF(Y71*13&gt;600000,1%*Y71,0)</f>
         <v>720.26080000000002</v>
       </c>
-      <c r="Z71" s="12">
-        <f>X71-Y71</f>
+      <c r="AA71" s="12">
+        <f>Y71-Z71</f>
         <v>71305.819199999998</v>
       </c>
-      <c r="AA71" s="2"/>
       <c r="AB71" s="2"/>
-    </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC71" s="2"/>
+    </row>
+    <row r="72" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -9205,30 +9629,31 @@
         <f>J72*2</f>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V72" s="4">
+      <c r="V72" s="2"/>
+      <c r="W72" s="4">
         <f>SUM(Q72:U72)</f>
         <v>18395.84</v>
       </c>
-      <c r="W72" s="2">
-        <f>X72+U72</f>
+      <c r="X72" s="2">
+        <f>Y72+U72</f>
         <v>37387.519999999997</v>
       </c>
-      <c r="X72" s="10">
-        <f>P72-V72</f>
+      <c r="Y72" s="10">
+        <f>P72-W72</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="Y72" s="2">
-        <f>IF(X72*13&gt;600000,1%*X72,0)</f>
-        <v>0</v>
-      </c>
       <c r="Z72" s="2">
-        <f>X72-Y72</f>
+        <f>IF(Y72*13&gt;600000,1%*Y72,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA72" s="2">
+        <f>Y72-Z72</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="AA72" s="2"/>
       <c r="AB72" s="2"/>
-    </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC72" s="2"/>
+    </row>
+    <row r="73" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -9290,30 +9715,31 @@
         <f>J73*2</f>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V73" s="4">
+      <c r="V73" s="2"/>
+      <c r="W73" s="4">
         <f>SUM(Q73:U73)</f>
         <v>18395.84</v>
       </c>
-      <c r="W73" s="2">
-        <f>X73+U73</f>
+      <c r="X73" s="2">
+        <f>Y73+U73</f>
         <v>37387.519999999997</v>
       </c>
-      <c r="X73" s="10">
-        <f>P73-V73</f>
+      <c r="Y73" s="10">
+        <f>P73-W73</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="Y73" s="2">
-        <f>IF(X73*13&gt;600000,1%*X73,0)</f>
-        <v>0</v>
-      </c>
       <c r="Z73" s="2">
-        <f>X73-Y73</f>
+        <f>IF(Y73*13&gt;600000,1%*Y73,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA73" s="2">
+        <f>Y73-Z73</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="AA73" s="2"/>
       <c r="AB73" s="2"/>
-    </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC73" s="2"/>
+    </row>
+    <row r="74" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -9375,30 +9801,31 @@
         <f>J74*2</f>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V74" s="4">
+      <c r="V74" s="2"/>
+      <c r="W74" s="4">
         <f>SUM(Q74:U74)</f>
         <v>18395.84</v>
       </c>
-      <c r="W74" s="2">
-        <f>X74+U74</f>
+      <c r="X74" s="2">
+        <f>Y74+U74</f>
         <v>37387.519999999997</v>
       </c>
-      <c r="X74" s="10">
-        <f>P74-V74</f>
+      <c r="Y74" s="10">
+        <f>P74-W74</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="Y74" s="2">
-        <f>IF(X74*13&gt;600000,1%*X74,0)</f>
-        <v>0</v>
-      </c>
       <c r="Z74" s="2">
-        <f>X74-Y74</f>
+        <f>IF(Y74*13&gt;600000,1%*Y74,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA74" s="2">
+        <f>Y74-Z74</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="AA74" s="2"/>
       <c r="AB74" s="2"/>
-    </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC74" s="2"/>
+    </row>
+    <row r="75" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -9406,31 +9833,31 @@
         <v>34730</v>
       </c>
       <c r="E75" s="4">
-        <f t="shared" ref="E75:E80" si="75">ROUNDUP(D75/30,0)*4</f>
+        <f t="shared" ref="E75:E80" si="68">ROUNDUP(D75/30,0)*4</f>
         <v>4632</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="8">
-        <f t="shared" ref="G75:G81" si="76">SUM(D75:F75)</f>
+        <f t="shared" ref="G75:G82" si="69">SUM(D75:F75)</f>
         <v>39362</v>
       </c>
       <c r="H75" s="2">
-        <f t="shared" ref="H75:H81" si="77">10%*G75</f>
+        <f t="shared" ref="H75:H82" si="70">10%*G75</f>
         <v>3936.2000000000003</v>
       </c>
       <c r="I75" s="2">
         <v>400</v>
       </c>
       <c r="J75" s="2">
-        <f t="shared" ref="J75:J81" si="78">6%*G75</f>
+        <f t="shared" ref="J75:J82" si="71">6%*G75</f>
         <v>2361.7199999999998</v>
       </c>
       <c r="K75" s="8">
-        <f t="shared" ref="K75:K81" si="79">SUM(G75:J75)</f>
+        <f t="shared" ref="K75:K82" si="72">SUM(G75:J75)</f>
         <v>46059.92</v>
       </c>
       <c r="L75" s="2">
-        <f t="shared" ref="L75:L84" si="80">2000+3000</f>
+        <f t="shared" ref="L75:L90" si="73">2000+3000</f>
         <v>5000</v>
       </c>
       <c r="M75" s="2">
@@ -9438,18 +9865,18 @@
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="4">
-        <f t="shared" ref="O75:O77" si="81">SUM(L75:M75)</f>
+        <f t="shared" ref="O75:O77" si="74">SUM(L75:M75)</f>
         <v>5000</v>
       </c>
       <c r="P75" s="8">
-        <f t="shared" ref="P75:P81" si="82">K75+O75</f>
+        <f t="shared" ref="P75:P82" si="75">K75+O75</f>
         <v>51059.92</v>
       </c>
       <c r="Q75" s="2">
         <v>800</v>
       </c>
       <c r="R75" s="2">
-        <f t="shared" ref="R75:R81" si="83">H75*2</f>
+        <f t="shared" ref="R75:R82" si="76">H75*2</f>
         <v>7872.4000000000005</v>
       </c>
       <c r="S75" s="2">
@@ -9457,33 +9884,34 @@
       </c>
       <c r="T75" s="2"/>
       <c r="U75" s="2">
-        <f t="shared" ref="U75:U81" si="84">J75*2</f>
+        <f t="shared" ref="U75:U82" si="77">J75*2</f>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V75" s="4">
-        <f t="shared" ref="V75:V81" si="85">SUM(Q75:U75)</f>
+      <c r="V75" s="2"/>
+      <c r="W75" s="4">
+        <f t="shared" ref="W75:W82" si="78">SUM(Q75:U75)</f>
         <v>18395.84</v>
       </c>
-      <c r="W75" s="2">
-        <f t="shared" ref="W75:W81" si="86">X75+U75</f>
+      <c r="X75" s="2">
+        <f>Y75+U75</f>
         <v>37387.519999999997</v>
       </c>
-      <c r="X75" s="10">
-        <f t="shared" ref="X75:X81" si="87">P75-V75</f>
+      <c r="Y75" s="10">
+        <f>P75-W75</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="Y75" s="2">
-        <f t="shared" ref="Y75:Y81" si="88">IF(X75*13&gt;600000,1%*X75,0)</f>
-        <v>0</v>
-      </c>
       <c r="Z75" s="2">
-        <f t="shared" ref="Z75:Z81" si="89">X75-Y75</f>
+        <f t="shared" ref="Z75:Z80" si="79">IF(Y75*13&gt;600000,1%*Y75,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA75" s="2">
+        <f t="shared" ref="AA75:AA82" si="80">Y75-Z75</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="AA75" s="2"/>
       <c r="AB75" s="2"/>
-    </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC75" s="2"/>
+    </row>
+    <row r="76" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -9491,31 +9919,31 @@
         <v>34730</v>
       </c>
       <c r="E76" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="68"/>
         <v>4632</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="69"/>
         <v>39362</v>
       </c>
       <c r="H76" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="70"/>
         <v>3936.2000000000003</v>
       </c>
       <c r="I76" s="2">
         <v>400</v>
       </c>
       <c r="J76" s="2">
-        <f t="shared" si="78"/>
+        <f t="shared" si="71"/>
         <v>2361.7199999999998</v>
       </c>
       <c r="K76" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="72"/>
         <v>46059.92</v>
       </c>
       <c r="L76" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="73"/>
         <v>5000</v>
       </c>
       <c r="M76" s="2">
@@ -9523,18 +9951,18 @@
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="4">
-        <f t="shared" si="81"/>
+        <f t="shared" si="74"/>
         <v>5000</v>
       </c>
       <c r="P76" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="75"/>
         <v>51059.92</v>
       </c>
       <c r="Q76" s="2">
         <v>800</v>
       </c>
       <c r="R76" s="2">
-        <f t="shared" si="83"/>
+        <f t="shared" si="76"/>
         <v>7872.4000000000005</v>
       </c>
       <c r="S76" s="2">
@@ -9542,33 +9970,34 @@
       </c>
       <c r="T76" s="2"/>
       <c r="U76" s="2">
-        <f t="shared" si="84"/>
+        <f t="shared" si="77"/>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V76" s="4">
-        <f t="shared" si="85"/>
+      <c r="V76" s="2"/>
+      <c r="W76" s="4">
+        <f t="shared" si="78"/>
         <v>18395.84</v>
       </c>
-      <c r="W76" s="2">
-        <f t="shared" si="86"/>
+      <c r="X76" s="2">
+        <f>Y76+U76</f>
         <v>37387.519999999997</v>
       </c>
-      <c r="X76" s="10">
-        <f t="shared" si="87"/>
+      <c r="Y76" s="10">
+        <f>P76-W76</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="Y76" s="2">
-        <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
       <c r="Z76" s="2">
-        <f t="shared" si="89"/>
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="AA76" s="2">
+        <f t="shared" si="80"/>
         <v>32664.079999999998</v>
       </c>
-      <c r="AA76" s="2"/>
       <c r="AB76" s="2"/>
-    </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC76" s="2"/>
+    </row>
+    <row r="77" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -9576,31 +10005,30 @@
         <v>34730</v>
       </c>
       <c r="E77" s="4">
-        <f t="shared" si="75"/>
-        <v>4632</v>
+        <v>0</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="8">
-        <f t="shared" si="76"/>
-        <v>39362</v>
+        <f t="shared" si="69"/>
+        <v>34730</v>
       </c>
       <c r="H77" s="2">
-        <f t="shared" si="77"/>
-        <v>3936.2000000000003</v>
+        <f t="shared" si="70"/>
+        <v>3473</v>
       </c>
       <c r="I77" s="2">
         <v>400</v>
       </c>
       <c r="J77" s="2">
-        <f t="shared" si="78"/>
-        <v>2361.7199999999998</v>
+        <f t="shared" si="71"/>
+        <v>2083.7999999999997</v>
       </c>
       <c r="K77" s="8">
-        <f t="shared" si="79"/>
-        <v>46059.92</v>
+        <f t="shared" si="72"/>
+        <v>40686.800000000003</v>
       </c>
       <c r="L77" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="73"/>
         <v>5000</v>
       </c>
       <c r="M77" s="2">
@@ -9608,52 +10036,53 @@
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="4">
-        <f t="shared" si="81"/>
+        <f t="shared" si="74"/>
         <v>5000</v>
       </c>
       <c r="P77" s="8">
-        <f t="shared" si="82"/>
-        <v>51059.92</v>
+        <f t="shared" si="75"/>
+        <v>45686.8</v>
       </c>
       <c r="Q77" s="2">
         <v>800</v>
       </c>
       <c r="R77" s="2">
-        <f t="shared" si="83"/>
-        <v>7872.4000000000005</v>
+        <f t="shared" si="76"/>
+        <v>6946</v>
       </c>
       <c r="S77" s="2">
         <v>5000</v>
       </c>
       <c r="T77" s="2"/>
       <c r="U77" s="2">
-        <f t="shared" si="84"/>
-        <v>4723.4399999999996</v>
-      </c>
-      <c r="V77" s="4">
-        <f t="shared" si="85"/>
-        <v>18395.84</v>
-      </c>
-      <c r="W77" s="2">
-        <f t="shared" si="86"/>
-        <v>37387.519999999997</v>
-      </c>
-      <c r="X77" s="10">
-        <f t="shared" si="87"/>
-        <v>32664.079999999998</v>
-      </c>
-      <c r="Y77" s="2">
-        <f t="shared" si="88"/>
-        <v>0</v>
+        <f t="shared" si="77"/>
+        <v>4167.5999999999995</v>
+      </c>
+      <c r="V77" s="2"/>
+      <c r="W77" s="4">
+        <f t="shared" si="78"/>
+        <v>16913.599999999999</v>
+      </c>
+      <c r="X77" s="2">
+        <f>Y77+U77</f>
+        <v>32940.800000000003</v>
+      </c>
+      <c r="Y77" s="10">
+        <f>P77-W77</f>
+        <v>28773.200000000004</v>
       </c>
       <c r="Z77" s="2">
-        <f t="shared" si="89"/>
-        <v>32664.079999999998</v>
-      </c>
-      <c r="AA77" s="2"/>
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="AA77" s="2">
+        <f t="shared" si="80"/>
+        <v>28773.200000000004</v>
+      </c>
       <c r="AB77" s="2"/>
-    </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC77" s="2"/>
+    </row>
+    <row r="78" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -9661,31 +10090,31 @@
         <v>34730</v>
       </c>
       <c r="E78" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="68"/>
         <v>4632</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="69"/>
         <v>39362</v>
       </c>
       <c r="H78" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="70"/>
         <v>3936.2000000000003</v>
       </c>
       <c r="I78" s="2">
         <v>400</v>
       </c>
       <c r="J78" s="2">
-        <f t="shared" si="78"/>
+        <f t="shared" si="71"/>
         <v>2361.7199999999998</v>
       </c>
       <c r="K78" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="72"/>
         <v>46059.92</v>
       </c>
       <c r="L78" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="73"/>
         <v>5000</v>
       </c>
       <c r="M78" s="2">
@@ -9699,14 +10128,14 @@
         <v>15000</v>
       </c>
       <c r="P78" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="75"/>
         <v>61059.92</v>
       </c>
       <c r="Q78" s="2">
         <v>800</v>
       </c>
       <c r="R78" s="2">
-        <f t="shared" si="83"/>
+        <f t="shared" si="76"/>
         <v>7872.4000000000005</v>
       </c>
       <c r="S78" s="2">
@@ -9714,33 +10143,34 @@
       </c>
       <c r="T78" s="2"/>
       <c r="U78" s="2">
-        <f t="shared" si="84"/>
+        <f t="shared" si="77"/>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V78" s="4">
-        <f t="shared" si="85"/>
+      <c r="V78" s="2"/>
+      <c r="W78" s="4">
+        <f t="shared" si="78"/>
         <v>18395.84</v>
       </c>
-      <c r="W78" s="2">
-        <f t="shared" si="86"/>
+      <c r="X78" s="2">
+        <f>Y78+U78</f>
         <v>47387.520000000004</v>
       </c>
-      <c r="X78" s="10">
-        <f t="shared" si="87"/>
+      <c r="Y78" s="10">
+        <f>P78-W78</f>
         <v>42664.08</v>
       </c>
-      <c r="Y78" s="2">
-        <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
       <c r="Z78" s="2">
-        <f t="shared" si="89"/>
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="AA78" s="2">
+        <f t="shared" si="80"/>
         <v>42664.08</v>
       </c>
-      <c r="AA78" s="2"/>
       <c r="AB78" s="2"/>
-    </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC78" s="2"/>
+    </row>
+    <row r="79" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -9748,31 +10178,31 @@
         <v>34730</v>
       </c>
       <c r="E79" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="68"/>
         <v>4632</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="69"/>
         <v>39362</v>
       </c>
       <c r="H79" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="70"/>
         <v>3936.2000000000003</v>
       </c>
       <c r="I79" s="2">
         <v>400</v>
       </c>
       <c r="J79" s="2">
-        <f t="shared" si="78"/>
+        <f t="shared" si="71"/>
         <v>2361.7199999999998</v>
       </c>
       <c r="K79" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="72"/>
         <v>46059.92</v>
       </c>
       <c r="L79" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="73"/>
         <v>5000</v>
       </c>
       <c r="M79" s="2">
@@ -9780,18 +10210,18 @@
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="4">
-        <f t="shared" ref="O79:O81" si="90">SUM(L79:M79)</f>
+        <f t="shared" ref="O79:O82" si="81">SUM(L79:M79)</f>
         <v>5000</v>
       </c>
       <c r="P79" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="75"/>
         <v>51059.92</v>
       </c>
       <c r="Q79" s="2">
         <v>800</v>
       </c>
       <c r="R79" s="2">
-        <f t="shared" si="83"/>
+        <f t="shared" si="76"/>
         <v>7872.4000000000005</v>
       </c>
       <c r="S79" s="2">
@@ -9799,33 +10229,34 @@
       </c>
       <c r="T79" s="2"/>
       <c r="U79" s="2">
-        <f t="shared" si="84"/>
+        <f t="shared" si="77"/>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V79" s="4">
-        <f t="shared" si="85"/>
+      <c r="V79" s="2"/>
+      <c r="W79" s="4">
+        <f t="shared" si="78"/>
         <v>18395.84</v>
       </c>
-      <c r="W79" s="2">
-        <f t="shared" si="86"/>
+      <c r="X79" s="2">
+        <f>Y79+U79</f>
         <v>37387.519999999997</v>
       </c>
-      <c r="X79" s="10">
-        <f t="shared" si="87"/>
+      <c r="Y79" s="10">
+        <f>P79-W79</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="Y79" s="2">
-        <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
       <c r="Z79" s="2">
-        <f t="shared" si="89"/>
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="AA79" s="2">
+        <f t="shared" si="80"/>
         <v>32664.079999999998</v>
       </c>
-      <c r="AA79" s="2"/>
       <c r="AB79" s="2"/>
-    </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC79" s="2"/>
+    </row>
+    <row r="80" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -9833,31 +10264,31 @@
         <v>34730</v>
       </c>
       <c r="E80" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="68"/>
         <v>4632</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="69"/>
         <v>39362</v>
       </c>
       <c r="H80" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="70"/>
         <v>3936.2000000000003</v>
       </c>
       <c r="I80" s="2">
         <v>400</v>
       </c>
       <c r="J80" s="2">
-        <f t="shared" si="78"/>
+        <f t="shared" si="71"/>
         <v>2361.7199999999998</v>
       </c>
       <c r="K80" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="72"/>
         <v>46059.92</v>
       </c>
       <c r="L80" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="73"/>
         <v>5000</v>
       </c>
       <c r="M80" s="2">
@@ -9865,18 +10296,18 @@
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="4">
-        <f t="shared" si="90"/>
+        <f t="shared" si="81"/>
         <v>5000</v>
       </c>
       <c r="P80" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="75"/>
         <v>51059.92</v>
       </c>
       <c r="Q80" s="2">
         <v>800</v>
       </c>
       <c r="R80" s="2">
-        <f t="shared" si="83"/>
+        <f t="shared" si="76"/>
         <v>7872.4000000000005</v>
       </c>
       <c r="S80" s="2">
@@ -9884,154 +10315,204 @@
       </c>
       <c r="T80" s="2"/>
       <c r="U80" s="2">
-        <f t="shared" si="84"/>
+        <f t="shared" si="77"/>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V80" s="4">
-        <f t="shared" si="85"/>
+      <c r="V80" s="2"/>
+      <c r="W80" s="4">
+        <f t="shared" si="78"/>
         <v>18395.84</v>
       </c>
-      <c r="W80" s="2">
-        <f t="shared" si="86"/>
+      <c r="X80" s="2">
+        <f>Y80+U80</f>
         <v>37387.519999999997</v>
       </c>
-      <c r="X80" s="10">
-        <f t="shared" si="87"/>
+      <c r="Y80" s="10">
+        <f>P80-W80</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="Y80" s="2">
-        <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
       <c r="Z80" s="2">
-        <f t="shared" si="89"/>
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="AA80" s="2">
+        <f t="shared" si="80"/>
         <v>32664.079999999998</v>
       </c>
-      <c r="AA80" s="2"/>
       <c r="AB80" s="2"/>
-    </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A81" s="2"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="4">
+      <c r="AC80" s="2"/>
+    </row>
+    <row r="81" spans="1:29" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="40"/>
+      <c r="B81" s="40"/>
+      <c r="C81" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="D81" s="35">
         <v>34730</v>
       </c>
-      <c r="E81" s="4">
-        <f>ROUNDUP(D81/30,0)*5</f>
+      <c r="E81" s="35">
+        <f t="shared" ref="E81" si="82">ROUNDUP(D81/30,0)*4</f>
+        <v>4632</v>
+      </c>
+      <c r="F81" s="40"/>
+      <c r="G81" s="41">
+        <f t="shared" ref="G81" si="83">SUM(D81:F81)</f>
+        <v>39362</v>
+      </c>
+      <c r="H81" s="40">
+        <f t="shared" ref="H81" si="84">10%*G81</f>
+        <v>3936.2000000000003</v>
+      </c>
+      <c r="I81" s="40">
+        <v>400</v>
+      </c>
+      <c r="J81" s="40">
+        <f t="shared" ref="J81" si="85">6%*G81</f>
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K81" s="41">
+        <f t="shared" ref="K81" si="86">SUM(G81:J81)</f>
+        <v>46059.92</v>
+      </c>
+      <c r="L81" s="40">
+        <f t="shared" si="73"/>
+        <v>5000</v>
+      </c>
+      <c r="M81" s="40">
+        <v>0</v>
+      </c>
+      <c r="N81" s="40"/>
+      <c r="O81" s="35">
+        <f t="shared" ref="O81" si="87">SUM(L81:M81)</f>
+        <v>5000</v>
+      </c>
+      <c r="P81" s="41">
+        <f t="shared" ref="P81" si="88">K81+O81</f>
+        <v>51059.92</v>
+      </c>
+      <c r="Q81" s="40">
+        <v>800</v>
+      </c>
+      <c r="R81" s="40">
+        <f t="shared" ref="R81" si="89">H81*2</f>
+        <v>7872.4000000000005</v>
+      </c>
+      <c r="S81" s="40">
+        <v>5000</v>
+      </c>
+      <c r="T81" s="40"/>
+      <c r="U81" s="40">
+        <f t="shared" ref="U81" si="90">J81*2</f>
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V81" s="40"/>
+      <c r="W81" s="35">
+        <f t="shared" ref="W81" si="91">SUM(Q81:U81)</f>
+        <v>18395.84</v>
+      </c>
+      <c r="X81" s="40">
+        <f>Y81+U81</f>
+        <v>37387.519999999997</v>
+      </c>
+      <c r="Y81" s="42">
+        <f>P81-W81</f>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="Z81" s="40"/>
+      <c r="AA81" s="40">
+        <f t="shared" ref="AA81" si="92">Y81-Z81</f>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="AB81" s="40"/>
+      <c r="AC81" s="40"/>
+    </row>
+    <row r="82" spans="1:29" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="19"/>
+      <c r="B82" s="19"/>
+      <c r="C82" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D82" s="20">
+        <v>34730</v>
+      </c>
+      <c r="E82" s="20">
+        <f>ROUNDUP(D82/30,0)*5</f>
         <v>5790</v>
       </c>
-      <c r="F81" s="2"/>
-      <c r="G81" s="8">
+      <c r="F82" s="19"/>
+      <c r="G82" s="22">
+        <f t="shared" si="69"/>
+        <v>40520</v>
+      </c>
+      <c r="H82" s="19">
+        <f t="shared" si="70"/>
+        <v>4052</v>
+      </c>
+      <c r="I82" s="19">
+        <v>400</v>
+      </c>
+      <c r="J82" s="19">
+        <f t="shared" si="71"/>
+        <v>2431.1999999999998</v>
+      </c>
+      <c r="K82" s="22">
+        <f t="shared" si="72"/>
+        <v>47403.199999999997</v>
+      </c>
+      <c r="L82" s="19">
+        <f t="shared" si="73"/>
+        <v>5000</v>
+      </c>
+      <c r="M82" s="19">
+        <v>0</v>
+      </c>
+      <c r="N82" s="19"/>
+      <c r="O82" s="20">
+        <f t="shared" si="81"/>
+        <v>5000</v>
+      </c>
+      <c r="P82" s="22">
+        <f t="shared" si="75"/>
+        <v>52403.199999999997</v>
+      </c>
+      <c r="Q82" s="19">
+        <v>800</v>
+      </c>
+      <c r="R82" s="19">
         <f t="shared" si="76"/>
-        <v>40520</v>
-      </c>
-      <c r="H81" s="2">
+        <v>8104</v>
+      </c>
+      <c r="S82" s="19">
+        <v>5000</v>
+      </c>
+      <c r="T82" s="19"/>
+      <c r="U82" s="19">
         <f t="shared" si="77"/>
-        <v>4052</v>
-      </c>
-      <c r="I81" s="2">
-        <v>400</v>
-      </c>
-      <c r="J81" s="2">
+        <v>4862.3999999999996</v>
+      </c>
+      <c r="V82" s="19"/>
+      <c r="W82" s="20">
         <f t="shared" si="78"/>
-        <v>2431.1999999999998</v>
-      </c>
-      <c r="K81" s="8">
-        <f t="shared" si="79"/>
-        <v>47403.199999999997</v>
-      </c>
-      <c r="L81" s="2">
+        <v>18766.400000000001</v>
+      </c>
+      <c r="X82" s="19">
+        <f>Y82+U82</f>
+        <v>38499.199999999997</v>
+      </c>
+      <c r="Y82" s="23">
+        <f>P82-W82</f>
+        <v>33636.799999999996</v>
+      </c>
+      <c r="Z82" s="19"/>
+      <c r="AA82" s="19">
         <f t="shared" si="80"/>
-        <v>5000</v>
-      </c>
-      <c r="M81" s="2">
-        <v>0</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="4">
-        <f t="shared" si="90"/>
-        <v>5000</v>
-      </c>
-      <c r="P81" s="8">
-        <f t="shared" si="82"/>
-        <v>52403.199999999997</v>
-      </c>
-      <c r="Q81" s="2">
-        <v>800</v>
-      </c>
-      <c r="R81" s="2">
-        <f t="shared" si="83"/>
-        <v>8104</v>
-      </c>
-      <c r="S81" s="2">
-        <v>5000</v>
-      </c>
-      <c r="T81" s="2"/>
-      <c r="U81" s="2">
-        <f t="shared" si="84"/>
-        <v>4862.3999999999996</v>
-      </c>
-      <c r="V81" s="4">
-        <f t="shared" si="85"/>
-        <v>18766.400000000001</v>
-      </c>
-      <c r="W81" s="2">
-        <f t="shared" si="86"/>
-        <v>38499.199999999997</v>
-      </c>
-      <c r="X81" s="10">
-        <f t="shared" si="87"/>
         <v>33636.799999999996</v>
       </c>
-      <c r="Y81" s="2">
-        <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="Z81" s="2">
-        <f t="shared" si="89"/>
-        <v>33636.799999999996</v>
-      </c>
-      <c r="AA81" s="2"/>
-      <c r="AB81" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="8">
-        <v>0</v>
-      </c>
-      <c r="L82" s="2"/>
-      <c r="M82" s="2">
-        <v>5100</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="4"/>
-      <c r="P82" s="8"/>
-      <c r="Q82" s="2"/>
-      <c r="R82" s="2"/>
-      <c r="S82" s="2"/>
-      <c r="T82" s="2"/>
-      <c r="U82" s="2"/>
-      <c r="V82" s="4"/>
-      <c r="W82" s="2"/>
-      <c r="X82" s="10"/>
-      <c r="Y82" s="2"/>
-      <c r="Z82" s="2"/>
-      <c r="AA82" s="2"/>
-      <c r="AB82" s="2"/>
-    </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AB82" s="19"/>
+      <c r="AC82" s="19"/>
+    </row>
+    <row r="83" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -10042,9 +10523,13 @@
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
-      <c r="K83" s="8"/>
+      <c r="K83" s="8">
+        <v>0</v>
+      </c>
       <c r="L83" s="2"/>
-      <c r="M83" s="2"/>
+      <c r="M83" s="2">
+        <v>5100</v>
+      </c>
       <c r="N83" s="2"/>
       <c r="O83" s="4"/>
       <c r="P83" s="8"/>
@@ -10053,342 +10538,519 @@
       <c r="S83" s="2"/>
       <c r="T83" s="2"/>
       <c r="U83" s="2"/>
-      <c r="V83" s="4"/>
-      <c r="W83" s="2"/>
-      <c r="X83" s="10"/>
-      <c r="Y83" s="2"/>
+      <c r="V83" s="2"/>
+      <c r="W83" s="4"/>
+      <c r="X83" s="2"/>
+      <c r="Y83" s="10"/>
       <c r="Z83" s="2"/>
       <c r="AA83" s="2"/>
       <c r="AB83" s="2"/>
-    </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC83" s="2"/>
+    </row>
+    <row r="84" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
-      <c r="D84" s="4">
-        <f>34730*1.1</f>
-        <v>38203</v>
-      </c>
-      <c r="E84" s="4">
-        <f>ROUNDUP(D84/30,0)*4</f>
-        <v>5096</v>
-      </c>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
       <c r="F84" s="2"/>
-      <c r="G84" s="8">
-        <f t="shared" ref="G84" si="91">SUM(D84:F84)</f>
-        <v>43299</v>
-      </c>
-      <c r="H84" s="2">
-        <f t="shared" ref="H84" si="92">10%*G84</f>
-        <v>4329.9000000000005</v>
-      </c>
-      <c r="I84" s="2">
-        <v>400</v>
-      </c>
-      <c r="J84" s="2">
-        <f t="shared" ref="J84" si="93">6%*G84</f>
-        <v>2597.94</v>
-      </c>
-      <c r="K84" s="8">
-        <f t="shared" ref="K84" si="94">SUM(G84:J84)</f>
-        <v>50626.840000000004</v>
-      </c>
-      <c r="L84" s="2">
-        <f t="shared" si="80"/>
-        <v>5000</v>
-      </c>
-      <c r="M84" s="2">
-        <f>10%*D84</f>
-        <v>3820.3</v>
-      </c>
+      <c r="G84" s="8"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+      <c r="K84" s="8"/>
+      <c r="L84" s="2"/>
+      <c r="M84" s="2"/>
       <c r="N84" s="2"/>
-      <c r="O84" s="4">
-        <f t="shared" ref="O84" si="95">SUM(L84:M84)</f>
-        <v>8820.2999999999993</v>
-      </c>
-      <c r="P84" s="8">
-        <f t="shared" ref="P84" si="96">K84+O84</f>
-        <v>59447.14</v>
-      </c>
-      <c r="Q84" s="2">
-        <v>800</v>
-      </c>
-      <c r="R84" s="2">
-        <f t="shared" ref="R84" si="97">H84*2</f>
-        <v>8659.8000000000011</v>
-      </c>
-      <c r="S84" s="2">
-        <v>5000</v>
-      </c>
+      <c r="O84" s="4"/>
+      <c r="P84" s="8"/>
+      <c r="Q84" s="2"/>
+      <c r="R84" s="2"/>
+      <c r="S84" s="2"/>
       <c r="T84" s="2"/>
-      <c r="U84" s="2">
-        <f t="shared" ref="U84" si="98">J84*2</f>
-        <v>5195.88</v>
-      </c>
-      <c r="V84" s="4">
-        <f t="shared" ref="V84" si="99">SUM(Q84:U84)</f>
-        <v>19655.68</v>
-      </c>
-      <c r="W84" s="2">
-        <f t="shared" ref="W84" si="100">X84+U84</f>
-        <v>44987.34</v>
-      </c>
-      <c r="X84" s="10">
-        <f t="shared" ref="X84" si="101">P84-V84</f>
-        <v>39791.46</v>
-      </c>
-      <c r="Y84" s="2">
-        <f t="shared" ref="Y84" si="102">IF(X84*13&gt;600000,1%*X84,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z84" s="2">
-        <f t="shared" ref="Z84" si="103">X84-Y84</f>
-        <v>39791.46</v>
-      </c>
+      <c r="U84" s="2"/>
+      <c r="V84" s="2"/>
+      <c r="W84" s="4"/>
+      <c r="X84" s="2"/>
+      <c r="Y84" s="10"/>
+      <c r="Z84" s="2"/>
       <c r="AA84" s="2"/>
       <c r="AB84" s="2"/>
-    </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A85" s="2"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="8"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
-      <c r="K85" s="8"/>
-      <c r="L85" s="2"/>
-      <c r="M85" s="2"/>
-      <c r="N85" s="2"/>
-      <c r="O85" s="4"/>
-      <c r="P85" s="8"/>
-      <c r="Q85" s="2"/>
-      <c r="R85" s="2"/>
-      <c r="S85" s="2"/>
-      <c r="T85" s="2"/>
-      <c r="U85" s="2"/>
-      <c r="V85" s="4"/>
-      <c r="W85" s="2"/>
-      <c r="X85" s="10"/>
-      <c r="Y85" s="2"/>
-      <c r="Z85" s="2"/>
-      <c r="AA85" s="2"/>
-      <c r="AB85" s="2"/>
-    </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC84" s="2"/>
+    </row>
+    <row r="85" spans="1:29" s="27" customFormat="1" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="A85" s="44"/>
+      <c r="B85" s="44"/>
+      <c r="C85" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="D85" s="46">
+        <f>D82-D81</f>
+        <v>0</v>
+      </c>
+      <c r="E85" s="46">
+        <f>E82-E81</f>
+        <v>1158</v>
+      </c>
+      <c r="F85" s="46"/>
+      <c r="G85" s="26">
+        <f>G82-G81</f>
+        <v>1158</v>
+      </c>
+      <c r="H85" s="46">
+        <f>H82-H81</f>
+        <v>115.79999999999973</v>
+      </c>
+      <c r="I85" s="46">
+        <f>I82-I81</f>
+        <v>0</v>
+      </c>
+      <c r="J85" s="46">
+        <f>J82-J81</f>
+        <v>69.480000000000018</v>
+      </c>
+      <c r="K85" s="46">
+        <f>K82-K81</f>
+        <v>1343.2799999999988</v>
+      </c>
+      <c r="L85" s="46">
+        <f>L82-L81</f>
+        <v>0</v>
+      </c>
+      <c r="M85" s="46">
+        <f>M82-M81</f>
+        <v>0</v>
+      </c>
+      <c r="N85" s="46"/>
+      <c r="O85" s="46">
+        <f>O82-O81</f>
+        <v>0</v>
+      </c>
+      <c r="P85" s="46">
+        <f>P82-P81</f>
+        <v>1343.2799999999988</v>
+      </c>
+      <c r="Q85" s="46">
+        <f>Q82-Q81</f>
+        <v>0</v>
+      </c>
+      <c r="R85" s="46">
+        <f>R82-R81</f>
+        <v>231.59999999999945</v>
+      </c>
+      <c r="S85" s="46">
+        <f>S82-S81</f>
+        <v>0</v>
+      </c>
+      <c r="T85" s="46"/>
+      <c r="U85" s="46">
+        <f>U82-U81</f>
+        <v>138.96000000000004</v>
+      </c>
+      <c r="V85" s="46"/>
+      <c r="W85" s="46">
+        <f>W82-W81</f>
+        <v>370.56000000000131</v>
+      </c>
+      <c r="X85" s="46">
+        <f>X82-X81</f>
+        <v>1111.6800000000003</v>
+      </c>
+      <c r="Y85" s="46">
+        <f>Y82-Y81</f>
+        <v>972.71999999999753</v>
+      </c>
+      <c r="Z85" s="46"/>
+      <c r="AA85" s="46">
+        <f>AA82-AA81</f>
+        <v>972.71999999999753</v>
+      </c>
+      <c r="AB85" s="25"/>
+      <c r="AC85" s="24"/>
+    </row>
+    <row r="86" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
-      <c r="D86" s="4">
-        <v>43689</v>
-      </c>
-      <c r="E86" s="4">
-        <v>0</v>
-      </c>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
       <c r="F86" s="2"/>
-      <c r="G86" s="8">
-        <f>SUM(D86:F86)</f>
-        <v>43689</v>
-      </c>
-      <c r="H86" s="2">
-        <f>10%*G86</f>
-        <v>4368.9000000000005</v>
-      </c>
-      <c r="I86" s="2">
-        <v>400</v>
-      </c>
-      <c r="J86" s="2">
-        <f>6%*G86</f>
-        <v>2621.3399999999997</v>
-      </c>
-      <c r="K86" s="8">
-        <f>SUM(G86:J86)</f>
-        <v>51079.24</v>
-      </c>
-      <c r="L86" s="2">
-        <f>2000+3000</f>
-        <v>5000</v>
-      </c>
-      <c r="M86" s="2">
-        <v>0</v>
-      </c>
+      <c r="G86" s="8"/>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="2"/>
+      <c r="M86" s="2"/>
       <c r="N86" s="2"/>
-      <c r="O86" s="4">
-        <f>SUM(L86:M86)</f>
-        <v>5000</v>
-      </c>
-      <c r="P86" s="8">
-        <f>K86+O86</f>
-        <v>56079.24</v>
-      </c>
-      <c r="Q86" s="2">
-        <v>801</v>
-      </c>
-      <c r="R86" s="2">
-        <f>H86*2</f>
-        <v>8737.8000000000011</v>
-      </c>
-      <c r="S86" s="2">
-        <v>1000</v>
-      </c>
+      <c r="O86" s="4"/>
+      <c r="P86" s="8"/>
+      <c r="Q86" s="2"/>
+      <c r="R86" s="2"/>
+      <c r="S86" s="2"/>
       <c r="T86" s="2"/>
-      <c r="U86" s="2">
-        <f>J86*2</f>
-        <v>5242.6799999999994</v>
-      </c>
-      <c r="V86" s="4">
-        <f>SUM(Q86:U86)</f>
-        <v>15781.48</v>
-      </c>
-      <c r="W86" s="2">
-        <f>X86+U86</f>
-        <v>45540.439999999995</v>
-      </c>
-      <c r="X86" s="10">
-        <f>P86-V86</f>
-        <v>40297.759999999995</v>
-      </c>
-      <c r="Y86" s="2">
-        <f>IF(X86*13&gt;600000,1%*X86,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z86" s="2">
-        <f>X86-Y86</f>
-        <v>40297.759999999995</v>
-      </c>
+      <c r="U86" s="2"/>
+      <c r="V86" s="2"/>
+      <c r="W86" s="4"/>
+      <c r="X86" s="2"/>
+      <c r="Y86" s="10"/>
+      <c r="Z86" s="2"/>
       <c r="AA86" s="2"/>
       <c r="AB86" s="2"/>
-    </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A87" s="2"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="8"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="8"/>
-      <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
-      <c r="N87" s="2"/>
-      <c r="O87" s="4"/>
-      <c r="P87" s="8"/>
-      <c r="Q87" s="2"/>
-      <c r="R87" s="2"/>
-      <c r="S87" s="2"/>
-      <c r="T87" s="2"/>
-      <c r="U87" s="2"/>
-      <c r="V87" s="4"/>
-      <c r="W87" s="2"/>
-      <c r="X87" s="10"/>
-      <c r="Y87" s="2"/>
-      <c r="Z87" s="2"/>
-      <c r="AA87" s="2"/>
-      <c r="AB87" s="2"/>
-    </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC86" s="2"/>
+    </row>
+    <row r="87" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="28"/>
+      <c r="B87" s="28"/>
+      <c r="C87" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D87" s="31">
+        <f>34730*1.1</f>
+        <v>38203</v>
+      </c>
+      <c r="E87" s="31">
+        <f>ROUNDDOWN(D87/30,0)*5</f>
+        <v>6365</v>
+      </c>
+      <c r="F87" s="30"/>
+      <c r="G87" s="32">
+        <f t="shared" ref="G87" si="93">SUM(D87:F87)</f>
+        <v>44568</v>
+      </c>
+      <c r="H87" s="30">
+        <f t="shared" ref="H87" si="94">10%*G87</f>
+        <v>4456.8</v>
+      </c>
+      <c r="I87" s="30">
+        <v>400</v>
+      </c>
+      <c r="J87" s="30">
+        <f t="shared" ref="J87" si="95">6%*G87</f>
+        <v>2674.08</v>
+      </c>
+      <c r="K87" s="32">
+        <f t="shared" ref="K87" si="96">SUM(G87:J87)</f>
+        <v>52098.880000000005</v>
+      </c>
+      <c r="L87" s="30">
+        <f t="shared" si="73"/>
+        <v>5000</v>
+      </c>
+      <c r="M87" s="30">
+        <f>10%*D87</f>
+        <v>3820.3</v>
+      </c>
+      <c r="N87" s="30"/>
+      <c r="O87" s="31">
+        <f t="shared" ref="O87" si="97">SUM(L87:M87)</f>
+        <v>8820.2999999999993</v>
+      </c>
+      <c r="P87" s="32">
+        <f t="shared" ref="P87" si="98">K87+O87</f>
+        <v>60919.180000000008</v>
+      </c>
+      <c r="Q87" s="30">
+        <v>800</v>
+      </c>
+      <c r="R87" s="30">
+        <f t="shared" ref="R87" si="99">H87*2</f>
+        <v>8913.6</v>
+      </c>
+      <c r="S87" s="30">
+        <v>5000</v>
+      </c>
+      <c r="T87" s="30"/>
+      <c r="U87" s="30">
+        <f t="shared" ref="U87" si="100">J87*2</f>
+        <v>5348.16</v>
+      </c>
+      <c r="V87" s="30"/>
+      <c r="W87" s="31">
+        <f t="shared" ref="W87" si="101">SUM(Q87:U87)</f>
+        <v>20061.760000000002</v>
+      </c>
+      <c r="X87" s="30">
+        <f>Y87+U87</f>
+        <v>46205.58</v>
+      </c>
+      <c r="Y87" s="33">
+        <f>P87-W87</f>
+        <v>40857.420000000006</v>
+      </c>
+      <c r="Z87" s="30"/>
+      <c r="AA87" s="30">
+        <f t="shared" ref="AA87" si="102">Y87-Z87</f>
+        <v>40857.420000000006</v>
+      </c>
+      <c r="AB87" s="30"/>
+      <c r="AC87" s="30"/>
+    </row>
+    <row r="88" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="8"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="8"/>
-      <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
-      <c r="N88" s="2"/>
-      <c r="O88" s="4"/>
-      <c r="P88" s="8"/>
-      <c r="Q88" s="2"/>
-      <c r="R88" s="2"/>
-      <c r="S88" s="2"/>
-      <c r="T88" s="2"/>
-      <c r="U88" s="2"/>
-      <c r="V88" s="4"/>
-      <c r="W88" s="2"/>
-      <c r="X88" s="8">
-        <f>SUM(X3:X81)</f>
-        <v>2186834.9200000013</v>
-      </c>
-      <c r="Y88" s="2"/>
-      <c r="Z88" s="2"/>
-      <c r="AA88" s="2"/>
+      <c r="C88" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="D88" s="35">
+        <f>D87-D85</f>
+        <v>38203</v>
+      </c>
+      <c r="E88" s="35">
+        <f t="shared" ref="E88:AA88" si="103">E87-E85</f>
+        <v>5207</v>
+      </c>
+      <c r="F88" s="35"/>
+      <c r="G88" s="41">
+        <f t="shared" si="103"/>
+        <v>43410</v>
+      </c>
+      <c r="H88" s="35">
+        <f t="shared" si="103"/>
+        <v>4341</v>
+      </c>
+      <c r="I88" s="35">
+        <f t="shared" si="103"/>
+        <v>400</v>
+      </c>
+      <c r="J88" s="35">
+        <f t="shared" si="103"/>
+        <v>2604.6</v>
+      </c>
+      <c r="K88" s="35">
+        <f t="shared" si="103"/>
+        <v>50755.600000000006</v>
+      </c>
+      <c r="L88" s="35">
+        <f t="shared" si="103"/>
+        <v>5000</v>
+      </c>
+      <c r="M88" s="35">
+        <f t="shared" si="103"/>
+        <v>3820.3</v>
+      </c>
+      <c r="N88" s="35"/>
+      <c r="O88" s="35">
+        <f t="shared" si="103"/>
+        <v>8820.2999999999993</v>
+      </c>
+      <c r="P88" s="35">
+        <f t="shared" si="103"/>
+        <v>59575.900000000009</v>
+      </c>
+      <c r="Q88" s="35">
+        <f t="shared" si="103"/>
+        <v>800</v>
+      </c>
+      <c r="R88" s="35">
+        <f t="shared" si="103"/>
+        <v>8682</v>
+      </c>
+      <c r="S88" s="35">
+        <f t="shared" si="103"/>
+        <v>5000</v>
+      </c>
+      <c r="T88" s="35"/>
+      <c r="U88" s="35">
+        <f t="shared" si="103"/>
+        <v>5209.2</v>
+      </c>
+      <c r="V88" s="35"/>
+      <c r="W88" s="35">
+        <f t="shared" si="103"/>
+        <v>19691.2</v>
+      </c>
+      <c r="X88" s="35">
+        <f t="shared" si="103"/>
+        <v>45093.9</v>
+      </c>
+      <c r="Y88" s="35">
+        <f t="shared" si="103"/>
+        <v>39884.700000000012</v>
+      </c>
+      <c r="Z88" s="35"/>
+      <c r="AA88" s="35">
+        <f t="shared" si="103"/>
+        <v>39884.700000000012</v>
+      </c>
       <c r="AB88" s="2"/>
-    </row>
-    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="8"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="8"/>
-      <c r="L89" s="2"/>
-      <c r="M89" s="2"/>
-      <c r="N89" s="2"/>
-      <c r="O89" s="4"/>
-      <c r="P89" s="8"/>
-      <c r="Q89" s="2"/>
-      <c r="R89" s="2"/>
-      <c r="S89" s="2"/>
-      <c r="T89" s="2"/>
-      <c r="U89" s="2"/>
-      <c r="V89" s="4"/>
-      <c r="W89" s="2"/>
-      <c r="X89" s="8">
-        <f>0.7*X88</f>
-        <v>1530784.4440000008</v>
-      </c>
-      <c r="Y89" s="2"/>
-      <c r="Z89" s="2"/>
-      <c r="AA89" s="2"/>
-      <c r="AB89" s="2"/>
-    </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC88" s="2"/>
+    </row>
+    <row r="89" spans="1:29" s="21" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A89" s="19"/>
+      <c r="B89" s="19"/>
+      <c r="C89" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="D89" s="20">
+        <f>D88-E85</f>
+        <v>37045</v>
+      </c>
+      <c r="E89" s="20">
+        <v>5092</v>
+      </c>
+      <c r="F89" s="20"/>
+      <c r="G89" s="38">
+        <f t="shared" ref="G89" si="104">SUM(D89:F89)</f>
+        <v>42137</v>
+      </c>
+      <c r="H89" s="19">
+        <f t="shared" ref="H89" si="105">10%*G89</f>
+        <v>4213.7</v>
+      </c>
+      <c r="I89" s="19">
+        <v>400</v>
+      </c>
+      <c r="J89" s="39">
+        <f t="shared" ref="J89" si="106">6%*G89</f>
+        <v>2528.2199999999998</v>
+      </c>
+      <c r="K89" s="22">
+        <f t="shared" ref="K89" si="107">SUM(G89:J89)</f>
+        <v>49278.92</v>
+      </c>
+      <c r="L89" s="19">
+        <f t="shared" si="73"/>
+        <v>5000</v>
+      </c>
+      <c r="M89" s="19">
+        <f>10%*D89</f>
+        <v>3704.5</v>
+      </c>
+      <c r="N89" s="19"/>
+      <c r="O89" s="20">
+        <f t="shared" ref="O89" si="108">SUM(L89:M89)</f>
+        <v>8704.5</v>
+      </c>
+      <c r="P89" s="22">
+        <f t="shared" ref="P89" si="109">K89+O89</f>
+        <v>57983.42</v>
+      </c>
+      <c r="Q89" s="19">
+        <v>800</v>
+      </c>
+      <c r="R89" s="19">
+        <f t="shared" ref="R89" si="110">H89*2</f>
+        <v>8427.4</v>
+      </c>
+      <c r="S89" s="19">
+        <v>5000</v>
+      </c>
+      <c r="T89" s="19"/>
+      <c r="U89" s="19">
+        <f t="shared" ref="U89" si="111">J89*2</f>
+        <v>5056.4399999999996</v>
+      </c>
+      <c r="V89" s="19"/>
+      <c r="W89" s="20">
+        <f t="shared" ref="W89" si="112">SUM(Q89:U89)</f>
+        <v>19283.84</v>
+      </c>
+      <c r="X89" s="19">
+        <f>Y89+U89</f>
+        <v>43756.020000000004</v>
+      </c>
+      <c r="Y89" s="23">
+        <f>P89-W89</f>
+        <v>38699.58</v>
+      </c>
+      <c r="Z89" s="19"/>
+      <c r="AA89" s="19">
+        <f t="shared" ref="AA89" si="113">Y89-Z89</f>
+        <v>38699.58</v>
+      </c>
+      <c r="AB89" s="19"/>
+      <c r="AC89" s="19"/>
+    </row>
+    <row r="90" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
+      <c r="D90" s="4">
+        <f>34730*1.1</f>
+        <v>38203</v>
+      </c>
+      <c r="E90" s="18">
+        <f>ROUNDDOWN(D90/30,0)*5</f>
+        <v>6365</v>
+      </c>
       <c r="F90" s="2"/>
-      <c r="G90" s="8"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="8"/>
-      <c r="L90" s="2"/>
-      <c r="M90" s="2"/>
+      <c r="G90" s="8">
+        <f t="shared" ref="G90" si="114">SUM(D90:F90)</f>
+        <v>44568</v>
+      </c>
+      <c r="H90" s="2">
+        <f t="shared" ref="H90" si="115">10%*G90</f>
+        <v>4456.8</v>
+      </c>
+      <c r="I90" s="2">
+        <v>400</v>
+      </c>
+      <c r="J90" s="13">
+        <f t="shared" ref="J90" si="116">6%*G90</f>
+        <v>2674.08</v>
+      </c>
+      <c r="K90" s="14">
+        <f t="shared" ref="K90" si="117">SUM(G90:J90)</f>
+        <v>52098.880000000005</v>
+      </c>
+      <c r="L90" s="2">
+        <f t="shared" si="73"/>
+        <v>5000</v>
+      </c>
+      <c r="M90" s="2">
+        <f>10%*D90</f>
+        <v>3820.3</v>
+      </c>
       <c r="N90" s="2"/>
-      <c r="O90" s="4"/>
-      <c r="P90" s="8"/>
-      <c r="Q90" s="2"/>
-      <c r="R90" s="2"/>
-      <c r="S90" s="2"/>
+      <c r="O90" s="4">
+        <f t="shared" ref="O90" si="118">SUM(L90:M90)</f>
+        <v>8820.2999999999993</v>
+      </c>
+      <c r="P90" s="8">
+        <f t="shared" ref="P90" si="119">K90+O90</f>
+        <v>60919.180000000008</v>
+      </c>
+      <c r="Q90" s="2">
+        <v>800</v>
+      </c>
+      <c r="R90" s="2">
+        <f t="shared" ref="R90" si="120">H90*2</f>
+        <v>8913.6</v>
+      </c>
+      <c r="S90" s="2">
+        <v>5000</v>
+      </c>
       <c r="T90" s="2"/>
-      <c r="U90" s="2"/>
-      <c r="V90" s="4"/>
-      <c r="W90" s="2"/>
-      <c r="X90" s="10"/>
-      <c r="Y90" s="2"/>
+      <c r="U90" s="2">
+        <f t="shared" ref="U90" si="121">J90*2</f>
+        <v>5348.16</v>
+      </c>
+      <c r="V90" s="12">
+        <f>ROUND(D90/30,1)*5</f>
+        <v>6367</v>
+      </c>
+      <c r="W90" s="4">
+        <f>SUM(Q90:V90)</f>
+        <v>26428.760000000002</v>
+      </c>
+      <c r="X90" s="2">
+        <f>Y90+U90</f>
+        <v>39838.58</v>
+      </c>
+      <c r="Y90" s="10">
+        <f>P90-W90</f>
+        <v>34490.420000000006</v>
+      </c>
       <c r="Z90" s="2"/>
-      <c r="AA90" s="2"/>
+      <c r="AA90" s="2">
+        <f t="shared" ref="AA90" si="122">Y90-Z90</f>
+        <v>34490.420000000006</v>
+      </c>
       <c r="AB90" s="2"/>
-    </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC90" s="2"/>
+    </row>
+    <row r="91" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -10410,75 +11072,188 @@
       <c r="S91" s="2"/>
       <c r="T91" s="2"/>
       <c r="U91" s="2"/>
-      <c r="V91" s="4"/>
-      <c r="W91" s="2"/>
-      <c r="X91" s="10"/>
-      <c r="Y91" s="2"/>
+      <c r="V91" s="2"/>
+      <c r="W91" s="4"/>
+      <c r="X91" s="2"/>
+      <c r="Y91" s="10"/>
       <c r="Z91" s="2"/>
       <c r="AA91" s="2"/>
       <c r="AB91" s="2"/>
-    </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC91" s="2"/>
+    </row>
+    <row r="92" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
+      <c r="D92" s="4">
+        <v>43689</v>
+      </c>
+      <c r="E92" s="4">
+        <v>0</v>
+      </c>
       <c r="F92" s="2"/>
-      <c r="G92" s="8"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="8"/>
-      <c r="L92" s="2"/>
-      <c r="M92" s="2"/>
+      <c r="G92" s="8">
+        <f>SUM(D92:F92)</f>
+        <v>43689</v>
+      </c>
+      <c r="H92" s="2">
+        <f>10%*G92</f>
+        <v>4368.9000000000005</v>
+      </c>
+      <c r="I92" s="2">
+        <v>400</v>
+      </c>
+      <c r="J92" s="2">
+        <f>6%*G92</f>
+        <v>2621.3399999999997</v>
+      </c>
+      <c r="K92" s="8">
+        <f>SUM(G92:J92)</f>
+        <v>51079.24</v>
+      </c>
+      <c r="L92" s="2">
+        <f>2000+3000</f>
+        <v>5000</v>
+      </c>
+      <c r="M92" s="2">
+        <v>0</v>
+      </c>
       <c r="N92" s="2"/>
-      <c r="O92" s="4"/>
-      <c r="P92" s="8"/>
-      <c r="Q92" s="2"/>
-      <c r="R92" s="2"/>
-      <c r="S92" s="2"/>
+      <c r="O92" s="4">
+        <f>SUM(L92:M92)</f>
+        <v>5000</v>
+      </c>
+      <c r="P92" s="8">
+        <f>K92+O92</f>
+        <v>56079.24</v>
+      </c>
+      <c r="Q92" s="2">
+        <v>801</v>
+      </c>
+      <c r="R92" s="2">
+        <f>H92*2</f>
+        <v>8737.8000000000011</v>
+      </c>
+      <c r="S92" s="2">
+        <v>1000</v>
+      </c>
       <c r="T92" s="2"/>
-      <c r="U92" s="2"/>
-      <c r="V92" s="4"/>
-      <c r="W92" s="2"/>
-      <c r="X92" s="10"/>
-      <c r="Y92" s="2"/>
+      <c r="U92" s="2">
+        <f>J92*2</f>
+        <v>5242.6799999999994</v>
+      </c>
+      <c r="V92" s="2"/>
+      <c r="W92" s="4">
+        <f>SUM(Q92:U92)</f>
+        <v>15781.48</v>
+      </c>
+      <c r="X92" s="2">
+        <f>Y92+U92</f>
+        <v>45540.439999999995</v>
+      </c>
+      <c r="Y92" s="10">
+        <f>P92-W92</f>
+        <v>40297.759999999995</v>
+      </c>
       <c r="Z92" s="2"/>
-      <c r="AA92" s="2"/>
+      <c r="AA92" s="2">
+        <f>Y92-Z92</f>
+        <v>40297.759999999995</v>
+      </c>
       <c r="AB92" s="2"/>
-    </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="8"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="8"/>
-      <c r="L93" s="2"/>
-      <c r="M93" s="2"/>
-      <c r="N93" s="2"/>
-      <c r="O93" s="4"/>
-      <c r="P93" s="8"/>
-      <c r="Q93" s="2"/>
-      <c r="R93" s="2"/>
-      <c r="S93" s="2"/>
-      <c r="T93" s="2"/>
-      <c r="U93" s="2"/>
-      <c r="V93" s="4"/>
-      <c r="W93" s="2"/>
-      <c r="X93" s="10"/>
-      <c r="Y93" s="2"/>
-      <c r="Z93" s="2"/>
-      <c r="AA93" s="2"/>
-      <c r="AB93" s="2"/>
-    </row>
-    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC92" s="2"/>
+    </row>
+    <row r="93" spans="1:29" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="24"/>
+      <c r="B93" s="24"/>
+      <c r="C93" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="D93" s="25">
+        <f>D89-D88</f>
+        <v>-1158</v>
+      </c>
+      <c r="E93" s="25">
+        <f t="shared" ref="E93:AA93" si="123">E89-E88</f>
+        <v>-115</v>
+      </c>
+      <c r="F93" s="25"/>
+      <c r="G93" s="26">
+        <f t="shared" si="123"/>
+        <v>-1273</v>
+      </c>
+      <c r="H93" s="25">
+        <f t="shared" si="123"/>
+        <v>-127.30000000000018</v>
+      </c>
+      <c r="I93" s="25">
+        <f t="shared" si="123"/>
+        <v>0</v>
+      </c>
+      <c r="J93" s="25">
+        <f t="shared" si="123"/>
+        <v>-76.380000000000109</v>
+      </c>
+      <c r="K93" s="25">
+        <f t="shared" si="123"/>
+        <v>-1476.6800000000076</v>
+      </c>
+      <c r="L93" s="25">
+        <f t="shared" si="123"/>
+        <v>0</v>
+      </c>
+      <c r="M93" s="25">
+        <f t="shared" si="123"/>
+        <v>-115.80000000000018</v>
+      </c>
+      <c r="N93" s="25"/>
+      <c r="O93" s="25">
+        <f t="shared" si="123"/>
+        <v>-115.79999999999927</v>
+      </c>
+      <c r="P93" s="25">
+        <f t="shared" si="123"/>
+        <v>-1592.4800000000105</v>
+      </c>
+      <c r="Q93" s="25">
+        <f t="shared" si="123"/>
+        <v>0</v>
+      </c>
+      <c r="R93" s="25">
+        <f t="shared" si="123"/>
+        <v>-254.60000000000036</v>
+      </c>
+      <c r="S93" s="25">
+        <f t="shared" si="123"/>
+        <v>0</v>
+      </c>
+      <c r="T93" s="25"/>
+      <c r="U93" s="25">
+        <f t="shared" si="123"/>
+        <v>-152.76000000000022</v>
+      </c>
+      <c r="V93" s="25"/>
+      <c r="W93" s="25">
+        <f t="shared" si="123"/>
+        <v>-407.36000000000058</v>
+      </c>
+      <c r="X93" s="25">
+        <f t="shared" si="123"/>
+        <v>-1337.8799999999974</v>
+      </c>
+      <c r="Y93" s="25">
+        <f t="shared" si="123"/>
+        <v>-1185.1200000000099</v>
+      </c>
+      <c r="Z93" s="25"/>
+      <c r="AA93" s="25">
+        <f t="shared" si="123"/>
+        <v>-1185.1200000000099</v>
+      </c>
+      <c r="AB93" s="25"/>
+      <c r="AC93" s="24"/>
+    </row>
+    <row r="94" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -10500,15 +11275,19 @@
       <c r="S94" s="2"/>
       <c r="T94" s="2"/>
       <c r="U94" s="2"/>
-      <c r="V94" s="4"/>
-      <c r="W94" s="2"/>
-      <c r="X94" s="10"/>
-      <c r="Y94" s="2"/>
+      <c r="V94" s="2"/>
+      <c r="W94" s="4"/>
+      <c r="X94" s="2"/>
+      <c r="Y94" s="8">
+        <f>SUM(Y3:Y82)</f>
+        <v>2215608.120000001</v>
+      </c>
       <c r="Z94" s="2"/>
       <c r="AA94" s="2"/>
       <c r="AB94" s="2"/>
-    </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC94" s="2"/>
+    </row>
+    <row r="95" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -10530,15 +11309,16 @@
       <c r="S95" s="2"/>
       <c r="T95" s="2"/>
       <c r="U95" s="2"/>
-      <c r="V95" s="4"/>
-      <c r="W95" s="2"/>
-      <c r="X95" s="10"/>
-      <c r="Y95" s="2"/>
+      <c r="V95" s="2"/>
+      <c r="W95" s="4"/>
+      <c r="X95" s="2"/>
+      <c r="Y95" s="10"/>
       <c r="Z95" s="2"/>
       <c r="AA95" s="2"/>
       <c r="AB95" s="2"/>
-    </row>
-    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC95" s="2"/>
+    </row>
+    <row r="96" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -10560,33 +11340,189 @@
       <c r="S96" s="2"/>
       <c r="T96" s="2"/>
       <c r="U96" s="2"/>
-      <c r="V96" s="4"/>
-      <c r="W96" s="2"/>
-      <c r="X96" s="10"/>
-      <c r="Y96" s="2"/>
+      <c r="V96" s="2"/>
+      <c r="W96" s="4"/>
+      <c r="X96" s="2"/>
+      <c r="Y96" s="10"/>
       <c r="Z96" s="2"/>
       <c r="AA96" s="2"/>
       <c r="AB96" s="2"/>
+      <c r="AC96" s="2"/>
+    </row>
+    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="4"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
+      <c r="K97" s="8"/>
+      <c r="L97" s="2"/>
+      <c r="M97" s="2"/>
+      <c r="N97" s="2"/>
+      <c r="O97" s="4"/>
+      <c r="P97" s="8"/>
+      <c r="Q97" s="2"/>
+      <c r="R97" s="2"/>
+      <c r="S97" s="2"/>
+      <c r="T97" s="2"/>
+      <c r="U97" s="2"/>
+      <c r="V97" s="2"/>
+      <c r="W97" s="4"/>
+      <c r="X97" s="2"/>
+      <c r="Y97" s="10"/>
+      <c r="Z97" s="2"/>
+      <c r="AA97" s="2"/>
+      <c r="AB97" s="2"/>
+      <c r="AC97" s="2"/>
+    </row>
+    <row r="98" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="4"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="8"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+      <c r="K98" s="8"/>
+      <c r="L98" s="2"/>
+      <c r="M98" s="2"/>
+      <c r="N98" s="2"/>
+      <c r="O98" s="4"/>
+      <c r="P98" s="8"/>
+      <c r="Q98" s="2"/>
+      <c r="R98" s="2"/>
+      <c r="S98" s="2"/>
+      <c r="T98" s="2"/>
+      <c r="U98" s="2"/>
+      <c r="V98" s="2"/>
+      <c r="W98" s="4"/>
+      <c r="X98" s="2"/>
+      <c r="Y98" s="10"/>
+      <c r="Z98" s="2"/>
+      <c r="AA98" s="2"/>
+      <c r="AB98" s="2"/>
+      <c r="AC98" s="2"/>
+    </row>
+    <row r="99" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="8"/>
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="2"/>
+      <c r="K99" s="8"/>
+      <c r="L99" s="2"/>
+      <c r="M99" s="2"/>
+      <c r="N99" s="2"/>
+      <c r="O99" s="4"/>
+      <c r="P99" s="8"/>
+      <c r="Q99" s="2"/>
+      <c r="R99" s="2"/>
+      <c r="S99" s="2"/>
+      <c r="T99" s="2"/>
+      <c r="U99" s="2"/>
+      <c r="V99" s="2"/>
+      <c r="W99" s="4"/>
+      <c r="X99" s="2"/>
+      <c r="Y99" s="10"/>
+      <c r="Z99" s="2"/>
+      <c r="AA99" s="2"/>
+      <c r="AB99" s="2"/>
+      <c r="AC99" s="2"/>
+    </row>
+    <row r="100" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+      <c r="K100" s="8"/>
+      <c r="L100" s="2"/>
+      <c r="M100" s="2"/>
+      <c r="N100" s="2"/>
+      <c r="O100" s="4"/>
+      <c r="P100" s="8"/>
+      <c r="Q100" s="2"/>
+      <c r="R100" s="2"/>
+      <c r="S100" s="2"/>
+      <c r="T100" s="2"/>
+      <c r="U100" s="2"/>
+      <c r="V100" s="2"/>
+      <c r="W100" s="4"/>
+      <c r="X100" s="2"/>
+      <c r="Y100" s="10"/>
+      <c r="Z100" s="2"/>
+      <c r="AA100" s="2"/>
+      <c r="AB100" s="2"/>
+      <c r="AC100" s="2"/>
+    </row>
+    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="8"/>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="2"/>
+      <c r="K101" s="8"/>
+      <c r="L101" s="2"/>
+      <c r="M101" s="2"/>
+      <c r="N101" s="2"/>
+      <c r="O101" s="4"/>
+      <c r="P101" s="8"/>
+      <c r="Q101" s="2"/>
+      <c r="R101" s="2"/>
+      <c r="S101" s="2"/>
+      <c r="T101" s="2"/>
+      <c r="U101" s="2"/>
+      <c r="V101" s="2"/>
+      <c r="W101" s="4"/>
+      <c r="X101" s="2"/>
+      <c r="Y101" s="10"/>
+      <c r="Z101" s="2"/>
+      <c r="AA101" s="2"/>
+      <c r="AB101" s="2"/>
+      <c r="AC101" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="AA1:AA2"/>
     <mergeCell ref="AB1:AB2"/>
+    <mergeCell ref="AC1:AC2"/>
     <mergeCell ref="P1:P2"/>
-    <mergeCell ref="Q1:V1"/>
-    <mergeCell ref="W1:W2"/>
+    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="X1:X2"/>
     <mergeCell ref="Y1:Y2"/>
     <mergeCell ref="Z1:Z2"/>
+    <mergeCell ref="AA1:AA2"/>
+    <mergeCell ref="L1:O1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="H1:K1"/>
-    <mergeCell ref="L1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="59" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/New Microsoft Excel Worksheet.xlsx
+++ b/New Microsoft Excel Worksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708B4B88-7CA8-446F-AB58-A8FE1D30A08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A18DF91-9997-4D9A-8553-BD2A17C3DE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -371,6 +371,54 @@
           </rPr>
           <t xml:space="preserve">
 From shrawan</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D18" authorId="1" shapeId="0" xr:uid="{A8704AFB-8DCA-4627-B43C-BEDAF3D78001}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>DELL:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+From Ashwin</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M18" authorId="0" shapeId="0" xr:uid="{CCBE993C-0077-4499-A14D-993908A9E603}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Dashain bonus</t>
         </r>
       </text>
     </comment>
@@ -1650,15 +1698,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1694,6 +1733,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1979,7 +2027,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB29"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
@@ -1995,83 +2043,85 @@
     <col min="11" max="11" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7" style="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.5703125" style="9" customWidth="1"/>
-    <col min="17" max="17" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9" style="5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8" customWidth="1"/>
-    <col min="24" max="24" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.85546875" customWidth="1"/>
-    <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.140625" customWidth="1"/>
+    <col min="14" max="14" width="7" customWidth="1"/>
+    <col min="15" max="15" width="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5703125" style="9" customWidth="1"/>
+    <col min="18" max="18" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9" style="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8" customWidth="1"/>
+    <col min="25" max="25" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.7109375" customWidth="1"/>
+    <col min="28" max="28" width="6" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16" t="s">
+    <row r="1" spans="1:29" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15" t="s">
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15" t="s">
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="17" t="s">
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="R1" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="16" t="s">
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="X1" s="17" t="s">
+      <c r="Y1" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="16" t="s">
+      <c r="Z1" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="16" t="s">
+      <c r="AA1" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="16" t="s">
+      <c r="AB1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="AB1" s="16" t="s">
+      <c r="AC1" s="44" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:28" s="6" customFormat="1" ht="71.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
+    <row r="2" spans="1:29" s="6" customFormat="1" ht="71.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
       <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
@@ -2102,39 +2152,40 @@
       <c r="M2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="3"/>
+      <c r="O2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="45"/>
+      <c r="R2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="W2" s="16"/>
-      <c r="X2" s="17"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="X2" s="44"/>
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="44"/>
+      <c r="AA2" s="44"/>
+      <c r="AB2" s="44"/>
+      <c r="AC2" s="44"/>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2172,53 +2223,54 @@
         <v>0</v>
       </c>
       <c r="N3" s="2"/>
-      <c r="O3" s="4">
+      <c r="O3" s="2"/>
+      <c r="P3" s="4">
         <f>SUM(L3:M3)</f>
         <v>2000</v>
       </c>
-      <c r="P3" s="8">
-        <f>K3+O3</f>
+      <c r="Q3" s="8">
+        <f>K3+P3</f>
         <v>45656.4</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="R3" s="2">
         <v>800</v>
       </c>
-      <c r="R3" s="2">
+      <c r="S3" s="2">
         <f>H3*2</f>
         <v>7458</v>
       </c>
-      <c r="S3" s="2">
-        <v>5000</v>
-      </c>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2">
+      <c r="T3" s="2">
+        <v>5000</v>
+      </c>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2">
         <f>J3*2</f>
         <v>4474.8</v>
       </c>
-      <c r="V3" s="4">
-        <f>SUM(Q3:U3)</f>
+      <c r="W3" s="4">
+        <f>SUM(R3:V3)</f>
         <v>17732.8</v>
       </c>
-      <c r="W3" s="2">
-        <f>X3+U3</f>
+      <c r="X3" s="2">
+        <f>Y3+V3</f>
         <v>32398.400000000001</v>
       </c>
-      <c r="X3" s="10">
-        <f>P3-V3</f>
+      <c r="Y3" s="10">
+        <f>Q3-W3</f>
         <v>27923.600000000002</v>
       </c>
-      <c r="Y3" s="2">
-        <f>IF(X3*13&gt;600000,1%*X3,0)</f>
-        <v>0</v>
-      </c>
       <c r="Z3" s="2">
-        <f>X3-Y3</f>
+        <f>IF(Y3*13&gt;600000,1%*Y3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2">
+        <f>Y3-Z3</f>
         <v>27923.600000000002</v>
       </c>
-      <c r="AA3" s="2"/>
       <c r="AB3" s="2"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC3" s="2"/>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2258,53 +2310,54 @@
         <v>39362</v>
       </c>
       <c r="N4" s="2"/>
-      <c r="O4" s="4">
+      <c r="O4" s="2"/>
+      <c r="P4" s="4">
         <f>SUM(L4:M4)</f>
         <v>44362</v>
       </c>
-      <c r="P4" s="8">
-        <f>K4+O4</f>
+      <c r="Q4" s="8">
+        <f>K4+P4</f>
         <v>90421.92</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="R4" s="2">
         <v>800</v>
       </c>
-      <c r="R4" s="2">
+      <c r="S4" s="2">
         <f>H4*2</f>
         <v>7872.4000000000005</v>
       </c>
-      <c r="S4" s="2">
-        <v>5000</v>
-      </c>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2">
+      <c r="T4" s="2">
+        <v>5000</v>
+      </c>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2">
         <f>J4*2</f>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V4" s="4">
-        <f>SUM(Q4:U4)</f>
+      <c r="W4" s="4">
+        <f>SUM(R4:V4)</f>
         <v>18395.84</v>
       </c>
-      <c r="W4" s="2">
-        <f>X4+U4</f>
+      <c r="X4" s="2">
+        <f>Y4+V4</f>
         <v>76749.52</v>
       </c>
-      <c r="X4" s="10">
-        <f>P4-V4</f>
+      <c r="Y4" s="10">
+        <f>Q4-W4</f>
         <v>72026.080000000002</v>
       </c>
-      <c r="Y4" s="12">
-        <f>IF(X4*13&gt;600000,1%*X4,0)</f>
+      <c r="Z4" s="12">
+        <f>IF(Y4*13&gt;600000,1%*Y4,0)</f>
         <v>720.26080000000002</v>
       </c>
-      <c r="Z4" s="12">
-        <f>X4-Y4</f>
+      <c r="AA4" s="12">
+        <f>Y4-Z4</f>
         <v>71305.819199999998</v>
       </c>
-      <c r="AA4" s="2"/>
       <c r="AB4" s="2"/>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC4" s="2"/>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2343,53 +2396,54 @@
         <v>0</v>
       </c>
       <c r="N5" s="2"/>
-      <c r="O5" s="4">
+      <c r="O5" s="2"/>
+      <c r="P5" s="4">
         <f>SUM(L5:M5)</f>
         <v>5000</v>
       </c>
-      <c r="P5" s="8">
-        <f>K5+O5</f>
+      <c r="Q5" s="8">
+        <f>K5+P5</f>
         <v>51059.92</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="R5" s="2">
         <v>800</v>
       </c>
-      <c r="R5" s="2">
+      <c r="S5" s="2">
         <f>H5*2</f>
         <v>7872.4000000000005</v>
       </c>
-      <c r="S5" s="2">
-        <v>5000</v>
-      </c>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2">
+      <c r="T5" s="2">
+        <v>5000</v>
+      </c>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2">
         <f>J5*2</f>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V5" s="4">
-        <f>SUM(Q5:U5)</f>
+      <c r="W5" s="4">
+        <f>SUM(R5:V5)</f>
         <v>18395.84</v>
       </c>
-      <c r="W5" s="2">
-        <f>X5+U5</f>
+      <c r="X5" s="2">
+        <f>Y5+V5</f>
         <v>37387.519999999997</v>
       </c>
-      <c r="X5" s="10">
-        <f>P5-V5</f>
+      <c r="Y5" s="10">
+        <f>Q5-W5</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="Y5" s="2">
-        <f>IF(X5*13&gt;600000,1%*X5,0)</f>
-        <v>0</v>
-      </c>
       <c r="Z5" s="2">
-        <f>X5-Y5</f>
+        <f>IF(Y5*13&gt;600000,1%*Y5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA5" s="2">
+        <f>Y5-Z5</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="AA5" s="2"/>
       <c r="AB5" s="2"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC5" s="2"/>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -2428,53 +2482,54 @@
         <v>0</v>
       </c>
       <c r="N6" s="2"/>
-      <c r="O6" s="4">
+      <c r="O6" s="2"/>
+      <c r="P6" s="4">
         <f>SUM(L6:M6)</f>
         <v>5000</v>
       </c>
-      <c r="P6" s="8">
-        <f>K6+O6</f>
+      <c r="Q6" s="8">
+        <f>K6+P6</f>
         <v>51059.92</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="R6" s="2">
         <v>800</v>
       </c>
-      <c r="R6" s="2">
+      <c r="S6" s="2">
         <f>H6*2</f>
         <v>7872.4000000000005</v>
       </c>
-      <c r="S6" s="2">
-        <v>5000</v>
-      </c>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2">
+      <c r="T6" s="2">
+        <v>5000</v>
+      </c>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2">
         <f>J6*2</f>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V6" s="4">
-        <f>SUM(Q6:U6)</f>
+      <c r="W6" s="4">
+        <f>SUM(R6:V6)</f>
         <v>18395.84</v>
       </c>
-      <c r="W6" s="2">
-        <f>X6+U6</f>
+      <c r="X6" s="2">
+        <f>Y6+V6</f>
         <v>37387.519999999997</v>
       </c>
-      <c r="X6" s="10">
-        <f>P6-V6</f>
+      <c r="Y6" s="10">
+        <f>Q6-W6</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="Y6" s="2">
-        <f>IF(X6*13&gt;600000,1%*X6,0)</f>
-        <v>0</v>
-      </c>
       <c r="Z6" s="2">
-        <f>X6-Y6</f>
+        <f>IF(Y6*13&gt;600000,1%*Y6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="2">
+        <f>Y6-Z6</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC6" s="2"/>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -2513,53 +2568,54 @@
         <v>0</v>
       </c>
       <c r="N7" s="2"/>
-      <c r="O7" s="4">
+      <c r="O7" s="2"/>
+      <c r="P7" s="4">
         <f>SUM(L7:M7)</f>
         <v>5000</v>
       </c>
-      <c r="P7" s="8">
-        <f>K7+O7</f>
+      <c r="Q7" s="8">
+        <f>K7+P7</f>
         <v>51059.92</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>800</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <f>H7*2</f>
         <v>7872.4000000000005</v>
       </c>
-      <c r="S7" s="2">
-        <v>5000</v>
-      </c>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2">
+      <c r="T7" s="2">
+        <v>5000</v>
+      </c>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2">
         <f>J7*2</f>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V7" s="4">
-        <f>SUM(Q7:U7)</f>
+      <c r="W7" s="4">
+        <f>SUM(R7:V7)</f>
         <v>18395.84</v>
       </c>
-      <c r="W7" s="2">
-        <f>X7+U7</f>
+      <c r="X7" s="2">
+        <f>Y7+V7</f>
         <v>37387.519999999997</v>
       </c>
-      <c r="X7" s="10">
-        <f>P7-V7</f>
+      <c r="Y7" s="10">
+        <f>Q7-W7</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="Y7" s="2">
-        <f>IF(X7*13&gt;600000,1%*X7,0)</f>
-        <v>0</v>
-      </c>
       <c r="Z7" s="2">
-        <f>X7-Y7</f>
+        <f>IF(Y7*13&gt;600000,1%*Y7,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA7" s="2">
+        <f>Y7-Z7</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="AA7" s="2"/>
       <c r="AB7" s="2"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC7" s="2"/>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -2591,60 +2647,61 @@
         <v>46059.92</v>
       </c>
       <c r="L8" s="2">
-        <f t="shared" ref="L8:L17" si="5">2000+3000</f>
+        <f t="shared" ref="L8:L18" si="5">2000+3000</f>
         <v>5000</v>
       </c>
       <c r="M8" s="2">
         <v>0</v>
       </c>
       <c r="N8" s="2"/>
-      <c r="O8" s="4">
-        <f t="shared" ref="O8:O10" si="6">SUM(L8:M8)</f>
-        <v>5000</v>
-      </c>
-      <c r="P8" s="8">
-        <f t="shared" ref="P8:P10" si="7">K8+O8</f>
+      <c r="O8" s="2"/>
+      <c r="P8" s="4">
+        <f t="shared" ref="P8:P10" si="6">SUM(L8:M8)</f>
+        <v>5000</v>
+      </c>
+      <c r="Q8" s="8">
+        <f t="shared" ref="Q8:Q10" si="7">K8+P8</f>
         <v>51059.92</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="R8" s="2">
         <v>800</v>
       </c>
-      <c r="R8" s="2">
-        <f t="shared" ref="R8:R10" si="8">H8*2</f>
+      <c r="S8" s="2">
+        <f t="shared" ref="S8:S10" si="8">H8*2</f>
         <v>7872.4000000000005</v>
       </c>
-      <c r="S8" s="2">
-        <v>5000</v>
-      </c>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2">
-        <f t="shared" ref="U8:U10" si="9">J8*2</f>
+      <c r="T8" s="2">
+        <v>5000</v>
+      </c>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2">
+        <f t="shared" ref="V8:V10" si="9">J8*2</f>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V8" s="4">
-        <f t="shared" ref="V8:V10" si="10">SUM(Q8:U8)</f>
+      <c r="W8" s="4">
+        <f t="shared" ref="W8:W10" si="10">SUM(R8:V8)</f>
         <v>18395.84</v>
       </c>
-      <c r="W8" s="2">
-        <f t="shared" ref="W8:W10" si="11">X8+U8</f>
+      <c r="X8" s="2">
+        <f t="shared" ref="X8:X10" si="11">Y8+V8</f>
         <v>37387.519999999997</v>
       </c>
-      <c r="X8" s="10">
-        <f t="shared" ref="X8:X10" si="12">P8-V8</f>
+      <c r="Y8" s="10">
+        <f t="shared" ref="Y8:Y10" si="12">Q8-W8</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="Y8" s="2">
-        <f t="shared" ref="Y8:Y10" si="13">IF(X8*13&gt;600000,1%*X8,0)</f>
-        <v>0</v>
-      </c>
       <c r="Z8" s="2">
-        <f t="shared" ref="Z8:Z10" si="14">X8-Y8</f>
+        <f t="shared" ref="Z8:Z10" si="13">IF(Y8*13&gt;600000,1%*Y8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA8" s="2">
+        <f t="shared" ref="AA8:AA10" si="14">Y8-Z8</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="AA8" s="2"/>
       <c r="AB8" s="2"/>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC8" s="2"/>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -2683,53 +2740,54 @@
         <v>0</v>
       </c>
       <c r="N9" s="2"/>
-      <c r="O9" s="4">
+      <c r="O9" s="2"/>
+      <c r="P9" s="4">
         <f t="shared" si="6"/>
         <v>5000</v>
       </c>
-      <c r="P9" s="8">
+      <c r="Q9" s="8">
         <f t="shared" si="7"/>
         <v>51059.92</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="R9" s="2">
         <v>800</v>
       </c>
-      <c r="R9" s="2">
+      <c r="S9" s="2">
         <f t="shared" si="8"/>
         <v>7872.4000000000005</v>
       </c>
-      <c r="S9" s="2">
-        <v>5000</v>
-      </c>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2">
+      <c r="T9" s="2">
+        <v>5000</v>
+      </c>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2">
         <f t="shared" si="9"/>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V9" s="4">
+      <c r="W9" s="4">
         <f t="shared" si="10"/>
         <v>18395.84</v>
       </c>
-      <c r="W9" s="2">
+      <c r="X9" s="2">
         <f t="shared" si="11"/>
         <v>37387.519999999997</v>
       </c>
-      <c r="X9" s="10">
+      <c r="Y9" s="10">
         <f t="shared" si="12"/>
         <v>32664.079999999998</v>
       </c>
-      <c r="Y9" s="2">
+      <c r="Z9" s="2">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Z9" s="2">
+      <c r="AA9" s="2">
         <f t="shared" si="14"/>
         <v>32664.079999999998</v>
       </c>
-      <c r="AA9" s="2"/>
       <c r="AB9" s="2"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC9" s="2"/>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -2768,53 +2826,54 @@
         <v>0</v>
       </c>
       <c r="N10" s="2"/>
-      <c r="O10" s="4">
+      <c r="O10" s="2"/>
+      <c r="P10" s="4">
         <f t="shared" si="6"/>
         <v>5000</v>
       </c>
-      <c r="P10" s="8">
+      <c r="Q10" s="8">
         <f t="shared" si="7"/>
         <v>51059.92</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="R10" s="2">
         <v>800</v>
       </c>
-      <c r="R10" s="2">
+      <c r="S10" s="2">
         <f t="shared" si="8"/>
         <v>7872.4000000000005</v>
       </c>
-      <c r="S10" s="2">
-        <v>5000</v>
-      </c>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2">
+      <c r="T10" s="2">
+        <v>5000</v>
+      </c>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2">
         <f t="shared" si="9"/>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V10" s="4">
+      <c r="W10" s="4">
         <f t="shared" si="10"/>
         <v>18395.84</v>
       </c>
-      <c r="W10" s="2">
+      <c r="X10" s="2">
         <f t="shared" si="11"/>
         <v>37387.519999999997</v>
       </c>
-      <c r="X10" s="10">
+      <c r="Y10" s="10">
         <f t="shared" si="12"/>
         <v>32664.079999999998</v>
       </c>
-      <c r="Y10" s="2">
+      <c r="Z10" s="2">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Z10" s="2">
+      <c r="AA10" s="2">
         <f t="shared" si="14"/>
         <v>32664.079999999998</v>
       </c>
-      <c r="AA10" s="2"/>
       <c r="AB10" s="2"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC10" s="2"/>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -2852,56 +2911,57 @@
       <c r="M11" s="2">
         <v>0</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" s="2"/>
+      <c r="O11" s="2">
         <v>10000</v>
       </c>
-      <c r="O11" s="4">
-        <f>SUM(L11:N11)</f>
+      <c r="P11" s="4">
+        <f>SUM(L11:O11)</f>
         <v>15000</v>
       </c>
-      <c r="P11" s="8">
-        <f t="shared" ref="P11:P12" si="20">K11+O11</f>
+      <c r="Q11" s="8">
+        <f t="shared" ref="Q11:Q12" si="20">K11+P11</f>
         <v>61059.92</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="R11" s="2">
         <v>800</v>
       </c>
-      <c r="R11" s="2">
-        <f t="shared" ref="R11:R12" si="21">H11*2</f>
+      <c r="S11" s="2">
+        <f t="shared" ref="S11:S12" si="21">H11*2</f>
         <v>7872.4000000000005</v>
       </c>
-      <c r="S11" s="2">
-        <v>5000</v>
-      </c>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2">
-        <f t="shared" ref="U11:U12" si="22">J11*2</f>
+      <c r="T11" s="2">
+        <v>5000</v>
+      </c>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2">
+        <f t="shared" ref="V11:V12" si="22">J11*2</f>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V11" s="4">
-        <f t="shared" ref="V11:V12" si="23">SUM(Q11:U11)</f>
+      <c r="W11" s="4">
+        <f t="shared" ref="W11:W12" si="23">SUM(R11:V11)</f>
         <v>18395.84</v>
       </c>
-      <c r="W11" s="2">
-        <f t="shared" ref="W11:W12" si="24">X11+U11</f>
+      <c r="X11" s="2">
+        <f t="shared" ref="X11:X12" si="24">Y11+V11</f>
         <v>47387.520000000004</v>
       </c>
-      <c r="X11" s="10">
-        <f t="shared" ref="X11:X12" si="25">P11-V11</f>
+      <c r="Y11" s="10">
+        <f t="shared" ref="Y11:Y12" si="25">Q11-W11</f>
         <v>42664.08</v>
       </c>
-      <c r="Y11" s="2">
-        <f t="shared" ref="Y11:Y12" si="26">IF(X11*13&gt;600000,1%*X11,0)</f>
-        <v>0</v>
-      </c>
       <c r="Z11" s="2">
-        <f t="shared" ref="Z11:Z12" si="27">X11-Y11</f>
+        <f t="shared" ref="Z11:Z12" si="26">IF(Y11*13&gt;600000,1%*Y11,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA11" s="2">
+        <f t="shared" ref="AA11:AA12" si="27">Y11-Z11</f>
         <v>42664.08</v>
       </c>
-      <c r="AA11" s="2"/>
       <c r="AB11" s="2"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC11" s="2"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -2940,53 +3000,54 @@
         <v>0</v>
       </c>
       <c r="N12" s="2"/>
-      <c r="O12" s="4">
-        <f t="shared" ref="O12" si="28">SUM(L12:M12)</f>
-        <v>5000</v>
-      </c>
-      <c r="P12" s="8">
+      <c r="O12" s="2"/>
+      <c r="P12" s="4">
+        <f t="shared" ref="P12" si="28">SUM(L12:M12)</f>
+        <v>5000</v>
+      </c>
+      <c r="Q12" s="8">
         <f t="shared" si="20"/>
         <v>51059.92</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="R12" s="2">
         <v>800</v>
       </c>
-      <c r="R12" s="2">
+      <c r="S12" s="2">
         <f t="shared" si="21"/>
         <v>7872.4000000000005</v>
       </c>
-      <c r="S12" s="2">
-        <v>5000</v>
-      </c>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2">
+      <c r="T12" s="2">
+        <v>5000</v>
+      </c>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2">
         <f t="shared" si="22"/>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V12" s="4">
+      <c r="W12" s="4">
         <f t="shared" si="23"/>
         <v>18395.84</v>
       </c>
-      <c r="W12" s="2">
+      <c r="X12" s="2">
         <f t="shared" si="24"/>
         <v>37387.519999999997</v>
       </c>
-      <c r="X12" s="10">
+      <c r="Y12" s="10">
         <f t="shared" si="25"/>
         <v>32664.079999999998</v>
       </c>
-      <c r="Y12" s="2">
+      <c r="Z12" s="2">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="Z12" s="2">
+      <c r="AA12" s="2">
         <f t="shared" si="27"/>
         <v>32664.079999999998</v>
       </c>
-      <c r="AA12" s="2"/>
       <c r="AB12" s="2"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC12" s="2"/>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -3025,53 +3086,54 @@
         <v>0</v>
       </c>
       <c r="N13" s="2"/>
-      <c r="O13" s="4">
-        <f t="shared" ref="O13" si="34">SUM(L13:M13)</f>
-        <v>5000</v>
-      </c>
-      <c r="P13" s="8">
-        <f t="shared" ref="P13" si="35">K13+O13</f>
+      <c r="O13" s="2"/>
+      <c r="P13" s="4">
+        <f t="shared" ref="P13" si="34">SUM(L13:M13)</f>
+        <v>5000</v>
+      </c>
+      <c r="Q13" s="8">
+        <f t="shared" ref="Q13" si="35">K13+P13</f>
         <v>51059.92</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="R13" s="2">
         <v>800</v>
       </c>
-      <c r="R13" s="2">
-        <f t="shared" ref="R13" si="36">H13*2</f>
+      <c r="S13" s="2">
+        <f t="shared" ref="S13" si="36">H13*2</f>
         <v>7872.4000000000005</v>
       </c>
-      <c r="S13" s="2">
-        <v>5000</v>
-      </c>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2">
-        <f t="shared" ref="U13" si="37">J13*2</f>
+      <c r="T13" s="2">
+        <v>5000</v>
+      </c>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2">
+        <f t="shared" ref="V13" si="37">J13*2</f>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V13" s="4">
-        <f t="shared" ref="V13" si="38">SUM(Q13:U13)</f>
+      <c r="W13" s="4">
+        <f t="shared" ref="W13" si="38">SUM(R13:V13)</f>
         <v>18395.84</v>
       </c>
-      <c r="W13" s="2">
-        <f t="shared" ref="W13" si="39">X13+U13</f>
+      <c r="X13" s="2">
+        <f t="shared" ref="X13" si="39">Y13+V13</f>
         <v>37387.519999999997</v>
       </c>
-      <c r="X13" s="10">
-        <f t="shared" ref="X13" si="40">P13-V13</f>
+      <c r="Y13" s="10">
+        <f t="shared" ref="Y13" si="40">Q13-W13</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="Y13" s="2">
-        <f t="shared" ref="Y13" si="41">IF(X13*13&gt;600000,1%*X13,0)</f>
-        <v>0</v>
-      </c>
       <c r="Z13" s="2">
-        <f t="shared" ref="Z13" si="42">X13-Y13</f>
+        <f t="shared" ref="Z13" si="41">IF(Y13*13&gt;600000,1%*Y13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA13" s="2">
+        <f t="shared" ref="AA13" si="42">Y13-Z13</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="AA13" s="2"/>
       <c r="AB13" s="2"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC13" s="2"/>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -3110,55 +3172,56 @@
         <v>0</v>
       </c>
       <c r="N14" s="2"/>
-      <c r="O14" s="4">
-        <f t="shared" ref="O14" si="47">SUM(L14:M14)</f>
-        <v>5000</v>
-      </c>
-      <c r="P14" s="8">
-        <f t="shared" ref="P14" si="48">K14+O14</f>
+      <c r="O14" s="2"/>
+      <c r="P14" s="4">
+        <f t="shared" ref="P14" si="47">SUM(L14:M14)</f>
+        <v>5000</v>
+      </c>
+      <c r="Q14" s="8">
+        <f t="shared" ref="Q14" si="48">K14+P14</f>
         <v>52403.199999999997</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="R14" s="2">
         <v>800</v>
       </c>
-      <c r="R14" s="2">
-        <f t="shared" ref="R14" si="49">H14*2</f>
+      <c r="S14" s="2">
+        <f t="shared" ref="S14" si="49">H14*2</f>
         <v>8104</v>
       </c>
-      <c r="S14" s="2">
-        <v>5000</v>
-      </c>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2">
-        <f t="shared" ref="U14" si="50">J14*2</f>
+      <c r="T14" s="2">
+        <v>5000</v>
+      </c>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2">
+        <f t="shared" ref="V14" si="50">J14*2</f>
         <v>4862.3999999999996</v>
       </c>
-      <c r="V14" s="4">
-        <f t="shared" ref="V14" si="51">SUM(Q14:U14)</f>
+      <c r="W14" s="4">
+        <f t="shared" ref="W14" si="51">SUM(R14:V14)</f>
         <v>18766.400000000001</v>
       </c>
-      <c r="W14" s="2">
-        <f t="shared" ref="W14" si="52">X14+U14</f>
+      <c r="X14" s="2">
+        <f t="shared" ref="X14" si="52">Y14+V14</f>
         <v>38499.199999999997</v>
       </c>
-      <c r="X14" s="10">
-        <f t="shared" ref="X14" si="53">P14-V14</f>
+      <c r="Y14" s="10">
+        <f t="shared" ref="Y14" si="53">Q14-W14</f>
         <v>33636.799999999996</v>
       </c>
-      <c r="Y14" s="2">
-        <f t="shared" ref="Y14" si="54">IF(X14*13&gt;600000,1%*X14,0)</f>
-        <v>0</v>
-      </c>
       <c r="Z14" s="2">
-        <f t="shared" ref="Z14" si="55">X14-Y14</f>
+        <f t="shared" ref="Z14" si="54">IF(Y14*13&gt;600000,1%*Y14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA14" s="2">
+        <f t="shared" ref="AA14" si="55">Y14-Z14</f>
         <v>33636.799999999996</v>
       </c>
-      <c r="AA14" s="2"/>
-      <c r="AB14" s="2" t="s">
+      <c r="AB14" s="2"/>
+      <c r="AC14" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -3177,22 +3240,23 @@
         <v>5100</v>
       </c>
       <c r="N15" s="2"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="8"/>
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
-      <c r="V15" s="4"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="10"/>
-      <c r="Y15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="4"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="10"/>
       <c r="Z15" s="2"/>
       <c r="AA15" s="2"/>
       <c r="AB15" s="2"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC15" s="2"/>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -3207,22 +3271,23 @@
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="8"/>
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
-      <c r="V16" s="4"/>
-      <c r="W16" s="2"/>
-      <c r="X16" s="10"/>
-      <c r="Y16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="4"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="10"/>
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
       <c r="AB16" s="2"/>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC16" s="2"/>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -3258,172 +3323,181 @@
         <f t="shared" si="5"/>
         <v>5000</v>
       </c>
-      <c r="M17" s="2">
+      <c r="M17" s="2"/>
+      <c r="N17" s="2">
         <f>10%*D17</f>
         <v>3820.3</v>
       </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="4">
-        <f t="shared" ref="O17" si="60">SUM(L17:M17)</f>
+      <c r="O17" s="2"/>
+      <c r="P17" s="4">
+        <f>SUM(L17:N17)</f>
         <v>8820.2999999999993</v>
       </c>
-      <c r="P17" s="8">
-        <f t="shared" ref="P17" si="61">K17+O17</f>
+      <c r="Q17" s="8">
+        <f t="shared" ref="Q17" si="60">K17+P17</f>
         <v>59447.14</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="R17" s="2">
         <v>800</v>
       </c>
-      <c r="R17" s="2">
-        <f t="shared" ref="R17" si="62">H17*2</f>
+      <c r="S17" s="2">
+        <f t="shared" ref="S17" si="61">H17*2</f>
         <v>8659.8000000000011</v>
       </c>
-      <c r="S17" s="2">
-        <v>5000</v>
-      </c>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2">
-        <f t="shared" ref="U17" si="63">J17*2</f>
+      <c r="T17" s="2">
+        <v>5000</v>
+      </c>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2">
+        <f t="shared" ref="V17" si="62">J17*2</f>
         <v>5195.88</v>
       </c>
-      <c r="V17" s="4">
-        <f t="shared" ref="V17" si="64">SUM(Q17:U17)</f>
+      <c r="W17" s="4">
+        <f t="shared" ref="W17" si="63">SUM(R17:V17)</f>
         <v>19655.68</v>
       </c>
-      <c r="W17" s="2">
-        <f t="shared" ref="W17" si="65">X17+U17</f>
+      <c r="X17" s="2">
+        <f t="shared" ref="X17" si="64">Y17+V17</f>
         <v>44987.34</v>
       </c>
-      <c r="X17" s="10">
-        <f t="shared" ref="X17" si="66">P17-V17</f>
+      <c r="Y17" s="10">
+        <f t="shared" ref="Y17" si="65">Q17-W17</f>
         <v>39791.46</v>
       </c>
-      <c r="Y17" s="2">
-        <f t="shared" ref="Y17" si="67">IF(X17*13&gt;600000,1%*X17,0)</f>
-        <v>0</v>
-      </c>
       <c r="Z17" s="2">
-        <f t="shared" ref="Z17" si="68">X17-Y17</f>
+        <f t="shared" ref="Z17" si="66">IF(Y17*13&gt;600000,1%*Y17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="2">
+        <f t="shared" ref="AA17" si="67">Y17-Z17</f>
         <v>39791.46</v>
       </c>
-      <c r="AA17" s="2"/>
       <c r="AB17" s="2"/>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC17" s="2"/>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="D18" s="4">
+        <f>34730*1.1</f>
+        <v>38203</v>
+      </c>
+      <c r="E18" s="4">
+        <f>(D18/30)*5</f>
+        <v>6367.166666666667</v>
+      </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
+      <c r="G18" s="8">
+        <f t="shared" ref="G18" si="68">SUM(D18:F18)</f>
+        <v>44570.166666666664</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" ref="H18" si="69">10%*G18</f>
+        <v>4457.0166666666664</v>
+      </c>
+      <c r="I18" s="2">
+        <v>400</v>
+      </c>
+      <c r="J18" s="2">
+        <f t="shared" ref="J18" si="70">6%*G18</f>
+        <v>2674.2099999999996</v>
+      </c>
+      <c r="K18" s="8">
+        <f t="shared" ref="K18" si="71">SUM(G18:J18)</f>
+        <v>52101.393333333333</v>
+      </c>
+      <c r="L18" s="2">
+        <f t="shared" si="5"/>
+        <v>5000</v>
+      </c>
+      <c r="M18" s="2">
+        <f>G18</f>
+        <v>44570.166666666664</v>
+      </c>
+      <c r="N18" s="2">
+        <f>10%*D18</f>
+        <v>3820.3</v>
+      </c>
+      <c r="O18" s="2"/>
+      <c r="P18" s="4">
+        <f>SUM(L18:O18)</f>
+        <v>53390.466666666667</v>
+      </c>
+      <c r="Q18" s="8">
+        <f t="shared" ref="Q18" si="72">K18+P18</f>
+        <v>105491.86</v>
+      </c>
+      <c r="R18" s="2">
+        <v>800</v>
+      </c>
+      <c r="S18" s="2">
+        <f t="shared" ref="S18" si="73">H18*2</f>
+        <v>8914.0333333333328</v>
+      </c>
+      <c r="T18" s="2">
+        <v>5000</v>
+      </c>
       <c r="U18" s="2"/>
-      <c r="V18" s="4"/>
-      <c r="W18" s="2"/>
-      <c r="X18" s="10"/>
-      <c r="Y18" s="2"/>
-      <c r="Z18" s="2"/>
-      <c r="AA18" s="2"/>
+      <c r="V18" s="2">
+        <f t="shared" ref="V18" si="74">J18*2</f>
+        <v>5348.4199999999992</v>
+      </c>
+      <c r="W18" s="4">
+        <f t="shared" ref="W18" si="75">SUM(R18:V18)</f>
+        <v>20062.453333333331</v>
+      </c>
+      <c r="X18" s="2">
+        <f t="shared" ref="X18" si="76">Y18+V18</f>
+        <v>90777.826666666675</v>
+      </c>
+      <c r="Y18" s="10">
+        <f t="shared" ref="Y18" si="77">Q18-W18</f>
+        <v>85429.406666666677</v>
+      </c>
+      <c r="Z18" s="2">
+        <f>IF(Y18*13&gt;600000,1%*Y18,0)-IF(Y18*13&gt;600000,1%*Y18,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA18" s="2">
+        <f>Y18-Z18-4</f>
+        <v>85425.406666666677</v>
+      </c>
       <c r="AB18" s="2"/>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC18" s="2"/>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="4">
-        <v>43689</v>
-      </c>
-      <c r="E19" s="4">
-        <v>0</v>
-      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="8">
-        <f>SUM(D19:F19)</f>
-        <v>43689</v>
-      </c>
-      <c r="H19" s="2">
-        <f>10%*G19</f>
-        <v>4368.9000000000005</v>
-      </c>
-      <c r="I19" s="2">
-        <v>400</v>
-      </c>
-      <c r="J19" s="2">
-        <f>6%*G19</f>
-        <v>2621.3399999999997</v>
-      </c>
-      <c r="K19" s="8">
-        <f>SUM(G19:J19)</f>
-        <v>51079.24</v>
-      </c>
-      <c r="L19" s="2">
-        <f>2000+3000</f>
-        <v>5000</v>
-      </c>
-      <c r="M19" s="2">
-        <v>0</v>
-      </c>
+      <c r="G19" s="8"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
       <c r="N19" s="2"/>
-      <c r="O19" s="4">
-        <f>SUM(L19:M19)</f>
-        <v>5000</v>
-      </c>
-      <c r="P19" s="8">
-        <f>K19+O19</f>
-        <v>56079.24</v>
-      </c>
-      <c r="Q19" s="2">
-        <v>801</v>
-      </c>
-      <c r="R19" s="2">
-        <f>H19*2</f>
-        <v>8737.8000000000011</v>
-      </c>
-      <c r="S19" s="2">
-        <v>1000</v>
-      </c>
+      <c r="O19" s="2"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
       <c r="T19" s="2"/>
-      <c r="U19" s="2">
-        <f>J19*2</f>
-        <v>5242.6799999999994</v>
-      </c>
-      <c r="V19" s="4">
-        <f>SUM(Q19:U19)</f>
-        <v>15781.48</v>
-      </c>
-      <c r="W19" s="2">
-        <f>X19+U19</f>
-        <v>45540.439999999995</v>
-      </c>
-      <c r="X19" s="10">
-        <f>P19-V19</f>
-        <v>40297.759999999995</v>
-      </c>
-      <c r="Y19" s="2">
-        <f>IF(X19*13&gt;600000,1%*X19,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z19" s="2">
-        <f>X19-Y19</f>
-        <v>40297.759999999995</v>
-      </c>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="4"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="10"/>
+      <c r="Z19" s="2"/>
       <c r="AA19" s="2"/>
       <c r="AB19" s="2"/>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC19" s="2"/>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -3438,22 +3512,23 @@
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="8"/>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
-      <c r="V20" s="4"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="10"/>
-      <c r="Y20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="4"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="10"/>
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
       <c r="AB20" s="2"/>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC20" s="2"/>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -3468,52 +3543,108 @@
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="8"/>
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
-      <c r="V21" s="4"/>
-      <c r="W21" s="2"/>
-      <c r="X21" s="10"/>
-      <c r="Y21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="4"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="10"/>
       <c r="Z21" s="2"/>
       <c r="AA21" s="2"/>
       <c r="AB21" s="2"/>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC21" s="2"/>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="D22" s="4">
+        <v>43689</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
       <c r="F22" s="2"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
+      <c r="G22" s="8">
+        <f>SUM(D22:F22)</f>
+        <v>43689</v>
+      </c>
+      <c r="H22" s="2">
+        <f>10%*G22</f>
+        <v>4368.9000000000005</v>
+      </c>
+      <c r="I22" s="2">
+        <v>400</v>
+      </c>
+      <c r="J22" s="2">
+        <f>6%*G22</f>
+        <v>2621.3399999999997</v>
+      </c>
+      <c r="K22" s="8">
+        <f>SUM(G22:J22)</f>
+        <v>51079.24</v>
+      </c>
+      <c r="L22" s="2">
+        <f>2000+3000</f>
+        <v>5000</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
       <c r="N22" s="2"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="4">
+        <f>SUM(L22:M22)</f>
+        <v>5000</v>
+      </c>
+      <c r="Q22" s="8">
+        <f>K22+P22</f>
+        <v>56079.24</v>
+      </c>
+      <c r="R22" s="2">
+        <v>801</v>
+      </c>
+      <c r="S22" s="2">
+        <f>H22*2</f>
+        <v>8737.8000000000011</v>
+      </c>
+      <c r="T22" s="2">
+        <v>1000</v>
+      </c>
       <c r="U22" s="2"/>
-      <c r="V22" s="4"/>
-      <c r="W22" s="2"/>
-      <c r="X22" s="10"/>
-      <c r="Y22" s="2"/>
-      <c r="Z22" s="2"/>
-      <c r="AA22" s="2"/>
+      <c r="V22" s="2">
+        <f>J22*2</f>
+        <v>5242.6799999999994</v>
+      </c>
+      <c r="W22" s="4">
+        <f>SUM(R22:V22)</f>
+        <v>15781.48</v>
+      </c>
+      <c r="X22" s="2">
+        <f>Y22+V22</f>
+        <v>45540.439999999995</v>
+      </c>
+      <c r="Y22" s="10">
+        <f>Q22-W22</f>
+        <v>40297.759999999995</v>
+      </c>
+      <c r="Z22" s="2">
+        <f>IF(Y22*13&gt;600000,1%*Y22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA22" s="2">
+        <f>Y22-Z22</f>
+        <v>40297.759999999995</v>
+      </c>
       <c r="AB22" s="2"/>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC22" s="2"/>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -3528,22 +3659,23 @@
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="8"/>
-      <c r="Q23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="8"/>
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
-      <c r="V23" s="4"/>
-      <c r="W23" s="2"/>
-      <c r="X23" s="10"/>
-      <c r="Y23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="4"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="10"/>
       <c r="Z23" s="2"/>
       <c r="AA23" s="2"/>
       <c r="AB23" s="2"/>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC23" s="2"/>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -3558,22 +3690,23 @@
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="8"/>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
-      <c r="V24" s="4"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="10"/>
-      <c r="Y24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="4"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="10"/>
       <c r="Z24" s="2"/>
       <c r="AA24" s="2"/>
       <c r="AB24" s="2"/>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC24" s="2"/>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3588,22 +3721,23 @@
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="8"/>
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
-      <c r="V25" s="4"/>
-      <c r="W25" s="2"/>
-      <c r="X25" s="10"/>
-      <c r="Y25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="4"/>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="10"/>
       <c r="Z25" s="2"/>
       <c r="AA25" s="2"/>
       <c r="AB25" s="2"/>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC25" s="2"/>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -3618,22 +3752,23 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="8"/>
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
-      <c r="V26" s="4"/>
-      <c r="W26" s="2"/>
-      <c r="X26" s="10"/>
-      <c r="Y26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="4"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="10"/>
       <c r="Z26" s="2"/>
       <c r="AA26" s="2"/>
       <c r="AB26" s="2"/>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC26" s="2"/>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3648,22 +3783,23 @@
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="8"/>
       <c r="R27" s="2"/>
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
-      <c r="V27" s="4"/>
-      <c r="W27" s="2"/>
-      <c r="X27" s="10"/>
-      <c r="Y27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="4"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="10"/>
       <c r="Z27" s="2"/>
       <c r="AA27" s="2"/>
       <c r="AB27" s="2"/>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC27" s="2"/>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3678,22 +3814,23 @@
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="8"/>
-      <c r="Q28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="8"/>
       <c r="R28" s="2"/>
       <c r="S28" s="2"/>
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
-      <c r="V28" s="4"/>
-      <c r="W28" s="2"/>
-      <c r="X28" s="10"/>
-      <c r="Y28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="4"/>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="10"/>
       <c r="Z28" s="2"/>
       <c r="AA28" s="2"/>
       <c r="AB28" s="2"/>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC28" s="2"/>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3708,37 +3845,131 @@
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="8"/>
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
-      <c r="V29" s="4"/>
-      <c r="W29" s="2"/>
-      <c r="X29" s="10"/>
-      <c r="Y29" s="2"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="4"/>
+      <c r="X29" s="2"/>
+      <c r="Y29" s="10"/>
       <c r="Z29" s="2"/>
       <c r="AA29" s="2"/>
       <c r="AB29" s="2"/>
+      <c r="AC29" s="2"/>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="8"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="4"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="10"/>
+      <c r="Z30" s="2"/>
+      <c r="AA30" s="2"/>
+      <c r="AB30" s="2"/>
+      <c r="AC30" s="2"/>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="8"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="4"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="10"/>
+      <c r="Z31" s="2"/>
+      <c r="AA31" s="2"/>
+      <c r="AB31" s="2"/>
+      <c r="AC31" s="2"/>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="4"/>
+      <c r="Q32" s="8"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="4"/>
+      <c r="X32" s="2"/>
+      <c r="Y32" s="10"/>
+      <c r="Z32" s="2"/>
+      <c r="AA32" s="2"/>
+      <c r="AB32" s="2"/>
+      <c r="AC32" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="W1:W2"/>
-    <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="L1:O1"/>
-    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="X1:X2"/>
+    <mergeCell ref="AC1:AC2"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="Q1:Q2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="H1:K1"/>
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="Q1:V1"/>
-    <mergeCell ref="X1:X2"/>
+    <mergeCell ref="R1:W1"/>
     <mergeCell ref="Y1:Y2"/>
     <mergeCell ref="Z1:Z2"/>
     <mergeCell ref="AA1:AA2"/>
+    <mergeCell ref="AB1:AB2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -3781,68 +4012,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16" t="s">
+      <c r="A1" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15" t="s">
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15" t="s">
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="17" t="s">
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="Q1" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="16" t="s">
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="Y1" s="17" t="s">
+      <c r="Y1" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="Z1" s="16" t="s">
+      <c r="Z1" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="AA1" s="16" t="s">
+      <c r="AA1" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="AB1" s="16" t="s">
+      <c r="AB1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="AC1" s="16" t="s">
+      <c r="AC1" s="44" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:29" s="6" customFormat="1" ht="71.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
       <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
@@ -3879,7 +4110,7 @@
       <c r="O2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="17"/>
+      <c r="P2" s="45"/>
       <c r="Q2" s="3" t="s">
         <v>14</v>
       </c>
@@ -3901,12 +4132,12 @@
       <c r="W2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="44"/>
+      <c r="AA2" s="44"/>
+      <c r="AB2" s="44"/>
+      <c r="AC2" s="44"/>
     </row>
     <row r="3" spans="1:29" s="6" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
@@ -4094,11 +4325,11 @@
         <v>14315.2</v>
       </c>
       <c r="X5" s="2">
-        <f>Y5+U5</f>
+        <f t="shared" ref="X5:X16" si="18">Y5+U5</f>
         <v>22806.6</v>
       </c>
       <c r="Y5" s="10">
-        <f>P5-W5</f>
+        <f t="shared" ref="Y5:Y16" si="19">P5-W5</f>
         <v>19613.399999999998</v>
       </c>
       <c r="Z5" s="2">
@@ -4106,7 +4337,7 @@
         <v>0</v>
       </c>
       <c r="AA5" s="2">
-        <f t="shared" ref="AA5:AA16" si="18">Y5-Z5</f>
+        <f t="shared" ref="AA5:AA16" si="20">Y5-Z5</f>
         <v>19613.399999999998</v>
       </c>
       <c r="AB5" s="2"/>
@@ -4120,7 +4351,7 @@
         <v>26610</v>
       </c>
       <c r="E6" s="4">
-        <f t="shared" ref="E6:E15" si="19">ROUNDUP(D6/30,0)*0</f>
+        <f t="shared" ref="E6:E15" si="21">ROUNDUP(D6/30,0)*0</f>
         <v>0</v>
       </c>
       <c r="F6" s="2"/>
@@ -4181,11 +4412,11 @@
         <v>14315.2</v>
       </c>
       <c r="X6" s="2">
-        <f>Y6+U6</f>
+        <f t="shared" si="18"/>
         <v>22806.6</v>
       </c>
       <c r="Y6" s="10">
-        <f>P6-W6</f>
+        <f t="shared" si="19"/>
         <v>19613.399999999998</v>
       </c>
       <c r="Z6" s="2">
@@ -4193,7 +4424,7 @@
         <v>0</v>
       </c>
       <c r="AA6" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>19613.399999999998</v>
       </c>
       <c r="AB6" s="2"/>
@@ -4207,7 +4438,7 @@
         <v>26610</v>
       </c>
       <c r="E7" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="F7" s="2"/>
@@ -4268,16 +4499,16 @@
         <v>14315.2</v>
       </c>
       <c r="X7" s="2">
-        <f>Y7+U7</f>
+        <f t="shared" si="18"/>
         <v>49416.599999999991</v>
       </c>
       <c r="Y7" s="10">
-        <f>P7-W7</f>
+        <f t="shared" si="19"/>
         <v>46223.399999999994</v>
       </c>
       <c r="Z7" s="2"/>
       <c r="AA7" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>46223.399999999994</v>
       </c>
       <c r="AB7" s="2"/>
@@ -4291,7 +4522,7 @@
         <v>26610</v>
       </c>
       <c r="E8" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="F8" s="2"/>
@@ -4319,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="2">
-        <f t="shared" ref="M8:M16" si="20">10%*D8</f>
+        <f t="shared" ref="M8:M16" si="22">10%*D8</f>
         <v>2661</v>
       </c>
       <c r="N8" s="2"/>
@@ -4352,11 +4583,11 @@
         <v>14315.2</v>
       </c>
       <c r="X8" s="2">
-        <f>Y8+U8</f>
+        <f t="shared" si="18"/>
         <v>22806.6</v>
       </c>
       <c r="Y8" s="10">
-        <f>P8-W8</f>
+        <f t="shared" si="19"/>
         <v>19613.399999999998</v>
       </c>
       <c r="Z8" s="2">
@@ -4364,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="AA8" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>19613.399999999998</v>
       </c>
       <c r="AB8" s="2"/>
@@ -4378,7 +4609,7 @@
         <v>26610</v>
       </c>
       <c r="E9" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="F9" s="2"/>
@@ -4406,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2661</v>
       </c>
       <c r="N9" s="2"/>
@@ -4439,11 +4670,11 @@
         <v>14315.2</v>
       </c>
       <c r="X9" s="2">
-        <f>Y9+U9</f>
+        <f t="shared" si="18"/>
         <v>22806.6</v>
       </c>
       <c r="Y9" s="10">
-        <f>P9-W9</f>
+        <f t="shared" si="19"/>
         <v>19613.399999999998</v>
       </c>
       <c r="Z9" s="2">
@@ -4451,7 +4682,7 @@
         <v>0</v>
       </c>
       <c r="AA9" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>19613.399999999998</v>
       </c>
       <c r="AB9" s="2"/>
@@ -4465,7 +4696,7 @@
         <v>26610</v>
       </c>
       <c r="E10" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="F10" s="2"/>
@@ -4493,7 +4724,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2661</v>
       </c>
       <c r="N10" s="2"/>
@@ -4526,11 +4757,11 @@
         <v>14315.2</v>
       </c>
       <c r="X10" s="2">
-        <f>Y10+U10</f>
+        <f t="shared" si="18"/>
         <v>22806.6</v>
       </c>
       <c r="Y10" s="10">
-        <f>P10-W10</f>
+        <f t="shared" si="19"/>
         <v>19613.399999999998</v>
       </c>
       <c r="Z10" s="2">
@@ -4538,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="AA10" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>19613.399999999998</v>
       </c>
       <c r="AB10" s="2"/>
@@ -4552,7 +4783,7 @@
         <v>26610</v>
       </c>
       <c r="E11" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="F11" s="2"/>
@@ -4580,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2661</v>
       </c>
       <c r="N11" s="2"/>
@@ -4613,11 +4844,11 @@
         <v>14315.2</v>
       </c>
       <c r="X11" s="2">
-        <f>Y11+U11</f>
+        <f t="shared" si="18"/>
         <v>22806.6</v>
       </c>
       <c r="Y11" s="10">
-        <f>P11-W11</f>
+        <f t="shared" si="19"/>
         <v>19613.399999999998</v>
       </c>
       <c r="Z11" s="2">
@@ -4625,7 +4856,7 @@
         <v>0</v>
       </c>
       <c r="AA11" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>19613.399999999998</v>
       </c>
       <c r="AB11" s="2"/>
@@ -4639,7 +4870,7 @@
         <v>26610</v>
       </c>
       <c r="E12" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="F12" s="2"/>
@@ -4667,7 +4898,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2661</v>
       </c>
       <c r="N12" s="2"/>
@@ -4700,11 +4931,11 @@
         <v>14315.2</v>
       </c>
       <c r="X12" s="2">
-        <f>Y12+U12</f>
+        <f t="shared" si="18"/>
         <v>22806.6</v>
       </c>
       <c r="Y12" s="10">
-        <f>P12-W12</f>
+        <f t="shared" si="19"/>
         <v>19613.399999999998</v>
       </c>
       <c r="Z12" s="2">
@@ -4712,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="AA12" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>19613.399999999998</v>
       </c>
       <c r="AB12" s="2"/>
@@ -4726,7 +4957,7 @@
         <v>26610</v>
       </c>
       <c r="E13" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="F13" s="2"/>
@@ -4754,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2661</v>
       </c>
       <c r="N13" s="2">
@@ -4789,11 +5020,11 @@
         <v>14315.2</v>
       </c>
       <c r="X13" s="2">
-        <f>Y13+U13</f>
+        <f t="shared" si="18"/>
         <v>32806.6</v>
       </c>
       <c r="Y13" s="10">
-        <f>P13-W13</f>
+        <f t="shared" si="19"/>
         <v>29613.399999999998</v>
       </c>
       <c r="Z13" s="2">
@@ -4801,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="AA13" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>29613.399999999998</v>
       </c>
       <c r="AB13" s="2"/>
@@ -4815,7 +5046,7 @@
         <v>26610</v>
       </c>
       <c r="E14" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="F14" s="2"/>
@@ -4843,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2661</v>
       </c>
       <c r="N14" s="2"/>
@@ -4876,11 +5107,11 @@
         <v>14315.2</v>
       </c>
       <c r="X14" s="2">
-        <f>Y14+U14</f>
+        <f t="shared" si="18"/>
         <v>22806.6</v>
       </c>
       <c r="Y14" s="10">
-        <f>P14-W14</f>
+        <f t="shared" si="19"/>
         <v>19613.399999999998</v>
       </c>
       <c r="Z14" s="2">
@@ -4888,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="AA14" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>19613.399999999998</v>
       </c>
       <c r="AB14" s="2"/>
@@ -4902,7 +5133,7 @@
         <v>26610</v>
       </c>
       <c r="E15" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="F15" s="2"/>
@@ -4930,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2661</v>
       </c>
       <c r="N15" s="2"/>
@@ -4963,11 +5194,11 @@
         <v>14315.2</v>
       </c>
       <c r="X15" s="2">
-        <f>Y15+U15</f>
+        <f t="shared" si="18"/>
         <v>22806.6</v>
       </c>
       <c r="Y15" s="10">
-        <f>P15-W15</f>
+        <f t="shared" si="19"/>
         <v>19613.399999999998</v>
       </c>
       <c r="Z15" s="2">
@@ -4975,7 +5206,7 @@
         <v>0</v>
       </c>
       <c r="AA15" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>19613.399999999998</v>
       </c>
       <c r="AB15" s="2"/>
@@ -4989,7 +5220,7 @@
         <v>26610</v>
       </c>
       <c r="E16" s="4">
-        <f t="shared" ref="E16" si="21">ROUNDUP(D16/30,0)</f>
+        <f t="shared" ref="E16" si="23">ROUNDUP(D16/30,0)</f>
         <v>887</v>
       </c>
       <c r="F16" s="2"/>
@@ -5017,7 +5248,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2661</v>
       </c>
       <c r="N16" s="2"/>
@@ -5050,11 +5281,11 @@
         <v>14599.04</v>
       </c>
       <c r="X16" s="2">
-        <f>Y16+U16</f>
+        <f t="shared" si="18"/>
         <v>23658.120000000003</v>
       </c>
       <c r="Y16" s="10">
-        <f>P16-W16</f>
+        <f t="shared" si="19"/>
         <v>20358.480000000003</v>
       </c>
       <c r="Z16" s="2">
@@ -5062,7 +5293,7 @@
         <v>0</v>
       </c>
       <c r="AA16" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>20358.480000000003</v>
       </c>
       <c r="AB16" s="2"/>
@@ -5112,7 +5343,7 @@
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="8">
-        <f t="shared" ref="G18:G29" si="22">SUM(D18:F18)</f>
+        <f t="shared" ref="G18:G29" si="24">SUM(D18:F18)</f>
         <v>29564</v>
       </c>
       <c r="H18" s="2">
@@ -5124,11 +5355,11 @@
         <v>400</v>
       </c>
       <c r="J18" s="2">
-        <f t="shared" ref="J18:J29" si="23">6%*G18</f>
+        <f t="shared" ref="J18:J29" si="25">6%*G18</f>
         <v>1773.84</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" ref="K18:K29" si="24">SUM(G18:J18)</f>
+        <f t="shared" ref="K18:K29" si="26">SUM(G18:J18)</f>
         <v>34694.239999999998</v>
       </c>
       <c r="L18" s="2">
@@ -5140,18 +5371,18 @@
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="4">
-        <f t="shared" ref="O18:O29" si="25">SUM(L18:N18)</f>
+        <f t="shared" ref="O18:O29" si="27">SUM(L18:N18)</f>
         <v>2861</v>
       </c>
       <c r="P18" s="8">
-        <f t="shared" ref="P18:P29" si="26">K18+O18</f>
+        <f t="shared" ref="P18:P29" si="28">K18+O18</f>
         <v>37555.24</v>
       </c>
       <c r="Q18" s="2">
         <v>800</v>
       </c>
       <c r="R18" s="2">
-        <f t="shared" ref="R18:R29" si="27">H18*2</f>
+        <f t="shared" ref="R18:R29" si="29">H18*2</f>
         <v>5912.8</v>
       </c>
       <c r="S18" s="2">
@@ -5159,20 +5390,20 @@
       </c>
       <c r="T18" s="2"/>
       <c r="U18" s="2">
-        <f t="shared" ref="U18:U29" si="28">J18*2</f>
+        <f t="shared" ref="U18:U29" si="30">J18*2</f>
         <v>3547.68</v>
       </c>
       <c r="V18" s="2"/>
       <c r="W18" s="4">
-        <f t="shared" ref="W18:W29" si="29">SUM(Q18:U18)</f>
+        <f t="shared" ref="W18:W29" si="31">SUM(Q18:U18)</f>
         <v>15260.48</v>
       </c>
       <c r="X18" s="2">
-        <f>Y18+U18</f>
+        <f t="shared" ref="X18:X29" si="32">Y18+U18</f>
         <v>25842.44</v>
       </c>
       <c r="Y18" s="10">
-        <f>P18-W18</f>
+        <f t="shared" ref="Y18:Y29" si="33">P18-W18</f>
         <v>22294.76</v>
       </c>
       <c r="Z18" s="2">
@@ -5180,7 +5411,7 @@
         <v>0</v>
       </c>
       <c r="AA18" s="2">
-        <f t="shared" ref="AA18:AA29" si="30">Y18-Z18</f>
+        <f t="shared" ref="AA18:AA29" si="34">Y18-Z18</f>
         <v>22294.76</v>
       </c>
       <c r="AB18" s="2"/>
@@ -5194,12 +5425,12 @@
         <v>28610</v>
       </c>
       <c r="E19" s="4">
-        <f t="shared" ref="E19:E28" si="31">ROUNDUP(D19/30,0)*1</f>
+        <f t="shared" ref="E19:E28" si="35">ROUNDUP(D19/30,0)*1</f>
         <v>954</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>29564</v>
       </c>
       <c r="H19" s="2">
@@ -5211,11 +5442,11 @@
         <v>400</v>
       </c>
       <c r="J19" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1773.84</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L19" s="2">
@@ -5227,18 +5458,18 @@
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2861</v>
       </c>
       <c r="P19" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>37555.24</v>
       </c>
       <c r="Q19" s="2">
         <v>800</v>
       </c>
       <c r="R19" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5912.8</v>
       </c>
       <c r="S19" s="2">
@@ -5246,20 +5477,20 @@
       </c>
       <c r="T19" s="2"/>
       <c r="U19" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>3547.68</v>
       </c>
       <c r="V19" s="2"/>
       <c r="W19" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>15260.48</v>
       </c>
       <c r="X19" s="2">
-        <f>Y19+U19</f>
+        <f t="shared" si="32"/>
         <v>25842.44</v>
       </c>
       <c r="Y19" s="10">
-        <f>P19-W19</f>
+        <f t="shared" si="33"/>
         <v>22294.76</v>
       </c>
       <c r="Z19" s="2">
@@ -5267,7 +5498,7 @@
         <v>0</v>
       </c>
       <c r="AA19" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>22294.76</v>
       </c>
       <c r="AB19" s="2"/>
@@ -5281,12 +5512,12 @@
         <v>28610</v>
       </c>
       <c r="E20" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>954</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>29564</v>
       </c>
       <c r="H20" s="2">
@@ -5298,11 +5529,11 @@
         <v>400</v>
       </c>
       <c r="J20" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1773.84</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L20" s="2">
@@ -5314,18 +5545,18 @@
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>31471</v>
       </c>
       <c r="P20" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>66165.239999999991</v>
       </c>
       <c r="Q20" s="2">
         <v>800</v>
       </c>
       <c r="R20" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5912.8</v>
       </c>
       <c r="S20" s="2">
@@ -5333,25 +5564,25 @@
       </c>
       <c r="T20" s="2"/>
       <c r="U20" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>3547.68</v>
       </c>
       <c r="V20" s="2"/>
       <c r="W20" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>15260.48</v>
       </c>
       <c r="X20" s="2">
-        <f>Y20+U20</f>
+        <f t="shared" si="32"/>
         <v>54452.439999999995</v>
       </c>
       <c r="Y20" s="10">
-        <f>P20-W20</f>
+        <f t="shared" si="33"/>
         <v>50904.759999999995</v>
       </c>
       <c r="Z20" s="2"/>
       <c r="AA20" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>50904.759999999995</v>
       </c>
       <c r="AB20" s="2"/>
@@ -5365,12 +5596,12 @@
         <v>28610</v>
       </c>
       <c r="E21" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>954</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>29564</v>
       </c>
       <c r="H21" s="2">
@@ -5382,34 +5613,34 @@
         <v>400</v>
       </c>
       <c r="J21" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1773.84</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L21" s="2">
         <v>0</v>
       </c>
       <c r="M21" s="2">
-        <f t="shared" ref="M21:M29" si="32">10%*D21</f>
+        <f t="shared" ref="M21:M29" si="36">10%*D21</f>
         <v>2861</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2861</v>
       </c>
       <c r="P21" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>37555.24</v>
       </c>
       <c r="Q21" s="2">
         <v>800</v>
       </c>
       <c r="R21" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5912.8</v>
       </c>
       <c r="S21" s="2">
@@ -5417,20 +5648,20 @@
       </c>
       <c r="T21" s="2"/>
       <c r="U21" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>3547.68</v>
       </c>
       <c r="V21" s="2"/>
       <c r="W21" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>15260.48</v>
       </c>
       <c r="X21" s="2">
-        <f>Y21+U21</f>
+        <f t="shared" si="32"/>
         <v>25842.44</v>
       </c>
       <c r="Y21" s="10">
-        <f>P21-W21</f>
+        <f t="shared" si="33"/>
         <v>22294.76</v>
       </c>
       <c r="Z21" s="2">
@@ -5438,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="AA21" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>22294.76</v>
       </c>
       <c r="AB21" s="2"/>
@@ -5452,12 +5683,12 @@
         <v>28610</v>
       </c>
       <c r="E22" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>954</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>29564</v>
       </c>
       <c r="H22" s="2">
@@ -5469,34 +5700,34 @@
         <v>400</v>
       </c>
       <c r="J22" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1773.84</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L22" s="2">
         <v>0</v>
       </c>
       <c r="M22" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>2861</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2861</v>
       </c>
       <c r="P22" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>37555.24</v>
       </c>
       <c r="Q22" s="2">
         <v>800</v>
       </c>
       <c r="R22" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5912.8</v>
       </c>
       <c r="S22" s="2">
@@ -5504,20 +5735,20 @@
       </c>
       <c r="T22" s="2"/>
       <c r="U22" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>3547.68</v>
       </c>
       <c r="V22" s="2"/>
       <c r="W22" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>15260.48</v>
       </c>
       <c r="X22" s="2">
-        <f>Y22+U22</f>
+        <f t="shared" si="32"/>
         <v>25842.44</v>
       </c>
       <c r="Y22" s="10">
-        <f>P22-W22</f>
+        <f t="shared" si="33"/>
         <v>22294.76</v>
       </c>
       <c r="Z22" s="2">
@@ -5525,7 +5756,7 @@
         <v>0</v>
       </c>
       <c r="AA22" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>22294.76</v>
       </c>
       <c r="AB22" s="2"/>
@@ -5539,12 +5770,12 @@
         <v>28610</v>
       </c>
       <c r="E23" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>954</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>29564</v>
       </c>
       <c r="H23" s="2">
@@ -5556,34 +5787,34 @@
         <v>400</v>
       </c>
       <c r="J23" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1773.84</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L23" s="2">
         <v>0</v>
       </c>
       <c r="M23" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>2861</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2861</v>
       </c>
       <c r="P23" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>37555.24</v>
       </c>
       <c r="Q23" s="2">
         <v>800</v>
       </c>
       <c r="R23" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5912.8</v>
       </c>
       <c r="S23" s="2">
@@ -5591,20 +5822,20 @@
       </c>
       <c r="T23" s="2"/>
       <c r="U23" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>3547.68</v>
       </c>
       <c r="V23" s="2"/>
       <c r="W23" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>15260.48</v>
       </c>
       <c r="X23" s="2">
-        <f>Y23+U23</f>
+        <f t="shared" si="32"/>
         <v>25842.44</v>
       </c>
       <c r="Y23" s="10">
-        <f>P23-W23</f>
+        <f t="shared" si="33"/>
         <v>22294.76</v>
       </c>
       <c r="Z23" s="2">
@@ -5612,7 +5843,7 @@
         <v>0</v>
       </c>
       <c r="AA23" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>22294.76</v>
       </c>
       <c r="AB23" s="2"/>
@@ -5626,12 +5857,12 @@
         <v>28610</v>
       </c>
       <c r="E24" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>954</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>29564</v>
       </c>
       <c r="H24" s="2">
@@ -5643,34 +5874,34 @@
         <v>400</v>
       </c>
       <c r="J24" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1773.84</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L24" s="2">
         <v>0</v>
       </c>
       <c r="M24" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>2861</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2861</v>
       </c>
       <c r="P24" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>37555.24</v>
       </c>
       <c r="Q24" s="2">
         <v>800</v>
       </c>
       <c r="R24" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5912.8</v>
       </c>
       <c r="S24" s="2">
@@ -5678,20 +5909,20 @@
       </c>
       <c r="T24" s="2"/>
       <c r="U24" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>3547.68</v>
       </c>
       <c r="V24" s="2"/>
       <c r="W24" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>15260.48</v>
       </c>
       <c r="X24" s="2">
-        <f>Y24+U24</f>
+        <f t="shared" si="32"/>
         <v>25842.44</v>
       </c>
       <c r="Y24" s="10">
-        <f>P24-W24</f>
+        <f t="shared" si="33"/>
         <v>22294.76</v>
       </c>
       <c r="Z24" s="2">
@@ -5699,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="AA24" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>22294.76</v>
       </c>
       <c r="AB24" s="2"/>
@@ -5713,12 +5944,12 @@
         <v>28610</v>
       </c>
       <c r="E25" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>954</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>29564</v>
       </c>
       <c r="H25" s="2">
@@ -5730,34 +5961,34 @@
         <v>400</v>
       </c>
       <c r="J25" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1773.84</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L25" s="2">
         <v>0</v>
       </c>
       <c r="M25" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>2861</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2861</v>
       </c>
       <c r="P25" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>37555.24</v>
       </c>
       <c r="Q25" s="2">
         <v>800</v>
       </c>
       <c r="R25" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5912.8</v>
       </c>
       <c r="S25" s="2">
@@ -5765,20 +5996,20 @@
       </c>
       <c r="T25" s="2"/>
       <c r="U25" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>3547.68</v>
       </c>
       <c r="V25" s="2"/>
       <c r="W25" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>15260.48</v>
       </c>
       <c r="X25" s="2">
-        <f>Y25+U25</f>
+        <f t="shared" si="32"/>
         <v>25842.44</v>
       </c>
       <c r="Y25" s="10">
-        <f>P25-W25</f>
+        <f t="shared" si="33"/>
         <v>22294.76</v>
       </c>
       <c r="Z25" s="2">
@@ -5786,7 +6017,7 @@
         <v>0</v>
       </c>
       <c r="AA25" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>22294.76</v>
       </c>
       <c r="AB25" s="2"/>
@@ -5800,12 +6031,12 @@
         <v>28610</v>
       </c>
       <c r="E26" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>954</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>29564</v>
       </c>
       <c r="H26" s="2">
@@ -5817,36 +6048,36 @@
         <v>400</v>
       </c>
       <c r="J26" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1773.84</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L26" s="2">
         <v>0</v>
       </c>
       <c r="M26" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>2861</v>
       </c>
       <c r="N26" s="2">
         <v>10000</v>
       </c>
       <c r="O26" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>12861</v>
       </c>
       <c r="P26" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>47555.24</v>
       </c>
       <c r="Q26" s="2">
         <v>800</v>
       </c>
       <c r="R26" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5912.8</v>
       </c>
       <c r="S26" s="2">
@@ -5854,20 +6085,20 @@
       </c>
       <c r="T26" s="2"/>
       <c r="U26" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>3547.68</v>
       </c>
       <c r="V26" s="2"/>
       <c r="W26" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>15260.48</v>
       </c>
       <c r="X26" s="2">
-        <f>Y26+U26</f>
+        <f t="shared" si="32"/>
         <v>35842.439999999995</v>
       </c>
       <c r="Y26" s="10">
-        <f>P26-W26</f>
+        <f t="shared" si="33"/>
         <v>32294.76</v>
       </c>
       <c r="Z26" s="2">
@@ -5875,7 +6106,7 @@
         <v>0</v>
       </c>
       <c r="AA26" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>32294.76</v>
       </c>
       <c r="AB26" s="2"/>
@@ -5889,12 +6120,12 @@
         <v>28610</v>
       </c>
       <c r="E27" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>954</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>29564</v>
       </c>
       <c r="H27" s="2">
@@ -5906,34 +6137,34 @@
         <v>400</v>
       </c>
       <c r="J27" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1773.84</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L27" s="2">
         <v>0</v>
       </c>
       <c r="M27" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>2861</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2861</v>
       </c>
       <c r="P27" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>37555.24</v>
       </c>
       <c r="Q27" s="2">
         <v>800</v>
       </c>
       <c r="R27" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5912.8</v>
       </c>
       <c r="S27" s="2">
@@ -5941,20 +6172,20 @@
       </c>
       <c r="T27" s="2"/>
       <c r="U27" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>3547.68</v>
       </c>
       <c r="V27" s="2"/>
       <c r="W27" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>15260.48</v>
       </c>
       <c r="X27" s="2">
-        <f>Y27+U27</f>
+        <f t="shared" si="32"/>
         <v>25842.44</v>
       </c>
       <c r="Y27" s="10">
-        <f>P27-W27</f>
+        <f t="shared" si="33"/>
         <v>22294.76</v>
       </c>
       <c r="Z27" s="2">
@@ -5962,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="AA27" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>22294.76</v>
       </c>
       <c r="AB27" s="2"/>
@@ -5976,12 +6207,12 @@
         <v>28610</v>
       </c>
       <c r="E28" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>954</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>29564</v>
       </c>
       <c r="H28" s="2">
@@ -5993,34 +6224,34 @@
         <v>400</v>
       </c>
       <c r="J28" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1773.84</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>34694.239999999998</v>
       </c>
       <c r="L28" s="2">
         <v>0</v>
       </c>
       <c r="M28" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>2861</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2861</v>
       </c>
       <c r="P28" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>37555.24</v>
       </c>
       <c r="Q28" s="2">
         <v>800</v>
       </c>
       <c r="R28" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5912.8</v>
       </c>
       <c r="S28" s="2">
@@ -6028,20 +6259,20 @@
       </c>
       <c r="T28" s="2"/>
       <c r="U28" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>3547.68</v>
       </c>
       <c r="V28" s="2"/>
       <c r="W28" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>15260.48</v>
       </c>
       <c r="X28" s="2">
-        <f>Y28+U28</f>
+        <f t="shared" si="32"/>
         <v>25842.44</v>
       </c>
       <c r="Y28" s="10">
-        <f>P28-W28</f>
+        <f t="shared" si="33"/>
         <v>22294.76</v>
       </c>
       <c r="Z28" s="2">
@@ -6049,7 +6280,7 @@
         <v>0</v>
       </c>
       <c r="AA28" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>22294.76</v>
       </c>
       <c r="AB28" s="2"/>
@@ -6068,7 +6299,7 @@
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>30518</v>
       </c>
       <c r="H29" s="2">
@@ -6080,34 +6311,34 @@
         <v>400</v>
       </c>
       <c r="J29" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1831.08</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>35800.880000000005</v>
       </c>
       <c r="L29" s="2">
         <v>0</v>
       </c>
       <c r="M29" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>2861</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2861</v>
       </c>
       <c r="P29" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>38661.880000000005</v>
       </c>
       <c r="Q29" s="2">
         <v>800</v>
       </c>
       <c r="R29" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>6103.6</v>
       </c>
       <c r="S29" s="2">
@@ -6115,20 +6346,20 @@
       </c>
       <c r="T29" s="2"/>
       <c r="U29" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>3662.16</v>
       </c>
       <c r="V29" s="2"/>
       <c r="W29" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>15565.76</v>
       </c>
       <c r="X29" s="2">
-        <f>Y29+U29</f>
+        <f t="shared" si="32"/>
         <v>26758.280000000002</v>
       </c>
       <c r="Y29" s="10">
-        <f>P29-W29</f>
+        <f t="shared" si="33"/>
         <v>23096.120000000003</v>
       </c>
       <c r="Z29" s="2">
@@ -6136,7 +6367,7 @@
         <v>0</v>
       </c>
       <c r="AA29" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>23096.120000000003</v>
       </c>
       <c r="AB29" s="2"/>
@@ -6186,7 +6417,7 @@
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="8">
-        <f t="shared" ref="G31:G42" si="33">SUM(D31:F31)</f>
+        <f t="shared" ref="G31:G42" si="37">SUM(D31:F31)</f>
         <v>35096</v>
       </c>
       <c r="H31" s="2">
@@ -6198,11 +6429,11 @@
         <v>400</v>
       </c>
       <c r="J31" s="2">
-        <f t="shared" ref="J31:J42" si="34">6%*G31</f>
+        <f t="shared" ref="J31:J42" si="38">6%*G31</f>
         <v>2105.7599999999998</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" ref="K31:K42" si="35">SUM(G31:J31)</f>
+        <f t="shared" ref="K31:K42" si="39">SUM(G31:J31)</f>
         <v>41111.360000000001</v>
       </c>
       <c r="L31" s="2">
@@ -6214,18 +6445,18 @@
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="4">
-        <f t="shared" ref="O31:O42" si="36">SUM(L31:N31)</f>
+        <f t="shared" ref="O31:O42" si="40">SUM(L31:N31)</f>
         <v>3290.2000000000003</v>
       </c>
       <c r="P31" s="8">
-        <f t="shared" ref="P31:P42" si="37">K31+O31</f>
+        <f t="shared" ref="P31:P42" si="41">K31+O31</f>
         <v>44401.56</v>
       </c>
       <c r="Q31" s="2">
         <v>800</v>
       </c>
       <c r="R31" s="2">
-        <f t="shared" ref="R31:R42" si="38">H31*2</f>
+        <f t="shared" ref="R31:R42" si="42">H31*2</f>
         <v>7019.2000000000007</v>
       </c>
       <c r="S31" s="2">
@@ -6233,20 +6464,20 @@
       </c>
       <c r="T31" s="2"/>
       <c r="U31" s="2">
-        <f t="shared" ref="U31:U42" si="39">J31*2</f>
+        <f t="shared" ref="U31:U42" si="43">J31*2</f>
         <v>4211.5199999999995</v>
       </c>
       <c r="V31" s="2"/>
       <c r="W31" s="4">
-        <f t="shared" ref="W31:W42" si="40">SUM(Q31:U31)</f>
+        <f t="shared" ref="W31:W42" si="44">SUM(Q31:U31)</f>
         <v>17030.72</v>
       </c>
       <c r="X31" s="2">
-        <f>Y31+U31</f>
+        <f t="shared" ref="X31:X42" si="45">Y31+U31</f>
         <v>31582.359999999997</v>
       </c>
       <c r="Y31" s="10">
-        <f>P31-W31</f>
+        <f t="shared" ref="Y31:Y42" si="46">P31-W31</f>
         <v>27370.839999999997</v>
       </c>
       <c r="Z31" s="2">
@@ -6254,7 +6485,7 @@
         <v>0</v>
       </c>
       <c r="AA31" s="2">
-        <f t="shared" ref="AA31:AA42" si="41">Y31-Z31</f>
+        <f t="shared" ref="AA31:AA42" si="47">Y31-Z31</f>
         <v>27370.839999999997</v>
       </c>
       <c r="AB31" s="2"/>
@@ -6268,12 +6499,12 @@
         <v>32902</v>
       </c>
       <c r="E32" s="4">
-        <f t="shared" ref="E32:E41" si="42">ROUNDUP(D32/30,0)*2</f>
+        <f t="shared" ref="E32:E41" si="48">ROUNDUP(D32/30,0)*2</f>
         <v>2194</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>35096</v>
       </c>
       <c r="H32" s="2">
@@ -6285,11 +6516,11 @@
         <v>400</v>
       </c>
       <c r="J32" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K32" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L32" s="2">
@@ -6301,18 +6532,18 @@
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P32" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>44401.56</v>
       </c>
       <c r="Q32" s="2">
         <v>800</v>
       </c>
       <c r="R32" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S32" s="2">
@@ -6320,20 +6551,20 @@
       </c>
       <c r="T32" s="2"/>
       <c r="U32" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>4211.5199999999995</v>
       </c>
       <c r="V32" s="2"/>
       <c r="W32" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>17030.72</v>
       </c>
       <c r="X32" s="2">
-        <f>Y32+U32</f>
+        <f t="shared" si="45"/>
         <v>31582.359999999997</v>
       </c>
       <c r="Y32" s="10">
-        <f>P32-W32</f>
+        <f t="shared" si="46"/>
         <v>27370.839999999997</v>
       </c>
       <c r="Z32" s="2">
@@ -6341,7 +6572,7 @@
         <v>0</v>
       </c>
       <c r="AA32" s="2">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>27370.839999999997</v>
       </c>
       <c r="AB32" s="2"/>
@@ -6355,12 +6586,12 @@
         <v>32902</v>
       </c>
       <c r="E33" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="48"/>
         <v>2194</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>35096</v>
       </c>
       <c r="H33" s="2">
@@ -6372,11 +6603,11 @@
         <v>400</v>
       </c>
       <c r="J33" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K33" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L33" s="2">
@@ -6388,18 +6619,18 @@
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>36192.199999999997</v>
       </c>
       <c r="P33" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>77303.56</v>
       </c>
       <c r="Q33" s="2">
         <v>800</v>
       </c>
       <c r="R33" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S33" s="2">
@@ -6407,25 +6638,25 @@
       </c>
       <c r="T33" s="2"/>
       <c r="U33" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>4211.5199999999995</v>
       </c>
       <c r="V33" s="2"/>
       <c r="W33" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>17030.72</v>
       </c>
       <c r="X33" s="2">
-        <f>Y33+U33</f>
+        <f t="shared" si="45"/>
         <v>64484.359999999993</v>
       </c>
       <c r="Y33" s="10">
-        <f>P33-W33</f>
+        <f t="shared" si="46"/>
         <v>60272.84</v>
       </c>
       <c r="Z33" s="2"/>
       <c r="AA33" s="2">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>60272.84</v>
       </c>
       <c r="AB33" s="2"/>
@@ -6439,12 +6670,12 @@
         <v>32902</v>
       </c>
       <c r="E34" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="48"/>
         <v>2194</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>35096</v>
       </c>
       <c r="H34" s="2">
@@ -6456,34 +6687,34 @@
         <v>400</v>
       </c>
       <c r="J34" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K34" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L34" s="2">
         <v>0</v>
       </c>
       <c r="M34" s="2">
-        <f t="shared" ref="M34:M42" si="43">10%*D34</f>
+        <f t="shared" ref="M34:M42" si="49">10%*D34</f>
         <v>3290.2000000000003</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P34" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>44401.56</v>
       </c>
       <c r="Q34" s="2">
         <v>800</v>
       </c>
       <c r="R34" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S34" s="2">
@@ -6491,20 +6722,20 @@
       </c>
       <c r="T34" s="2"/>
       <c r="U34" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>4211.5199999999995</v>
       </c>
       <c r="V34" s="2"/>
       <c r="W34" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>17030.72</v>
       </c>
       <c r="X34" s="2">
-        <f>Y34+U34</f>
+        <f t="shared" si="45"/>
         <v>31582.359999999997</v>
       </c>
       <c r="Y34" s="10">
-        <f>P34-W34</f>
+        <f t="shared" si="46"/>
         <v>27370.839999999997</v>
       </c>
       <c r="Z34" s="2">
@@ -6512,7 +6743,7 @@
         <v>0</v>
       </c>
       <c r="AA34" s="2">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>27370.839999999997</v>
       </c>
       <c r="AB34" s="2"/>
@@ -6526,12 +6757,12 @@
         <v>32902</v>
       </c>
       <c r="E35" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="48"/>
         <v>2194</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>35096</v>
       </c>
       <c r="H35" s="2">
@@ -6543,34 +6774,34 @@
         <v>400</v>
       </c>
       <c r="J35" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K35" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L35" s="2">
         <v>0</v>
       </c>
       <c r="M35" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P35" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>44401.56</v>
       </c>
       <c r="Q35" s="2">
         <v>800</v>
       </c>
       <c r="R35" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S35" s="2">
@@ -6578,20 +6809,20 @@
       </c>
       <c r="T35" s="2"/>
       <c r="U35" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>4211.5199999999995</v>
       </c>
       <c r="V35" s="2"/>
       <c r="W35" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>17030.72</v>
       </c>
       <c r="X35" s="2">
-        <f>Y35+U35</f>
+        <f t="shared" si="45"/>
         <v>31582.359999999997</v>
       </c>
       <c r="Y35" s="10">
-        <f>P35-W35</f>
+        <f t="shared" si="46"/>
         <v>27370.839999999997</v>
       </c>
       <c r="Z35" s="2">
@@ -6599,7 +6830,7 @@
         <v>0</v>
       </c>
       <c r="AA35" s="2">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>27370.839999999997</v>
       </c>
       <c r="AB35" s="2"/>
@@ -6613,12 +6844,12 @@
         <v>32902</v>
       </c>
       <c r="E36" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="48"/>
         <v>2194</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>35096</v>
       </c>
       <c r="H36" s="2">
@@ -6630,34 +6861,34 @@
         <v>400</v>
       </c>
       <c r="J36" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K36" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L36" s="2">
         <v>0</v>
       </c>
       <c r="M36" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P36" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>44401.56</v>
       </c>
       <c r="Q36" s="2">
         <v>800</v>
       </c>
       <c r="R36" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S36" s="2">
@@ -6665,20 +6896,20 @@
       </c>
       <c r="T36" s="2"/>
       <c r="U36" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>4211.5199999999995</v>
       </c>
       <c r="V36" s="2"/>
       <c r="W36" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>17030.72</v>
       </c>
       <c r="X36" s="2">
-        <f>Y36+U36</f>
+        <f t="shared" si="45"/>
         <v>31582.359999999997</v>
       </c>
       <c r="Y36" s="10">
-        <f>P36-W36</f>
+        <f t="shared" si="46"/>
         <v>27370.839999999997</v>
       </c>
       <c r="Z36" s="2">
@@ -6686,7 +6917,7 @@
         <v>0</v>
       </c>
       <c r="AA36" s="2">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>27370.839999999997</v>
       </c>
       <c r="AB36" s="2"/>
@@ -6700,12 +6931,12 @@
         <v>32902</v>
       </c>
       <c r="E37" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="48"/>
         <v>2194</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>35096</v>
       </c>
       <c r="H37" s="2">
@@ -6717,34 +6948,34 @@
         <v>400</v>
       </c>
       <c r="J37" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K37" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L37" s="2">
         <v>0</v>
       </c>
       <c r="M37" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P37" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>44401.56</v>
       </c>
       <c r="Q37" s="2">
         <v>800</v>
       </c>
       <c r="R37" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S37" s="2">
@@ -6752,20 +6983,20 @@
       </c>
       <c r="T37" s="2"/>
       <c r="U37" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>4211.5199999999995</v>
       </c>
       <c r="V37" s="2"/>
       <c r="W37" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>17030.72</v>
       </c>
       <c r="X37" s="2">
-        <f>Y37+U37</f>
+        <f t="shared" si="45"/>
         <v>31582.359999999997</v>
       </c>
       <c r="Y37" s="10">
-        <f>P37-W37</f>
+        <f t="shared" si="46"/>
         <v>27370.839999999997</v>
       </c>
       <c r="Z37" s="2">
@@ -6773,7 +7004,7 @@
         <v>0</v>
       </c>
       <c r="AA37" s="2">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>27370.839999999997</v>
       </c>
       <c r="AB37" s="2"/>
@@ -6787,12 +7018,12 @@
         <v>32902</v>
       </c>
       <c r="E38" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="48"/>
         <v>2194</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>35096</v>
       </c>
       <c r="H38" s="2">
@@ -6804,34 +7035,34 @@
         <v>400</v>
       </c>
       <c r="J38" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K38" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L38" s="2">
         <v>0</v>
       </c>
       <c r="M38" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P38" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>44401.56</v>
       </c>
       <c r="Q38" s="2">
         <v>800</v>
       </c>
       <c r="R38" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S38" s="2">
@@ -6839,20 +7070,20 @@
       </c>
       <c r="T38" s="2"/>
       <c r="U38" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>4211.5199999999995</v>
       </c>
       <c r="V38" s="2"/>
       <c r="W38" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>17030.72</v>
       </c>
       <c r="X38" s="2">
-        <f>Y38+U38</f>
+        <f t="shared" si="45"/>
         <v>31582.359999999997</v>
       </c>
       <c r="Y38" s="10">
-        <f>P38-W38</f>
+        <f t="shared" si="46"/>
         <v>27370.839999999997</v>
       </c>
       <c r="Z38" s="2">
@@ -6860,7 +7091,7 @@
         <v>0</v>
       </c>
       <c r="AA38" s="2">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>27370.839999999997</v>
       </c>
       <c r="AB38" s="2"/>
@@ -6874,12 +7105,12 @@
         <v>32902</v>
       </c>
       <c r="E39" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="48"/>
         <v>2194</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>35096</v>
       </c>
       <c r="H39" s="2">
@@ -6891,36 +7122,36 @@
         <v>400</v>
       </c>
       <c r="J39" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K39" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L39" s="2">
         <v>0</v>
       </c>
       <c r="M39" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N39" s="2">
         <v>10000</v>
       </c>
       <c r="O39" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>13290.2</v>
       </c>
       <c r="P39" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>54401.56</v>
       </c>
       <c r="Q39" s="2">
         <v>800</v>
       </c>
       <c r="R39" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S39" s="2">
@@ -6928,20 +7159,20 @@
       </c>
       <c r="T39" s="2"/>
       <c r="U39" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>4211.5199999999995</v>
       </c>
       <c r="V39" s="2"/>
       <c r="W39" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>17030.72</v>
       </c>
       <c r="X39" s="2">
-        <f>Y39+U39</f>
+        <f t="shared" si="45"/>
         <v>41582.359999999993</v>
       </c>
       <c r="Y39" s="10">
-        <f>P39-W39</f>
+        <f t="shared" si="46"/>
         <v>37370.839999999997</v>
       </c>
       <c r="Z39" s="2">
@@ -6949,7 +7180,7 @@
         <v>0</v>
       </c>
       <c r="AA39" s="2">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>37370.839999999997</v>
       </c>
       <c r="AB39" s="2"/>
@@ -6963,12 +7194,12 @@
         <v>32902</v>
       </c>
       <c r="E40" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="48"/>
         <v>2194</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>35096</v>
       </c>
       <c r="H40" s="2">
@@ -6980,34 +7211,34 @@
         <v>400</v>
       </c>
       <c r="J40" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K40" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L40" s="2">
         <v>0</v>
       </c>
       <c r="M40" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P40" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>44401.56</v>
       </c>
       <c r="Q40" s="2">
         <v>800</v>
       </c>
       <c r="R40" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S40" s="2">
@@ -7015,20 +7246,20 @@
       </c>
       <c r="T40" s="2"/>
       <c r="U40" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>4211.5199999999995</v>
       </c>
       <c r="V40" s="2"/>
       <c r="W40" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>17030.72</v>
       </c>
       <c r="X40" s="2">
-        <f>Y40+U40</f>
+        <f t="shared" si="45"/>
         <v>31582.359999999997</v>
       </c>
       <c r="Y40" s="10">
-        <f>P40-W40</f>
+        <f t="shared" si="46"/>
         <v>27370.839999999997</v>
       </c>
       <c r="Z40" s="2">
@@ -7036,7 +7267,7 @@
         <v>0</v>
       </c>
       <c r="AA40" s="2">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>27370.839999999997</v>
       </c>
       <c r="AB40" s="2"/>
@@ -7050,12 +7281,12 @@
         <v>32902</v>
       </c>
       <c r="E41" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="48"/>
         <v>2194</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>35096</v>
       </c>
       <c r="H41" s="2">
@@ -7067,34 +7298,34 @@
         <v>400</v>
       </c>
       <c r="J41" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>2105.7599999999998</v>
       </c>
       <c r="K41" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>41111.360000000001</v>
       </c>
       <c r="L41" s="2">
         <v>0</v>
       </c>
       <c r="M41" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P41" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>44401.56</v>
       </c>
       <c r="Q41" s="2">
         <v>800</v>
       </c>
       <c r="R41" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>7019.2000000000007</v>
       </c>
       <c r="S41" s="2">
@@ -7102,20 +7333,20 @@
       </c>
       <c r="T41" s="2"/>
       <c r="U41" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>4211.5199999999995</v>
       </c>
       <c r="V41" s="2"/>
       <c r="W41" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>17030.72</v>
       </c>
       <c r="X41" s="2">
-        <f>Y41+U41</f>
+        <f t="shared" si="45"/>
         <v>31582.359999999997</v>
       </c>
       <c r="Y41" s="10">
-        <f>P41-W41</f>
+        <f t="shared" si="46"/>
         <v>27370.839999999997</v>
       </c>
       <c r="Z41" s="2">
@@ -7123,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="AA41" s="2">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>27370.839999999997</v>
       </c>
       <c r="AB41" s="2"/>
@@ -7142,7 +7373,7 @@
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>36193</v>
       </c>
       <c r="H42" s="2">
@@ -7154,34 +7385,34 @@
         <v>400</v>
       </c>
       <c r="J42" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>2171.58</v>
       </c>
       <c r="K42" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L42" s="2">
         <v>0</v>
       </c>
       <c r="M42" s="2">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P42" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>45674.080000000002</v>
       </c>
       <c r="Q42" s="2">
         <v>800</v>
       </c>
       <c r="R42" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>7238.6</v>
       </c>
       <c r="S42" s="2">
@@ -7189,20 +7420,20 @@
       </c>
       <c r="T42" s="2"/>
       <c r="U42" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>4343.16</v>
       </c>
       <c r="V42" s="2"/>
       <c r="W42" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>17381.760000000002</v>
       </c>
       <c r="X42" s="2">
-        <f>Y42+U42</f>
+        <f t="shared" si="45"/>
         <v>32635.48</v>
       </c>
       <c r="Y42" s="10">
-        <f>P42-W42</f>
+        <f t="shared" si="46"/>
         <v>28292.32</v>
       </c>
       <c r="Z42" s="2">
@@ -7210,7 +7441,7 @@
         <v>0</v>
       </c>
       <c r="AA42" s="2">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>28292.32</v>
       </c>
       <c r="AB42" s="2"/>
@@ -7260,7 +7491,7 @@
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="8">
-        <f t="shared" ref="G44:G55" si="44">SUM(D44:F44)</f>
+        <f t="shared" ref="G44:G55" si="50">SUM(D44:F44)</f>
         <v>36193</v>
       </c>
       <c r="H44" s="2">
@@ -7272,11 +7503,11 @@
         <v>400</v>
       </c>
       <c r="J44" s="2">
-        <f t="shared" ref="J44:J55" si="45">6%*G44</f>
+        <f t="shared" ref="J44:J55" si="51">6%*G44</f>
         <v>2171.58</v>
       </c>
       <c r="K44" s="8">
-        <f t="shared" ref="K44:K55" si="46">SUM(G44:J44)</f>
+        <f t="shared" ref="K44:K55" si="52">SUM(G44:J44)</f>
         <v>42383.880000000005</v>
       </c>
       <c r="L44" s="2">
@@ -7288,18 +7519,18 @@
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="4">
-        <f t="shared" ref="O44:O55" si="47">SUM(L44:N44)</f>
+        <f t="shared" ref="O44:O55" si="53">SUM(L44:N44)</f>
         <v>3290.2000000000003</v>
       </c>
       <c r="P44" s="8">
-        <f t="shared" ref="P44:P55" si="48">K44+O44</f>
+        <f t="shared" ref="P44:P55" si="54">K44+O44</f>
         <v>45674.080000000002</v>
       </c>
       <c r="Q44" s="2">
         <v>800</v>
       </c>
       <c r="R44" s="2">
-        <f t="shared" ref="R44:R55" si="49">H44*2</f>
+        <f t="shared" ref="R44:R55" si="55">H44*2</f>
         <v>7238.6</v>
       </c>
       <c r="S44" s="2">
@@ -7307,20 +7538,20 @@
       </c>
       <c r="T44" s="2"/>
       <c r="U44" s="2">
-        <f t="shared" ref="U44:U55" si="50">J44*2</f>
+        <f t="shared" ref="U44:U55" si="56">J44*2</f>
         <v>4343.16</v>
       </c>
       <c r="V44" s="2"/>
       <c r="W44" s="4">
-        <f t="shared" ref="W44:W55" si="51">SUM(Q44:U44)</f>
+        <f t="shared" ref="W44:W55" si="57">SUM(Q44:U44)</f>
         <v>17381.760000000002</v>
       </c>
       <c r="X44" s="2">
-        <f>Y44+U44</f>
+        <f t="shared" ref="X44:X55" si="58">Y44+U44</f>
         <v>32635.48</v>
       </c>
       <c r="Y44" s="10">
-        <f>P44-W44</f>
+        <f t="shared" ref="Y44:Y55" si="59">P44-W44</f>
         <v>28292.32</v>
       </c>
       <c r="Z44" s="2">
@@ -7328,7 +7559,7 @@
         <v>0</v>
       </c>
       <c r="AA44" s="2">
-        <f t="shared" ref="AA44:AA55" si="52">Y44-Z44</f>
+        <f t="shared" ref="AA44:AA55" si="60">Y44-Z44</f>
         <v>28292.32</v>
       </c>
       <c r="AB44" s="2"/>
@@ -7342,12 +7573,12 @@
         <v>32902</v>
       </c>
       <c r="E45" s="4">
-        <f t="shared" ref="E45:E54" si="53">ROUNDUP(D45/30,0)*3</f>
+        <f t="shared" ref="E45:E54" si="61">ROUNDUP(D45/30,0)*3</f>
         <v>3291</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>36193</v>
       </c>
       <c r="H45" s="2">
@@ -7359,11 +7590,11 @@
         <v>400</v>
       </c>
       <c r="J45" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>2171.58</v>
       </c>
       <c r="K45" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L45" s="2">
@@ -7375,18 +7606,18 @@
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P45" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>45674.080000000002</v>
       </c>
       <c r="Q45" s="2">
         <v>800</v>
       </c>
       <c r="R45" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>7238.6</v>
       </c>
       <c r="S45" s="2">
@@ -7394,20 +7625,20 @@
       </c>
       <c r="T45" s="2"/>
       <c r="U45" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>4343.16</v>
       </c>
       <c r="V45" s="2"/>
       <c r="W45" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>17381.760000000002</v>
       </c>
       <c r="X45" s="2">
-        <f>Y45+U45</f>
+        <f t="shared" si="58"/>
         <v>32635.48</v>
       </c>
       <c r="Y45" s="10">
-        <f>P45-W45</f>
+        <f t="shared" si="59"/>
         <v>28292.32</v>
       </c>
       <c r="Z45" s="2">
@@ -7415,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="AA45" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>28292.32</v>
       </c>
       <c r="AB45" s="2"/>
@@ -7429,12 +7660,12 @@
         <v>32902</v>
       </c>
       <c r="E46" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>3291</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>36193</v>
       </c>
       <c r="H46" s="2">
@@ -7446,11 +7677,11 @@
         <v>400</v>
       </c>
       <c r="J46" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>2171.58</v>
       </c>
       <c r="K46" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L46" s="2">
@@ -7462,18 +7693,18 @@
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>36192.199999999997</v>
       </c>
       <c r="P46" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>78576.08</v>
       </c>
       <c r="Q46" s="2">
         <v>800</v>
       </c>
       <c r="R46" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>7238.6</v>
       </c>
       <c r="S46" s="2">
@@ -7481,25 +7712,25 @@
       </c>
       <c r="T46" s="2"/>
       <c r="U46" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>4343.16</v>
       </c>
       <c r="V46" s="2"/>
       <c r="W46" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>17381.760000000002</v>
       </c>
       <c r="X46" s="2">
-        <f>Y46+U46</f>
+        <f t="shared" si="58"/>
         <v>65537.48</v>
       </c>
       <c r="Y46" s="10">
-        <f>P46-W46</f>
+        <f t="shared" si="59"/>
         <v>61194.32</v>
       </c>
       <c r="Z46" s="2"/>
       <c r="AA46" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>61194.32</v>
       </c>
       <c r="AB46" s="2"/>
@@ -7513,12 +7744,12 @@
         <v>32902</v>
       </c>
       <c r="E47" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>3291</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>36193</v>
       </c>
       <c r="H47" s="2">
@@ -7530,34 +7761,34 @@
         <v>400</v>
       </c>
       <c r="J47" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>2171.58</v>
       </c>
       <c r="K47" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L47" s="2">
         <v>0</v>
       </c>
       <c r="M47" s="2">
-        <f t="shared" ref="M47:M55" si="54">10%*D47</f>
+        <f t="shared" ref="M47:M55" si="62">10%*D47</f>
         <v>3290.2000000000003</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P47" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>45674.080000000002</v>
       </c>
       <c r="Q47" s="2">
         <v>800</v>
       </c>
       <c r="R47" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>7238.6</v>
       </c>
       <c r="S47" s="2">
@@ -7565,20 +7796,20 @@
       </c>
       <c r="T47" s="2"/>
       <c r="U47" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>4343.16</v>
       </c>
       <c r="V47" s="2"/>
       <c r="W47" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>17381.760000000002</v>
       </c>
       <c r="X47" s="2">
-        <f>Y47+U47</f>
+        <f t="shared" si="58"/>
         <v>32635.48</v>
       </c>
       <c r="Y47" s="10">
-        <f>P47-W47</f>
+        <f t="shared" si="59"/>
         <v>28292.32</v>
       </c>
       <c r="Z47" s="2">
@@ -7586,7 +7817,7 @@
         <v>0</v>
       </c>
       <c r="AA47" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>28292.32</v>
       </c>
       <c r="AB47" s="2"/>
@@ -7600,12 +7831,12 @@
         <v>32902</v>
       </c>
       <c r="E48" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>3291</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>36193</v>
       </c>
       <c r="H48" s="2">
@@ -7617,34 +7848,34 @@
         <v>400</v>
       </c>
       <c r="J48" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>2171.58</v>
       </c>
       <c r="K48" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L48" s="2">
         <v>0</v>
       </c>
       <c r="M48" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P48" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>45674.080000000002</v>
       </c>
       <c r="Q48" s="2">
         <v>800</v>
       </c>
       <c r="R48" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>7238.6</v>
       </c>
       <c r="S48" s="2">
@@ -7652,20 +7883,20 @@
       </c>
       <c r="T48" s="2"/>
       <c r="U48" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>4343.16</v>
       </c>
       <c r="V48" s="2"/>
       <c r="W48" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>17381.760000000002</v>
       </c>
       <c r="X48" s="2">
-        <f>Y48+U48</f>
+        <f t="shared" si="58"/>
         <v>32635.48</v>
       </c>
       <c r="Y48" s="10">
-        <f>P48-W48</f>
+        <f t="shared" si="59"/>
         <v>28292.32</v>
       </c>
       <c r="Z48" s="2">
@@ -7673,7 +7904,7 @@
         <v>0</v>
       </c>
       <c r="AA48" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>28292.32</v>
       </c>
       <c r="AB48" s="2"/>
@@ -7687,12 +7918,12 @@
         <v>32902</v>
       </c>
       <c r="E49" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>3291</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>36193</v>
       </c>
       <c r="H49" s="2">
@@ -7704,34 +7935,34 @@
         <v>400</v>
       </c>
       <c r="J49" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>2171.58</v>
       </c>
       <c r="K49" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L49" s="2">
         <v>0</v>
       </c>
       <c r="M49" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P49" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>45674.080000000002</v>
       </c>
       <c r="Q49" s="2">
         <v>800</v>
       </c>
       <c r="R49" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>7238.6</v>
       </c>
       <c r="S49" s="2">
@@ -7739,20 +7970,20 @@
       </c>
       <c r="T49" s="2"/>
       <c r="U49" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>4343.16</v>
       </c>
       <c r="V49" s="2"/>
       <c r="W49" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>17381.760000000002</v>
       </c>
       <c r="X49" s="2">
-        <f>Y49+U49</f>
+        <f t="shared" si="58"/>
         <v>32635.48</v>
       </c>
       <c r="Y49" s="10">
-        <f>P49-W49</f>
+        <f t="shared" si="59"/>
         <v>28292.32</v>
       </c>
       <c r="Z49" s="2">
@@ -7760,7 +7991,7 @@
         <v>0</v>
       </c>
       <c r="AA49" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>28292.32</v>
       </c>
       <c r="AB49" s="2"/>
@@ -7774,12 +8005,12 @@
         <v>32902</v>
       </c>
       <c r="E50" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>3291</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>36193</v>
       </c>
       <c r="H50" s="2">
@@ -7791,34 +8022,34 @@
         <v>400</v>
       </c>
       <c r="J50" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>2171.58</v>
       </c>
       <c r="K50" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L50" s="2">
         <v>0</v>
       </c>
       <c r="M50" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P50" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>45674.080000000002</v>
       </c>
       <c r="Q50" s="2">
         <v>800</v>
       </c>
       <c r="R50" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>7238.6</v>
       </c>
       <c r="S50" s="2">
@@ -7826,20 +8057,20 @@
       </c>
       <c r="T50" s="2"/>
       <c r="U50" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>4343.16</v>
       </c>
       <c r="V50" s="2"/>
       <c r="W50" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>17381.760000000002</v>
       </c>
       <c r="X50" s="2">
-        <f>Y50+U50</f>
+        <f t="shared" si="58"/>
         <v>32635.48</v>
       </c>
       <c r="Y50" s="10">
-        <f>P50-W50</f>
+        <f t="shared" si="59"/>
         <v>28292.32</v>
       </c>
       <c r="Z50" s="2">
@@ -7847,7 +8078,7 @@
         <v>0</v>
       </c>
       <c r="AA50" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>28292.32</v>
       </c>
       <c r="AB50" s="2"/>
@@ -7861,12 +8092,12 @@
         <v>32902</v>
       </c>
       <c r="E51" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>3291</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>36193</v>
       </c>
       <c r="H51" s="2">
@@ -7878,34 +8109,34 @@
         <v>400</v>
       </c>
       <c r="J51" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>2171.58</v>
       </c>
       <c r="K51" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L51" s="2">
         <v>0</v>
       </c>
       <c r="M51" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P51" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>45674.080000000002</v>
       </c>
       <c r="Q51" s="2">
         <v>800</v>
       </c>
       <c r="R51" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>7238.6</v>
       </c>
       <c r="S51" s="2">
@@ -7913,20 +8144,20 @@
       </c>
       <c r="T51" s="2"/>
       <c r="U51" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>4343.16</v>
       </c>
       <c r="V51" s="2"/>
       <c r="W51" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>17381.760000000002</v>
       </c>
       <c r="X51" s="2">
-        <f>Y51+U51</f>
+        <f t="shared" si="58"/>
         <v>32635.48</v>
       </c>
       <c r="Y51" s="10">
-        <f>P51-W51</f>
+        <f t="shared" si="59"/>
         <v>28292.32</v>
       </c>
       <c r="Z51" s="2">
@@ -7934,7 +8165,7 @@
         <v>0</v>
       </c>
       <c r="AA51" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>28292.32</v>
       </c>
       <c r="AB51" s="2"/>
@@ -7948,12 +8179,12 @@
         <v>32902</v>
       </c>
       <c r="E52" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>3291</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>36193</v>
       </c>
       <c r="H52" s="2">
@@ -7965,36 +8196,36 @@
         <v>400</v>
       </c>
       <c r="J52" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>2171.58</v>
       </c>
       <c r="K52" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L52" s="2">
         <v>0</v>
       </c>
       <c r="M52" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N52" s="2">
         <v>10000</v>
       </c>
       <c r="O52" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>13290.2</v>
       </c>
       <c r="P52" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>55674.080000000002</v>
       </c>
       <c r="Q52" s="2">
         <v>800</v>
       </c>
       <c r="R52" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>7238.6</v>
       </c>
       <c r="S52" s="2">
@@ -8002,20 +8233,20 @@
       </c>
       <c r="T52" s="2"/>
       <c r="U52" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>4343.16</v>
       </c>
       <c r="V52" s="2"/>
       <c r="W52" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>17381.760000000002</v>
       </c>
       <c r="X52" s="2">
-        <f>Y52+U52</f>
+        <f t="shared" si="58"/>
         <v>42635.479999999996</v>
       </c>
       <c r="Y52" s="10">
-        <f>P52-W52</f>
+        <f t="shared" si="59"/>
         <v>38292.32</v>
       </c>
       <c r="Z52" s="2">
@@ -8023,7 +8254,7 @@
         <v>0</v>
       </c>
       <c r="AA52" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>38292.32</v>
       </c>
       <c r="AB52" s="2"/>
@@ -8037,12 +8268,12 @@
         <v>32902</v>
       </c>
       <c r="E53" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>3291</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>36193</v>
       </c>
       <c r="H53" s="2">
@@ -8054,34 +8285,34 @@
         <v>400</v>
       </c>
       <c r="J53" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>2171.58</v>
       </c>
       <c r="K53" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L53" s="2">
         <v>0</v>
       </c>
       <c r="M53" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P53" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>45674.080000000002</v>
       </c>
       <c r="Q53" s="2">
         <v>800</v>
       </c>
       <c r="R53" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>7238.6</v>
       </c>
       <c r="S53" s="2">
@@ -8089,20 +8320,20 @@
       </c>
       <c r="T53" s="2"/>
       <c r="U53" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>4343.16</v>
       </c>
       <c r="V53" s="2"/>
       <c r="W53" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>17381.760000000002</v>
       </c>
       <c r="X53" s="2">
-        <f>Y53+U53</f>
+        <f t="shared" si="58"/>
         <v>32635.48</v>
       </c>
       <c r="Y53" s="10">
-        <f>P53-W53</f>
+        <f t="shared" si="59"/>
         <v>28292.32</v>
       </c>
       <c r="Z53" s="2">
@@ -8110,7 +8341,7 @@
         <v>0</v>
       </c>
       <c r="AA53" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>28292.32</v>
       </c>
       <c r="AB53" s="2"/>
@@ -8124,12 +8355,12 @@
         <v>32902</v>
       </c>
       <c r="E54" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="61"/>
         <v>3291</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>36193</v>
       </c>
       <c r="H54" s="2">
@@ -8141,34 +8372,34 @@
         <v>400</v>
       </c>
       <c r="J54" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>2171.58</v>
       </c>
       <c r="K54" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>42383.880000000005</v>
       </c>
       <c r="L54" s="2">
         <v>0</v>
       </c>
       <c r="M54" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P54" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>45674.080000000002</v>
       </c>
       <c r="Q54" s="2">
         <v>800</v>
       </c>
       <c r="R54" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>7238.6</v>
       </c>
       <c r="S54" s="2">
@@ -8176,20 +8407,20 @@
       </c>
       <c r="T54" s="2"/>
       <c r="U54" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>4343.16</v>
       </c>
       <c r="V54" s="2"/>
       <c r="W54" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>17381.760000000002</v>
       </c>
       <c r="X54" s="2">
-        <f>Y54+U54</f>
+        <f t="shared" si="58"/>
         <v>32635.48</v>
       </c>
       <c r="Y54" s="10">
-        <f>P54-W54</f>
+        <f t="shared" si="59"/>
         <v>28292.32</v>
       </c>
       <c r="Z54" s="2">
@@ -8197,7 +8428,7 @@
         <v>0</v>
       </c>
       <c r="AA54" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>28292.32</v>
       </c>
       <c r="AB54" s="2"/>
@@ -8211,12 +8442,12 @@
         <v>32902</v>
       </c>
       <c r="E55" s="4">
-        <f t="shared" ref="E55:E67" si="55">ROUNDUP(D55/30,0)*4</f>
+        <f t="shared" ref="E55:E67" si="63">ROUNDUP(D55/30,0)*4</f>
         <v>4388</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>37290</v>
       </c>
       <c r="H55" s="2">
@@ -8228,34 +8459,34 @@
         <v>400</v>
       </c>
       <c r="J55" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>2237.4</v>
       </c>
       <c r="K55" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>43656.4</v>
       </c>
       <c r="L55" s="2">
         <v>0</v>
       </c>
       <c r="M55" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="62"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P55" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>46946.6</v>
       </c>
       <c r="Q55" s="2">
         <v>800</v>
       </c>
       <c r="R55" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>7458</v>
       </c>
       <c r="S55" s="2">
@@ -8263,20 +8494,20 @@
       </c>
       <c r="T55" s="2"/>
       <c r="U55" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>4474.8</v>
       </c>
       <c r="V55" s="2"/>
       <c r="W55" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>17732.8</v>
       </c>
       <c r="X55" s="2">
-        <f>Y55+U55</f>
+        <f t="shared" si="58"/>
         <v>33688.6</v>
       </c>
       <c r="Y55" s="10">
-        <f>P55-W55</f>
+        <f t="shared" si="59"/>
         <v>29213.8</v>
       </c>
       <c r="Z55" s="2">
@@ -8284,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="AA55" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>29213.8</v>
       </c>
       <c r="AB55" s="2"/>
@@ -8329,12 +8560,12 @@
         <v>32902</v>
       </c>
       <c r="E57" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>4388</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="8">
-        <f t="shared" ref="G57:G68" si="56">SUM(D57:F57)</f>
+        <f t="shared" ref="G57:G68" si="64">SUM(D57:F57)</f>
         <v>37290</v>
       </c>
       <c r="H57" s="2">
@@ -8346,11 +8577,11 @@
         <v>400</v>
       </c>
       <c r="J57" s="2">
-        <f t="shared" ref="J57:J68" si="57">6%*G57</f>
+        <f t="shared" ref="J57:J68" si="65">6%*G57</f>
         <v>2237.4</v>
       </c>
       <c r="K57" s="8">
-        <f t="shared" ref="K57:K68" si="58">SUM(G57:J57)</f>
+        <f t="shared" ref="K57:K68" si="66">SUM(G57:J57)</f>
         <v>43656.4</v>
       </c>
       <c r="L57" s="2">
@@ -8362,18 +8593,18 @@
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="4">
-        <f t="shared" ref="O57:O68" si="59">SUM(L57:N57)</f>
+        <f t="shared" ref="O57:O68" si="67">SUM(L57:N57)</f>
         <v>3290.2000000000003</v>
       </c>
       <c r="P57" s="8">
-        <f t="shared" ref="P57:P68" si="60">K57+O57</f>
+        <f t="shared" ref="P57:P68" si="68">K57+O57</f>
         <v>46946.6</v>
       </c>
       <c r="Q57" s="2">
         <v>800</v>
       </c>
       <c r="R57" s="2">
-        <f t="shared" ref="R57:R68" si="61">H57*2</f>
+        <f t="shared" ref="R57:R68" si="69">H57*2</f>
         <v>7458</v>
       </c>
       <c r="S57" s="2">
@@ -8381,20 +8612,20 @@
       </c>
       <c r="T57" s="2"/>
       <c r="U57" s="2">
-        <f t="shared" ref="U57:U68" si="62">J57*2</f>
+        <f t="shared" ref="U57:U68" si="70">J57*2</f>
         <v>4474.8</v>
       </c>
       <c r="V57" s="2"/>
       <c r="W57" s="4">
-        <f t="shared" ref="W57:W68" si="63">SUM(Q57:U57)</f>
+        <f t="shared" ref="W57:W68" si="71">SUM(Q57:U57)</f>
         <v>17732.8</v>
       </c>
       <c r="X57" s="2">
-        <f>Y57+U57</f>
+        <f t="shared" ref="X57:X68" si="72">Y57+U57</f>
         <v>33688.6</v>
       </c>
       <c r="Y57" s="10">
-        <f>P57-W57</f>
+        <f t="shared" ref="Y57:Y68" si="73">P57-W57</f>
         <v>29213.8</v>
       </c>
       <c r="Z57" s="2">
@@ -8402,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="AA57" s="2">
-        <f t="shared" ref="AA57:AA68" si="64">Y57-Z57</f>
+        <f t="shared" ref="AA57:AA68" si="74">Y57-Z57</f>
         <v>29213.8</v>
       </c>
       <c r="AB57" s="2"/>
@@ -8416,12 +8647,12 @@
         <v>32902</v>
       </c>
       <c r="E58" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>4388</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>37290</v>
       </c>
       <c r="H58" s="2">
@@ -8433,11 +8664,11 @@
         <v>400</v>
       </c>
       <c r="J58" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>2237.4</v>
       </c>
       <c r="K58" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>43656.4</v>
       </c>
       <c r="L58" s="2">
@@ -8449,18 +8680,18 @@
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P58" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>46946.6</v>
       </c>
       <c r="Q58" s="2">
         <v>800</v>
       </c>
       <c r="R58" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>7458</v>
       </c>
       <c r="S58" s="2">
@@ -8468,20 +8699,20 @@
       </c>
       <c r="T58" s="2"/>
       <c r="U58" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>4474.8</v>
       </c>
       <c r="V58" s="2"/>
       <c r="W58" s="4">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>17732.8</v>
       </c>
       <c r="X58" s="2">
-        <f>Y58+U58</f>
+        <f t="shared" si="72"/>
         <v>33688.6</v>
       </c>
       <c r="Y58" s="10">
-        <f>P58-W58</f>
+        <f t="shared" si="73"/>
         <v>29213.8</v>
       </c>
       <c r="Z58" s="2">
@@ -8489,7 +8720,7 @@
         <v>0</v>
       </c>
       <c r="AA58" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>29213.8</v>
       </c>
       <c r="AB58" s="2"/>
@@ -8503,12 +8734,12 @@
         <v>32902</v>
       </c>
       <c r="E59" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>4388</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>37290</v>
       </c>
       <c r="H59" s="2">
@@ -8520,11 +8751,11 @@
         <v>400</v>
       </c>
       <c r="J59" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>2237.4</v>
       </c>
       <c r="K59" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>43656.4</v>
       </c>
       <c r="L59" s="2">
@@ -8536,18 +8767,18 @@
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>36192.199999999997</v>
       </c>
       <c r="P59" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>79848.600000000006</v>
       </c>
       <c r="Q59" s="2">
         <v>800</v>
       </c>
       <c r="R59" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>7458</v>
       </c>
       <c r="S59" s="2">
@@ -8555,25 +8786,25 @@
       </c>
       <c r="T59" s="2"/>
       <c r="U59" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>4474.8</v>
       </c>
       <c r="V59" s="2"/>
       <c r="W59" s="4">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>17732.8</v>
       </c>
       <c r="X59" s="2">
-        <f>Y59+U59</f>
+        <f t="shared" si="72"/>
         <v>66590.600000000006</v>
       </c>
       <c r="Y59" s="10">
-        <f>P59-W59</f>
+        <f t="shared" si="73"/>
         <v>62115.8</v>
       </c>
       <c r="Z59" s="2"/>
       <c r="AA59" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>62115.8</v>
       </c>
       <c r="AB59" s="2"/>
@@ -8587,12 +8818,12 @@
         <v>32902</v>
       </c>
       <c r="E60" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>4388</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>37290</v>
       </c>
       <c r="H60" s="2">
@@ -8604,34 +8835,34 @@
         <v>400</v>
       </c>
       <c r="J60" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>2237.4</v>
       </c>
       <c r="K60" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>43656.4</v>
       </c>
       <c r="L60" s="2">
         <v>0</v>
       </c>
       <c r="M60" s="2">
-        <f t="shared" ref="M60:M68" si="65">10%*D60</f>
+        <f t="shared" ref="M60:M68" si="75">10%*D60</f>
         <v>3290.2000000000003</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P60" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>46946.6</v>
       </c>
       <c r="Q60" s="2">
         <v>800</v>
       </c>
       <c r="R60" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>7458</v>
       </c>
       <c r="S60" s="2">
@@ -8639,20 +8870,20 @@
       </c>
       <c r="T60" s="2"/>
       <c r="U60" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>4474.8</v>
       </c>
       <c r="V60" s="2"/>
       <c r="W60" s="4">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>17732.8</v>
       </c>
       <c r="X60" s="2">
-        <f>Y60+U60</f>
+        <f t="shared" si="72"/>
         <v>33688.6</v>
       </c>
       <c r="Y60" s="10">
-        <f>P60-W60</f>
+        <f t="shared" si="73"/>
         <v>29213.8</v>
       </c>
       <c r="Z60" s="2">
@@ -8660,7 +8891,7 @@
         <v>0</v>
       </c>
       <c r="AA60" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>29213.8</v>
       </c>
       <c r="AB60" s="2"/>
@@ -8674,12 +8905,12 @@
         <v>32902</v>
       </c>
       <c r="E61" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>4388</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>37290</v>
       </c>
       <c r="H61" s="2">
@@ -8691,34 +8922,34 @@
         <v>400</v>
       </c>
       <c r="J61" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>2237.4</v>
       </c>
       <c r="K61" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>43656.4</v>
       </c>
       <c r="L61" s="2">
         <v>0</v>
       </c>
       <c r="M61" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P61" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>46946.6</v>
       </c>
       <c r="Q61" s="2">
         <v>800</v>
       </c>
       <c r="R61" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>7458</v>
       </c>
       <c r="S61" s="2">
@@ -8726,20 +8957,20 @@
       </c>
       <c r="T61" s="2"/>
       <c r="U61" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>4474.8</v>
       </c>
       <c r="V61" s="2"/>
       <c r="W61" s="4">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>17732.8</v>
       </c>
       <c r="X61" s="2">
-        <f>Y61+U61</f>
+        <f t="shared" si="72"/>
         <v>33688.6</v>
       </c>
       <c r="Y61" s="10">
-        <f>P61-W61</f>
+        <f t="shared" si="73"/>
         <v>29213.8</v>
       </c>
       <c r="Z61" s="2">
@@ -8747,7 +8978,7 @@
         <v>0</v>
       </c>
       <c r="AA61" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>29213.8</v>
       </c>
       <c r="AB61" s="2"/>
@@ -8761,12 +8992,12 @@
         <v>32902</v>
       </c>
       <c r="E62" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>4388</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>37290</v>
       </c>
       <c r="H62" s="2">
@@ -8778,34 +9009,34 @@
         <v>400</v>
       </c>
       <c r="J62" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>2237.4</v>
       </c>
       <c r="K62" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>43656.4</v>
       </c>
       <c r="L62" s="2">
         <v>0</v>
       </c>
       <c r="M62" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P62" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>46946.6</v>
       </c>
       <c r="Q62" s="2">
         <v>800</v>
       </c>
       <c r="R62" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>7458</v>
       </c>
       <c r="S62" s="2">
@@ -8813,20 +9044,20 @@
       </c>
       <c r="T62" s="2"/>
       <c r="U62" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>4474.8</v>
       </c>
       <c r="V62" s="2"/>
       <c r="W62" s="4">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>17732.8</v>
       </c>
       <c r="X62" s="2">
-        <f>Y62+U62</f>
+        <f t="shared" si="72"/>
         <v>33688.6</v>
       </c>
       <c r="Y62" s="10">
-        <f>P62-W62</f>
+        <f t="shared" si="73"/>
         <v>29213.8</v>
       </c>
       <c r="Z62" s="2">
@@ -8834,7 +9065,7 @@
         <v>0</v>
       </c>
       <c r="AA62" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>29213.8</v>
       </c>
       <c r="AB62" s="2"/>
@@ -8848,12 +9079,12 @@
         <v>32902</v>
       </c>
       <c r="E63" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>4388</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>37290</v>
       </c>
       <c r="H63" s="2">
@@ -8865,34 +9096,34 @@
         <v>400</v>
       </c>
       <c r="J63" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>2237.4</v>
       </c>
       <c r="K63" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>43656.4</v>
       </c>
       <c r="L63" s="2">
         <v>0</v>
       </c>
       <c r="M63" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P63" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>46946.6</v>
       </c>
       <c r="Q63" s="2">
         <v>800</v>
       </c>
       <c r="R63" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>7458</v>
       </c>
       <c r="S63" s="2">
@@ -8900,20 +9131,20 @@
       </c>
       <c r="T63" s="2"/>
       <c r="U63" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>4474.8</v>
       </c>
       <c r="V63" s="2"/>
       <c r="W63" s="4">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>17732.8</v>
       </c>
       <c r="X63" s="2">
-        <f>Y63+U63</f>
+        <f t="shared" si="72"/>
         <v>33688.6</v>
       </c>
       <c r="Y63" s="10">
-        <f>P63-W63</f>
+        <f t="shared" si="73"/>
         <v>29213.8</v>
       </c>
       <c r="Z63" s="2">
@@ -8921,7 +9152,7 @@
         <v>0</v>
       </c>
       <c r="AA63" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>29213.8</v>
       </c>
       <c r="AB63" s="2"/>
@@ -8935,12 +9166,12 @@
         <v>32902</v>
       </c>
       <c r="E64" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>4388</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>37290</v>
       </c>
       <c r="H64" s="2">
@@ -8952,34 +9183,34 @@
         <v>400</v>
       </c>
       <c r="J64" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>2237.4</v>
       </c>
       <c r="K64" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>43656.4</v>
       </c>
       <c r="L64" s="2">
         <v>0</v>
       </c>
       <c r="M64" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P64" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>46946.6</v>
       </c>
       <c r="Q64" s="2">
         <v>800</v>
       </c>
       <c r="R64" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>7458</v>
       </c>
       <c r="S64" s="2">
@@ -8987,20 +9218,20 @@
       </c>
       <c r="T64" s="2"/>
       <c r="U64" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>4474.8</v>
       </c>
       <c r="V64" s="2"/>
       <c r="W64" s="4">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>17732.8</v>
       </c>
       <c r="X64" s="2">
-        <f>Y64+U64</f>
+        <f t="shared" si="72"/>
         <v>33688.6</v>
       </c>
       <c r="Y64" s="10">
-        <f>P64-W64</f>
+        <f t="shared" si="73"/>
         <v>29213.8</v>
       </c>
       <c r="Z64" s="2">
@@ -9008,7 +9239,7 @@
         <v>0</v>
       </c>
       <c r="AA64" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>29213.8</v>
       </c>
       <c r="AB64" s="2"/>
@@ -9022,12 +9253,12 @@
         <v>32902</v>
       </c>
       <c r="E65" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>4388</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>37290</v>
       </c>
       <c r="H65" s="2">
@@ -9039,36 +9270,36 @@
         <v>400</v>
       </c>
       <c r="J65" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>2237.4</v>
       </c>
       <c r="K65" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>43656.4</v>
       </c>
       <c r="L65" s="2">
         <v>0</v>
       </c>
       <c r="M65" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N65" s="2">
         <v>10000</v>
       </c>
       <c r="O65" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>13290.2</v>
       </c>
       <c r="P65" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>56946.600000000006</v>
       </c>
       <c r="Q65" s="2">
         <v>800</v>
       </c>
       <c r="R65" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>7458</v>
       </c>
       <c r="S65" s="2">
@@ -9076,20 +9307,20 @@
       </c>
       <c r="T65" s="2"/>
       <c r="U65" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>4474.8</v>
       </c>
       <c r="V65" s="2"/>
       <c r="W65" s="4">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>17732.8</v>
       </c>
       <c r="X65" s="2">
-        <f>Y65+U65</f>
+        <f t="shared" si="72"/>
         <v>43688.600000000006</v>
       </c>
       <c r="Y65" s="10">
-        <f>P65-W65</f>
+        <f t="shared" si="73"/>
         <v>39213.800000000003</v>
       </c>
       <c r="Z65" s="2">
@@ -9097,7 +9328,7 @@
         <v>0</v>
       </c>
       <c r="AA65" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>39213.800000000003</v>
       </c>
       <c r="AB65" s="2"/>
@@ -9111,12 +9342,12 @@
         <v>32902</v>
       </c>
       <c r="E66" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>4388</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>37290</v>
       </c>
       <c r="H66" s="2">
@@ -9128,34 +9359,34 @@
         <v>400</v>
       </c>
       <c r="J66" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>2237.4</v>
       </c>
       <c r="K66" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>43656.4</v>
       </c>
       <c r="L66" s="2">
         <v>0</v>
       </c>
       <c r="M66" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P66" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>46946.6</v>
       </c>
       <c r="Q66" s="2">
         <v>800</v>
       </c>
       <c r="R66" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>7458</v>
       </c>
       <c r="S66" s="2">
@@ -9163,20 +9394,20 @@
       </c>
       <c r="T66" s="2"/>
       <c r="U66" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>4474.8</v>
       </c>
       <c r="V66" s="2"/>
       <c r="W66" s="4">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>17732.8</v>
       </c>
       <c r="X66" s="2">
-        <f>Y66+U66</f>
+        <f t="shared" si="72"/>
         <v>33688.6</v>
       </c>
       <c r="Y66" s="10">
-        <f>P66-W66</f>
+        <f t="shared" si="73"/>
         <v>29213.8</v>
       </c>
       <c r="Z66" s="2">
@@ -9184,7 +9415,7 @@
         <v>0</v>
       </c>
       <c r="AA66" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>29213.8</v>
       </c>
       <c r="AB66" s="2"/>
@@ -9198,16 +9429,16 @@
         <v>32902</v>
       </c>
       <c r="E67" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="63"/>
         <v>4388</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>37290</v>
       </c>
       <c r="H67" s="2">
-        <f t="shared" ref="H67:H68" si="66">10%*G67</f>
+        <f t="shared" ref="H67:H68" si="76">10%*G67</f>
         <v>3729</v>
       </c>
       <c r="I67" s="2">
@@ -9215,34 +9446,34 @@
         <v>400</v>
       </c>
       <c r="J67" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>2237.4</v>
       </c>
       <c r="K67" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>43656.4</v>
       </c>
       <c r="L67" s="2">
         <v>0</v>
       </c>
       <c r="M67" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P67" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>46946.6</v>
       </c>
       <c r="Q67" s="2">
         <v>800</v>
       </c>
       <c r="R67" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>7458</v>
       </c>
       <c r="S67" s="2">
@@ -9250,28 +9481,28 @@
       </c>
       <c r="T67" s="2"/>
       <c r="U67" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>4474.8</v>
       </c>
       <c r="V67" s="2"/>
       <c r="W67" s="4">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>17732.8</v>
       </c>
       <c r="X67" s="2">
-        <f>Y67+U67</f>
+        <f t="shared" si="72"/>
         <v>33688.6</v>
       </c>
       <c r="Y67" s="10">
-        <f>P67-W67</f>
+        <f t="shared" si="73"/>
         <v>29213.8</v>
       </c>
       <c r="Z67" s="2">
-        <f t="shared" ref="Z67:Z68" si="67">IF(Y67*13&gt;600000,1%*Y67,0)</f>
+        <f t="shared" ref="Z67:Z68" si="77">IF(Y67*13&gt;600000,1%*Y67,0)</f>
         <v>0</v>
       </c>
       <c r="AA67" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>29213.8</v>
       </c>
       <c r="AB67" s="2"/>
@@ -9290,11 +9521,11 @@
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="64"/>
         <v>38387</v>
       </c>
       <c r="H68" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="76"/>
         <v>3838.7000000000003</v>
       </c>
       <c r="I68" s="2">
@@ -9302,34 +9533,34 @@
         <v>400</v>
       </c>
       <c r="J68" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" si="65"/>
         <v>2303.2199999999998</v>
       </c>
       <c r="K68" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="66"/>
         <v>44928.92</v>
       </c>
       <c r="L68" s="2">
         <v>0</v>
       </c>
       <c r="M68" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="67"/>
         <v>3290.2000000000003</v>
       </c>
       <c r="P68" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="68"/>
         <v>48219.119999999995</v>
       </c>
       <c r="Q68" s="2">
         <v>800</v>
       </c>
       <c r="R68" s="2">
-        <f t="shared" si="61"/>
+        <f t="shared" si="69"/>
         <v>7677.4000000000005</v>
       </c>
       <c r="S68" s="2">
@@ -9337,28 +9568,28 @@
       </c>
       <c r="T68" s="2"/>
       <c r="U68" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="70"/>
         <v>4606.4399999999996</v>
       </c>
       <c r="V68" s="2"/>
       <c r="W68" s="4">
-        <f t="shared" si="63"/>
+        <f t="shared" si="71"/>
         <v>18083.84</v>
       </c>
       <c r="X68" s="2">
-        <f>Y68+U68</f>
+        <f t="shared" si="72"/>
         <v>34741.719999999994</v>
       </c>
       <c r="Y68" s="10">
-        <f>P68-W68</f>
+        <f t="shared" si="73"/>
         <v>30135.279999999995</v>
       </c>
       <c r="Z68" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AA68" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="74"/>
         <v>30135.279999999995</v>
       </c>
       <c r="AB68" s="2"/>
@@ -9462,11 +9693,11 @@
         <v>17732.8</v>
       </c>
       <c r="X70" s="2">
-        <f>Y70+U70</f>
+        <f t="shared" ref="X70:X82" si="78">Y70+U70</f>
         <v>32398.400000000001</v>
       </c>
       <c r="Y70" s="10">
-        <f>P70-W70</f>
+        <f t="shared" ref="Y70:Y82" si="79">P70-W70</f>
         <v>27923.600000000002</v>
       </c>
       <c r="Z70" s="2">
@@ -9549,11 +9780,11 @@
         <v>18395.84</v>
       </c>
       <c r="X71" s="2">
-        <f>Y71+U71</f>
+        <f t="shared" si="78"/>
         <v>76749.52</v>
       </c>
       <c r="Y71" s="10">
-        <f>P71-W71</f>
+        <f t="shared" si="79"/>
         <v>72026.080000000002</v>
       </c>
       <c r="Z71" s="12">
@@ -9635,11 +9866,11 @@
         <v>18395.84</v>
       </c>
       <c r="X72" s="2">
-        <f>Y72+U72</f>
+        <f t="shared" si="78"/>
         <v>37387.519999999997</v>
       </c>
       <c r="Y72" s="10">
-        <f>P72-W72</f>
+        <f t="shared" si="79"/>
         <v>32664.079999999998</v>
       </c>
       <c r="Z72" s="2">
@@ -9721,11 +9952,11 @@
         <v>18395.84</v>
       </c>
       <c r="X73" s="2">
-        <f>Y73+U73</f>
+        <f t="shared" si="78"/>
         <v>37387.519999999997</v>
       </c>
       <c r="Y73" s="10">
-        <f>P73-W73</f>
+        <f t="shared" si="79"/>
         <v>32664.079999999998</v>
       </c>
       <c r="Z73" s="2">
@@ -9807,11 +10038,11 @@
         <v>18395.84</v>
       </c>
       <c r="X74" s="2">
-        <f>Y74+U74</f>
+        <f t="shared" si="78"/>
         <v>37387.519999999997</v>
       </c>
       <c r="Y74" s="10">
-        <f>P74-W74</f>
+        <f t="shared" si="79"/>
         <v>32664.079999999998</v>
       </c>
       <c r="Z74" s="2">
@@ -9833,31 +10064,31 @@
         <v>34730</v>
       </c>
       <c r="E75" s="4">
-        <f t="shared" ref="E75:E80" si="68">ROUNDUP(D75/30,0)*4</f>
+        <f t="shared" ref="E75:E80" si="80">ROUNDUP(D75/30,0)*4</f>
         <v>4632</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="8">
-        <f t="shared" ref="G75:G82" si="69">SUM(D75:F75)</f>
+        <f t="shared" ref="G75:G82" si="81">SUM(D75:F75)</f>
         <v>39362</v>
       </c>
       <c r="H75" s="2">
-        <f t="shared" ref="H75:H82" si="70">10%*G75</f>
+        <f t="shared" ref="H75:H82" si="82">10%*G75</f>
         <v>3936.2000000000003</v>
       </c>
       <c r="I75" s="2">
         <v>400</v>
       </c>
       <c r="J75" s="2">
-        <f t="shared" ref="J75:J82" si="71">6%*G75</f>
+        <f t="shared" ref="J75:J82" si="83">6%*G75</f>
         <v>2361.7199999999998</v>
       </c>
       <c r="K75" s="8">
-        <f t="shared" ref="K75:K82" si="72">SUM(G75:J75)</f>
+        <f t="shared" ref="K75:K82" si="84">SUM(G75:J75)</f>
         <v>46059.92</v>
       </c>
       <c r="L75" s="2">
-        <f t="shared" ref="L75:L90" si="73">2000+3000</f>
+        <f t="shared" ref="L75:L90" si="85">2000+3000</f>
         <v>5000</v>
       </c>
       <c r="M75" s="2">
@@ -9865,18 +10096,18 @@
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="4">
-        <f t="shared" ref="O75:O77" si="74">SUM(L75:M75)</f>
+        <f t="shared" ref="O75:O77" si="86">SUM(L75:M75)</f>
         <v>5000</v>
       </c>
       <c r="P75" s="8">
-        <f t="shared" ref="P75:P82" si="75">K75+O75</f>
+        <f t="shared" ref="P75:P82" si="87">K75+O75</f>
         <v>51059.92</v>
       </c>
       <c r="Q75" s="2">
         <v>800</v>
       </c>
       <c r="R75" s="2">
-        <f t="shared" ref="R75:R82" si="76">H75*2</f>
+        <f t="shared" ref="R75:R82" si="88">H75*2</f>
         <v>7872.4000000000005</v>
       </c>
       <c r="S75" s="2">
@@ -9884,28 +10115,28 @@
       </c>
       <c r="T75" s="2"/>
       <c r="U75" s="2">
-        <f t="shared" ref="U75:U82" si="77">J75*2</f>
+        <f t="shared" ref="U75:U82" si="89">J75*2</f>
         <v>4723.4399999999996</v>
       </c>
       <c r="V75" s="2"/>
       <c r="W75" s="4">
-        <f t="shared" ref="W75:W82" si="78">SUM(Q75:U75)</f>
+        <f t="shared" ref="W75:W82" si="90">SUM(Q75:U75)</f>
         <v>18395.84</v>
       </c>
       <c r="X75" s="2">
-        <f>Y75+U75</f>
+        <f t="shared" si="78"/>
         <v>37387.519999999997</v>
       </c>
       <c r="Y75" s="10">
-        <f>P75-W75</f>
+        <f t="shared" si="79"/>
         <v>32664.079999999998</v>
       </c>
       <c r="Z75" s="2">
-        <f t="shared" ref="Z75:Z80" si="79">IF(Y75*13&gt;600000,1%*Y75,0)</f>
+        <f t="shared" ref="Z75:Z80" si="91">IF(Y75*13&gt;600000,1%*Y75,0)</f>
         <v>0</v>
       </c>
       <c r="AA75" s="2">
-        <f t="shared" ref="AA75:AA82" si="80">Y75-Z75</f>
+        <f t="shared" ref="AA75:AA82" si="92">Y75-Z75</f>
         <v>32664.079999999998</v>
       </c>
       <c r="AB75" s="2"/>
@@ -9919,31 +10150,31 @@
         <v>34730</v>
       </c>
       <c r="E76" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>4632</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="81"/>
         <v>39362</v>
       </c>
       <c r="H76" s="2">
-        <f t="shared" si="70"/>
+        <f t="shared" si="82"/>
         <v>3936.2000000000003</v>
       </c>
       <c r="I76" s="2">
         <v>400</v>
       </c>
       <c r="J76" s="2">
-        <f t="shared" si="71"/>
+        <f t="shared" si="83"/>
         <v>2361.7199999999998</v>
       </c>
       <c r="K76" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>46059.92</v>
       </c>
       <c r="L76" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="85"/>
         <v>5000</v>
       </c>
       <c r="M76" s="2">
@@ -9951,18 +10182,18 @@
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="86"/>
         <v>5000</v>
       </c>
       <c r="P76" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>51059.92</v>
       </c>
       <c r="Q76" s="2">
         <v>800</v>
       </c>
       <c r="R76" s="2">
-        <f t="shared" si="76"/>
+        <f t="shared" si="88"/>
         <v>7872.4000000000005</v>
       </c>
       <c r="S76" s="2">
@@ -9970,28 +10201,28 @@
       </c>
       <c r="T76" s="2"/>
       <c r="U76" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="89"/>
         <v>4723.4399999999996</v>
       </c>
       <c r="V76" s="2"/>
       <c r="W76" s="4">
+        <f t="shared" si="90"/>
+        <v>18395.84</v>
+      </c>
+      <c r="X76" s="2">
         <f t="shared" si="78"/>
-        <v>18395.84</v>
-      </c>
-      <c r="X76" s="2">
-        <f>Y76+U76</f>
         <v>37387.519999999997</v>
       </c>
       <c r="Y76" s="10">
-        <f>P76-W76</f>
+        <f t="shared" si="79"/>
         <v>32664.079999999998</v>
       </c>
       <c r="Z76" s="2">
-        <f t="shared" si="79"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="AA76" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="92"/>
         <v>32664.079999999998</v>
       </c>
       <c r="AB76" s="2"/>
@@ -10009,26 +10240,26 @@
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="81"/>
         <v>34730</v>
       </c>
       <c r="H77" s="2">
-        <f t="shared" si="70"/>
+        <f t="shared" si="82"/>
         <v>3473</v>
       </c>
       <c r="I77" s="2">
         <v>400</v>
       </c>
       <c r="J77" s="2">
-        <f t="shared" si="71"/>
+        <f t="shared" si="83"/>
         <v>2083.7999999999997</v>
       </c>
       <c r="K77" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>40686.800000000003</v>
       </c>
       <c r="L77" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="85"/>
         <v>5000</v>
       </c>
       <c r="M77" s="2">
@@ -10036,18 +10267,18 @@
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="86"/>
         <v>5000</v>
       </c>
       <c r="P77" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>45686.8</v>
       </c>
       <c r="Q77" s="2">
         <v>800</v>
       </c>
       <c r="R77" s="2">
-        <f t="shared" si="76"/>
+        <f t="shared" si="88"/>
         <v>6946</v>
       </c>
       <c r="S77" s="2">
@@ -10055,28 +10286,28 @@
       </c>
       <c r="T77" s="2"/>
       <c r="U77" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="89"/>
         <v>4167.5999999999995</v>
       </c>
       <c r="V77" s="2"/>
       <c r="W77" s="4">
+        <f t="shared" si="90"/>
+        <v>16913.599999999999</v>
+      </c>
+      <c r="X77" s="2">
         <f t="shared" si="78"/>
-        <v>16913.599999999999</v>
-      </c>
-      <c r="X77" s="2">
-        <f>Y77+U77</f>
         <v>32940.800000000003</v>
       </c>
       <c r="Y77" s="10">
-        <f>P77-W77</f>
+        <f t="shared" si="79"/>
         <v>28773.200000000004</v>
       </c>
       <c r="Z77" s="2">
-        <f t="shared" si="79"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="AA77" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="92"/>
         <v>28773.200000000004</v>
       </c>
       <c r="AB77" s="2"/>
@@ -10090,31 +10321,31 @@
         <v>34730</v>
       </c>
       <c r="E78" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>4632</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="81"/>
         <v>39362</v>
       </c>
       <c r="H78" s="2">
-        <f t="shared" si="70"/>
+        <f t="shared" si="82"/>
         <v>3936.2000000000003</v>
       </c>
       <c r="I78" s="2">
         <v>400</v>
       </c>
       <c r="J78" s="2">
-        <f t="shared" si="71"/>
+        <f t="shared" si="83"/>
         <v>2361.7199999999998</v>
       </c>
       <c r="K78" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>46059.92</v>
       </c>
       <c r="L78" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="85"/>
         <v>5000</v>
       </c>
       <c r="M78" s="2">
@@ -10128,14 +10359,14 @@
         <v>15000</v>
       </c>
       <c r="P78" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>61059.92</v>
       </c>
       <c r="Q78" s="2">
         <v>800</v>
       </c>
       <c r="R78" s="2">
-        <f t="shared" si="76"/>
+        <f t="shared" si="88"/>
         <v>7872.4000000000005</v>
       </c>
       <c r="S78" s="2">
@@ -10143,28 +10374,28 @@
       </c>
       <c r="T78" s="2"/>
       <c r="U78" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="89"/>
         <v>4723.4399999999996</v>
       </c>
       <c r="V78" s="2"/>
       <c r="W78" s="4">
+        <f t="shared" si="90"/>
+        <v>18395.84</v>
+      </c>
+      <c r="X78" s="2">
         <f t="shared" si="78"/>
-        <v>18395.84</v>
-      </c>
-      <c r="X78" s="2">
-        <f>Y78+U78</f>
         <v>47387.520000000004</v>
       </c>
       <c r="Y78" s="10">
-        <f>P78-W78</f>
+        <f t="shared" si="79"/>
         <v>42664.08</v>
       </c>
       <c r="Z78" s="2">
-        <f t="shared" si="79"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="AA78" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="92"/>
         <v>42664.08</v>
       </c>
       <c r="AB78" s="2"/>
@@ -10178,31 +10409,31 @@
         <v>34730</v>
       </c>
       <c r="E79" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>4632</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="81"/>
         <v>39362</v>
       </c>
       <c r="H79" s="2">
-        <f t="shared" si="70"/>
+        <f t="shared" si="82"/>
         <v>3936.2000000000003</v>
       </c>
       <c r="I79" s="2">
         <v>400</v>
       </c>
       <c r="J79" s="2">
-        <f t="shared" si="71"/>
+        <f t="shared" si="83"/>
         <v>2361.7199999999998</v>
       </c>
       <c r="K79" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>46059.92</v>
       </c>
       <c r="L79" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="85"/>
         <v>5000</v>
       </c>
       <c r="M79" s="2">
@@ -10210,18 +10441,18 @@
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="4">
-        <f t="shared" ref="O79:O82" si="81">SUM(L79:M79)</f>
+        <f t="shared" ref="O79:O82" si="93">SUM(L79:M79)</f>
         <v>5000</v>
       </c>
       <c r="P79" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>51059.92</v>
       </c>
       <c r="Q79" s="2">
         <v>800</v>
       </c>
       <c r="R79" s="2">
-        <f t="shared" si="76"/>
+        <f t="shared" si="88"/>
         <v>7872.4000000000005</v>
       </c>
       <c r="S79" s="2">
@@ -10229,28 +10460,28 @@
       </c>
       <c r="T79" s="2"/>
       <c r="U79" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="89"/>
         <v>4723.4399999999996</v>
       </c>
       <c r="V79" s="2"/>
       <c r="W79" s="4">
+        <f t="shared" si="90"/>
+        <v>18395.84</v>
+      </c>
+      <c r="X79" s="2">
         <f t="shared" si="78"/>
-        <v>18395.84</v>
-      </c>
-      <c r="X79" s="2">
-        <f>Y79+U79</f>
         <v>37387.519999999997</v>
       </c>
       <c r="Y79" s="10">
-        <f>P79-W79</f>
+        <f t="shared" si="79"/>
         <v>32664.079999999998</v>
       </c>
       <c r="Z79" s="2">
-        <f t="shared" si="79"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="AA79" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="92"/>
         <v>32664.079999999998</v>
       </c>
       <c r="AB79" s="2"/>
@@ -10264,31 +10495,31 @@
         <v>34730</v>
       </c>
       <c r="E80" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>4632</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="81"/>
         <v>39362</v>
       </c>
       <c r="H80" s="2">
-        <f t="shared" si="70"/>
+        <f t="shared" si="82"/>
         <v>3936.2000000000003</v>
       </c>
       <c r="I80" s="2">
         <v>400</v>
       </c>
       <c r="J80" s="2">
-        <f t="shared" si="71"/>
+        <f t="shared" si="83"/>
         <v>2361.7199999999998</v>
       </c>
       <c r="K80" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>46059.92</v>
       </c>
       <c r="L80" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="85"/>
         <v>5000</v>
       </c>
       <c r="M80" s="2">
@@ -10296,18 +10527,18 @@
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="4">
-        <f t="shared" si="81"/>
+        <f t="shared" si="93"/>
         <v>5000</v>
       </c>
       <c r="P80" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>51059.92</v>
       </c>
       <c r="Q80" s="2">
         <v>800</v>
       </c>
       <c r="R80" s="2">
-        <f t="shared" si="76"/>
+        <f t="shared" si="88"/>
         <v>7872.4000000000005</v>
       </c>
       <c r="S80" s="2">
@@ -10315,202 +10546,202 @@
       </c>
       <c r="T80" s="2"/>
       <c r="U80" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="89"/>
         <v>4723.4399999999996</v>
       </c>
       <c r="V80" s="2"/>
       <c r="W80" s="4">
+        <f t="shared" si="90"/>
+        <v>18395.84</v>
+      </c>
+      <c r="X80" s="2">
         <f t="shared" si="78"/>
-        <v>18395.84</v>
-      </c>
-      <c r="X80" s="2">
-        <f>Y80+U80</f>
         <v>37387.519999999997</v>
       </c>
       <c r="Y80" s="10">
-        <f>P80-W80</f>
+        <f t="shared" si="79"/>
         <v>32664.079999999998</v>
       </c>
       <c r="Z80" s="2">
-        <f t="shared" si="79"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="AA80" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="92"/>
         <v>32664.079999999998</v>
       </c>
       <c r="AB80" s="2"/>
       <c r="AC80" s="2"/>
     </row>
-    <row r="81" spans="1:29" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="40"/>
-      <c r="B81" s="40"/>
-      <c r="C81" s="40" t="s">
+    <row r="81" spans="1:29" s="40" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="37"/>
+      <c r="B81" s="37"/>
+      <c r="C81" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="D81" s="35">
+      <c r="D81" s="32">
         <v>34730</v>
       </c>
-      <c r="E81" s="35">
-        <f t="shared" ref="E81" si="82">ROUNDUP(D81/30,0)*4</f>
+      <c r="E81" s="32">
+        <f t="shared" ref="E81" si="94">ROUNDUP(D81/30,0)*4</f>
         <v>4632</v>
       </c>
-      <c r="F81" s="40"/>
-      <c r="G81" s="41">
-        <f t="shared" ref="G81" si="83">SUM(D81:F81)</f>
+      <c r="F81" s="37"/>
+      <c r="G81" s="38">
+        <f t="shared" ref="G81" si="95">SUM(D81:F81)</f>
         <v>39362</v>
       </c>
-      <c r="H81" s="40">
-        <f t="shared" ref="H81" si="84">10%*G81</f>
+      <c r="H81" s="37">
+        <f t="shared" ref="H81" si="96">10%*G81</f>
         <v>3936.2000000000003</v>
       </c>
-      <c r="I81" s="40">
+      <c r="I81" s="37">
         <v>400</v>
       </c>
-      <c r="J81" s="40">
-        <f t="shared" ref="J81" si="85">6%*G81</f>
+      <c r="J81" s="37">
+        <f t="shared" ref="J81" si="97">6%*G81</f>
         <v>2361.7199999999998</v>
       </c>
-      <c r="K81" s="41">
-        <f t="shared" ref="K81" si="86">SUM(G81:J81)</f>
+      <c r="K81" s="38">
+        <f t="shared" ref="K81" si="98">SUM(G81:J81)</f>
         <v>46059.92</v>
       </c>
-      <c r="L81" s="40">
-        <f t="shared" si="73"/>
-        <v>5000</v>
-      </c>
-      <c r="M81" s="40">
-        <v>0</v>
-      </c>
-      <c r="N81" s="40"/>
-      <c r="O81" s="35">
-        <f t="shared" ref="O81" si="87">SUM(L81:M81)</f>
-        <v>5000</v>
-      </c>
-      <c r="P81" s="41">
-        <f t="shared" ref="P81" si="88">K81+O81</f>
+      <c r="L81" s="37">
+        <f t="shared" si="85"/>
+        <v>5000</v>
+      </c>
+      <c r="M81" s="37">
+        <v>0</v>
+      </c>
+      <c r="N81" s="37"/>
+      <c r="O81" s="32">
+        <f t="shared" ref="O81" si="99">SUM(L81:M81)</f>
+        <v>5000</v>
+      </c>
+      <c r="P81" s="38">
+        <f t="shared" ref="P81" si="100">K81+O81</f>
         <v>51059.92</v>
       </c>
-      <c r="Q81" s="40">
+      <c r="Q81" s="37">
         <v>800</v>
       </c>
-      <c r="R81" s="40">
-        <f t="shared" ref="R81" si="89">H81*2</f>
+      <c r="R81" s="37">
+        <f t="shared" ref="R81" si="101">H81*2</f>
         <v>7872.4000000000005</v>
       </c>
-      <c r="S81" s="40">
-        <v>5000</v>
-      </c>
-      <c r="T81" s="40"/>
-      <c r="U81" s="40">
-        <f t="shared" ref="U81" si="90">J81*2</f>
+      <c r="S81" s="37">
+        <v>5000</v>
+      </c>
+      <c r="T81" s="37"/>
+      <c r="U81" s="37">
+        <f t="shared" ref="U81" si="102">J81*2</f>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V81" s="40"/>
-      <c r="W81" s="35">
-        <f t="shared" ref="W81" si="91">SUM(Q81:U81)</f>
+      <c r="V81" s="37"/>
+      <c r="W81" s="32">
+        <f t="shared" ref="W81" si="103">SUM(Q81:U81)</f>
         <v>18395.84</v>
       </c>
-      <c r="X81" s="40">
-        <f>Y81+U81</f>
+      <c r="X81" s="37">
+        <f t="shared" si="78"/>
         <v>37387.519999999997</v>
       </c>
-      <c r="Y81" s="42">
-        <f>P81-W81</f>
+      <c r="Y81" s="39">
+        <f t="shared" si="79"/>
         <v>32664.079999999998</v>
       </c>
-      <c r="Z81" s="40"/>
-      <c r="AA81" s="40">
-        <f t="shared" ref="AA81" si="92">Y81-Z81</f>
+      <c r="Z81" s="37"/>
+      <c r="AA81" s="37">
+        <f t="shared" ref="AA81" si="104">Y81-Z81</f>
         <v>32664.079999999998</v>
       </c>
-      <c r="AB81" s="40"/>
-      <c r="AC81" s="40"/>
-    </row>
-    <row r="82" spans="1:29" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="19"/>
-      <c r="B82" s="19"/>
-      <c r="C82" s="19" t="s">
+      <c r="AB81" s="37"/>
+      <c r="AC81" s="37"/>
+    </row>
+    <row r="82" spans="1:29" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="16"/>
+      <c r="B82" s="16"/>
+      <c r="C82" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D82" s="20">
+      <c r="D82" s="17">
         <v>34730</v>
       </c>
-      <c r="E82" s="20">
+      <c r="E82" s="17">
         <f>ROUNDUP(D82/30,0)*5</f>
         <v>5790</v>
       </c>
-      <c r="F82" s="19"/>
-      <c r="G82" s="22">
-        <f t="shared" si="69"/>
+      <c r="F82" s="16"/>
+      <c r="G82" s="19">
+        <f t="shared" si="81"/>
         <v>40520</v>
       </c>
-      <c r="H82" s="19">
-        <f t="shared" si="70"/>
+      <c r="H82" s="16">
+        <f t="shared" si="82"/>
         <v>4052</v>
       </c>
-      <c r="I82" s="19">
+      <c r="I82" s="16">
         <v>400</v>
       </c>
-      <c r="J82" s="19">
-        <f t="shared" si="71"/>
+      <c r="J82" s="16">
+        <f t="shared" si="83"/>
         <v>2431.1999999999998</v>
       </c>
-      <c r="K82" s="22">
-        <f t="shared" si="72"/>
+      <c r="K82" s="19">
+        <f t="shared" si="84"/>
         <v>47403.199999999997</v>
       </c>
-      <c r="L82" s="19">
-        <f t="shared" si="73"/>
-        <v>5000</v>
-      </c>
-      <c r="M82" s="19">
-        <v>0</v>
-      </c>
-      <c r="N82" s="19"/>
-      <c r="O82" s="20">
-        <f t="shared" si="81"/>
-        <v>5000</v>
-      </c>
-      <c r="P82" s="22">
-        <f t="shared" si="75"/>
+      <c r="L82" s="16">
+        <f t="shared" si="85"/>
+        <v>5000</v>
+      </c>
+      <c r="M82" s="16">
+        <v>0</v>
+      </c>
+      <c r="N82" s="16"/>
+      <c r="O82" s="17">
+        <f t="shared" si="93"/>
+        <v>5000</v>
+      </c>
+      <c r="P82" s="19">
+        <f t="shared" si="87"/>
         <v>52403.199999999997</v>
       </c>
-      <c r="Q82" s="19">
+      <c r="Q82" s="16">
         <v>800</v>
       </c>
-      <c r="R82" s="19">
-        <f t="shared" si="76"/>
+      <c r="R82" s="16">
+        <f t="shared" si="88"/>
         <v>8104</v>
       </c>
-      <c r="S82" s="19">
-        <v>5000</v>
-      </c>
-      <c r="T82" s="19"/>
-      <c r="U82" s="19">
-        <f t="shared" si="77"/>
+      <c r="S82" s="16">
+        <v>5000</v>
+      </c>
+      <c r="T82" s="16"/>
+      <c r="U82" s="16">
+        <f t="shared" si="89"/>
         <v>4862.3999999999996</v>
       </c>
-      <c r="V82" s="19"/>
-      <c r="W82" s="20">
+      <c r="V82" s="16"/>
+      <c r="W82" s="17">
+        <f t="shared" si="90"/>
+        <v>18766.400000000001</v>
+      </c>
+      <c r="X82" s="16">
         <f t="shared" si="78"/>
-        <v>18766.400000000001</v>
-      </c>
-      <c r="X82" s="19">
-        <f>Y82+U82</f>
         <v>38499.199999999997</v>
       </c>
-      <c r="Y82" s="23">
-        <f>P82-W82</f>
+      <c r="Y82" s="20">
+        <f t="shared" si="79"/>
         <v>33636.799999999996</v>
       </c>
-      <c r="Z82" s="19"/>
-      <c r="AA82" s="19">
-        <f t="shared" si="80"/>
+      <c r="Z82" s="16"/>
+      <c r="AA82" s="16">
+        <f t="shared" si="92"/>
         <v>33636.799999999996</v>
       </c>
-      <c r="AB82" s="19"/>
-      <c r="AC82" s="19"/>
+      <c r="AB82" s="16"/>
+      <c r="AC82" s="16"/>
     </row>
     <row r="83" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
@@ -10578,95 +10809,95 @@
       <c r="AB84" s="2"/>
       <c r="AC84" s="2"/>
     </row>
-    <row r="85" spans="1:29" s="27" customFormat="1" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="A85" s="44"/>
-      <c r="B85" s="44"/>
-      <c r="C85" s="45" t="s">
+    <row r="85" spans="1:29" s="24" customFormat="1" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="A85" s="41"/>
+      <c r="B85" s="41"/>
+      <c r="C85" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="D85" s="46">
+      <c r="D85" s="43">
         <f>D82-D81</f>
         <v>0</v>
       </c>
-      <c r="E85" s="46">
+      <c r="E85" s="43">
         <f>E82-E81</f>
         <v>1158</v>
       </c>
-      <c r="F85" s="46"/>
-      <c r="G85" s="26">
-        <f>G82-G81</f>
+      <c r="F85" s="43"/>
+      <c r="G85" s="23">
+        <f t="shared" ref="G85:M85" si="105">G82-G81</f>
         <v>1158</v>
       </c>
-      <c r="H85" s="46">
-        <f>H82-H81</f>
+      <c r="H85" s="43">
+        <f t="shared" si="105"/>
         <v>115.79999999999973</v>
       </c>
-      <c r="I85" s="46">
-        <f>I82-I81</f>
-        <v>0</v>
-      </c>
-      <c r="J85" s="46">
-        <f>J82-J81</f>
+      <c r="I85" s="43">
+        <f t="shared" si="105"/>
+        <v>0</v>
+      </c>
+      <c r="J85" s="43">
+        <f t="shared" si="105"/>
         <v>69.480000000000018</v>
       </c>
-      <c r="K85" s="46">
-        <f>K82-K81</f>
+      <c r="K85" s="43">
+        <f t="shared" si="105"/>
         <v>1343.2799999999988</v>
       </c>
-      <c r="L85" s="46">
-        <f>L82-L81</f>
-        <v>0</v>
-      </c>
-      <c r="M85" s="46">
-        <f>M82-M81</f>
-        <v>0</v>
-      </c>
-      <c r="N85" s="46"/>
-      <c r="O85" s="46">
+      <c r="L85" s="43">
+        <f t="shared" si="105"/>
+        <v>0</v>
+      </c>
+      <c r="M85" s="43">
+        <f t="shared" si="105"/>
+        <v>0</v>
+      </c>
+      <c r="N85" s="43"/>
+      <c r="O85" s="43">
         <f>O82-O81</f>
         <v>0</v>
       </c>
-      <c r="P85" s="46">
+      <c r="P85" s="43">
         <f>P82-P81</f>
         <v>1343.2799999999988</v>
       </c>
-      <c r="Q85" s="46">
+      <c r="Q85" s="43">
         <f>Q82-Q81</f>
         <v>0</v>
       </c>
-      <c r="R85" s="46">
+      <c r="R85" s="43">
         <f>R82-R81</f>
         <v>231.59999999999945</v>
       </c>
-      <c r="S85" s="46">
+      <c r="S85" s="43">
         <f>S82-S81</f>
         <v>0</v>
       </c>
-      <c r="T85" s="46"/>
-      <c r="U85" s="46">
+      <c r="T85" s="43"/>
+      <c r="U85" s="43">
         <f>U82-U81</f>
         <v>138.96000000000004</v>
       </c>
-      <c r="V85" s="46"/>
-      <c r="W85" s="46">
+      <c r="V85" s="43"/>
+      <c r="W85" s="43">
         <f>W82-W81</f>
         <v>370.56000000000131</v>
       </c>
-      <c r="X85" s="46">
+      <c r="X85" s="43">
         <f>X82-X81</f>
         <v>1111.6800000000003</v>
       </c>
-      <c r="Y85" s="46">
+      <c r="Y85" s="43">
         <f>Y82-Y81</f>
         <v>972.71999999999753</v>
       </c>
-      <c r="Z85" s="46"/>
-      <c r="AA85" s="46">
+      <c r="Z85" s="43"/>
+      <c r="AA85" s="43">
         <f>AA82-AA81</f>
         <v>972.71999999999753</v>
       </c>
-      <c r="AB85" s="25"/>
-      <c r="AC85" s="24"/>
+      <c r="AB85" s="22"/>
+      <c r="AC85" s="21"/>
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
@@ -10699,268 +10930,268 @@
       <c r="AB86" s="2"/>
       <c r="AC86" s="2"/>
     </row>
-    <row r="87" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="28"/>
-      <c r="B87" s="28"/>
+    <row r="87" spans="1:29" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="25"/>
+      <c r="B87" s="25"/>
       <c r="C87" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D87" s="31">
+      <c r="D87" s="28">
         <f>34730*1.1</f>
         <v>38203</v>
       </c>
-      <c r="E87" s="31">
+      <c r="E87" s="28">
         <f>ROUNDDOWN(D87/30,0)*5</f>
         <v>6365</v>
       </c>
-      <c r="F87" s="30"/>
-      <c r="G87" s="32">
-        <f t="shared" ref="G87" si="93">SUM(D87:F87)</f>
+      <c r="F87" s="27"/>
+      <c r="G87" s="29">
+        <f t="shared" ref="G87" si="106">SUM(D87:F87)</f>
         <v>44568</v>
       </c>
-      <c r="H87" s="30">
-        <f t="shared" ref="H87" si="94">10%*G87</f>
+      <c r="H87" s="27">
+        <f t="shared" ref="H87" si="107">10%*G87</f>
         <v>4456.8</v>
       </c>
-      <c r="I87" s="30">
+      <c r="I87" s="27">
         <v>400</v>
       </c>
-      <c r="J87" s="30">
-        <f t="shared" ref="J87" si="95">6%*G87</f>
+      <c r="J87" s="27">
+        <f t="shared" ref="J87" si="108">6%*G87</f>
         <v>2674.08</v>
       </c>
-      <c r="K87" s="32">
-        <f t="shared" ref="K87" si="96">SUM(G87:J87)</f>
+      <c r="K87" s="29">
+        <f t="shared" ref="K87" si="109">SUM(G87:J87)</f>
         <v>52098.880000000005</v>
       </c>
-      <c r="L87" s="30">
-        <f t="shared" si="73"/>
-        <v>5000</v>
-      </c>
-      <c r="M87" s="30">
+      <c r="L87" s="27">
+        <f t="shared" si="85"/>
+        <v>5000</v>
+      </c>
+      <c r="M87" s="27">
         <f>10%*D87</f>
         <v>3820.3</v>
       </c>
-      <c r="N87" s="30"/>
-      <c r="O87" s="31">
-        <f t="shared" ref="O87" si="97">SUM(L87:M87)</f>
+      <c r="N87" s="27"/>
+      <c r="O87" s="28">
+        <f t="shared" ref="O87" si="110">SUM(L87:M87)</f>
         <v>8820.2999999999993</v>
       </c>
-      <c r="P87" s="32">
-        <f t="shared" ref="P87" si="98">K87+O87</f>
+      <c r="P87" s="29">
+        <f t="shared" ref="P87" si="111">K87+O87</f>
         <v>60919.180000000008</v>
       </c>
-      <c r="Q87" s="30">
+      <c r="Q87" s="27">
         <v>800</v>
       </c>
-      <c r="R87" s="30">
-        <f t="shared" ref="R87" si="99">H87*2</f>
+      <c r="R87" s="27">
+        <f t="shared" ref="R87" si="112">H87*2</f>
         <v>8913.6</v>
       </c>
-      <c r="S87" s="30">
-        <v>5000</v>
-      </c>
-      <c r="T87" s="30"/>
-      <c r="U87" s="30">
-        <f t="shared" ref="U87" si="100">J87*2</f>
+      <c r="S87" s="27">
+        <v>5000</v>
+      </c>
+      <c r="T87" s="27"/>
+      <c r="U87" s="27">
+        <f t="shared" ref="U87" si="113">J87*2</f>
         <v>5348.16</v>
       </c>
-      <c r="V87" s="30"/>
-      <c r="W87" s="31">
-        <f t="shared" ref="W87" si="101">SUM(Q87:U87)</f>
+      <c r="V87" s="27"/>
+      <c r="W87" s="28">
+        <f t="shared" ref="W87" si="114">SUM(Q87:U87)</f>
         <v>20061.760000000002</v>
       </c>
-      <c r="X87" s="30">
+      <c r="X87" s="27">
         <f>Y87+U87</f>
         <v>46205.58</v>
       </c>
-      <c r="Y87" s="33">
+      <c r="Y87" s="30">
         <f>P87-W87</f>
         <v>40857.420000000006</v>
       </c>
-      <c r="Z87" s="30"/>
-      <c r="AA87" s="30">
-        <f t="shared" ref="AA87" si="102">Y87-Z87</f>
+      <c r="Z87" s="27"/>
+      <c r="AA87" s="27">
+        <f t="shared" ref="AA87" si="115">Y87-Z87</f>
         <v>40857.420000000006</v>
       </c>
-      <c r="AB87" s="30"/>
-      <c r="AC87" s="30"/>
+      <c r="AB87" s="27"/>
+      <c r="AC87" s="27"/>
     </row>
     <row r="88" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
-      <c r="C88" s="34" t="s">
+      <c r="C88" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D88" s="35">
+      <c r="D88" s="32">
         <f>D87-D85</f>
         <v>38203</v>
       </c>
-      <c r="E88" s="35">
-        <f t="shared" ref="E88:AA88" si="103">E87-E85</f>
+      <c r="E88" s="32">
+        <f t="shared" ref="E88:AA88" si="116">E87-E85</f>
         <v>5207</v>
       </c>
-      <c r="F88" s="35"/>
-      <c r="G88" s="41">
-        <f t="shared" si="103"/>
+      <c r="F88" s="32"/>
+      <c r="G88" s="38">
+        <f t="shared" si="116"/>
         <v>43410</v>
       </c>
-      <c r="H88" s="35">
-        <f t="shared" si="103"/>
+      <c r="H88" s="32">
+        <f t="shared" si="116"/>
         <v>4341</v>
       </c>
-      <c r="I88" s="35">
-        <f t="shared" si="103"/>
+      <c r="I88" s="32">
+        <f t="shared" si="116"/>
         <v>400</v>
       </c>
-      <c r="J88" s="35">
-        <f t="shared" si="103"/>
+      <c r="J88" s="32">
+        <f t="shared" si="116"/>
         <v>2604.6</v>
       </c>
-      <c r="K88" s="35">
-        <f t="shared" si="103"/>
+      <c r="K88" s="32">
+        <f t="shared" si="116"/>
         <v>50755.600000000006</v>
       </c>
-      <c r="L88" s="35">
-        <f t="shared" si="103"/>
-        <v>5000</v>
-      </c>
-      <c r="M88" s="35">
-        <f t="shared" si="103"/>
+      <c r="L88" s="32">
+        <f t="shared" si="116"/>
+        <v>5000</v>
+      </c>
+      <c r="M88" s="32">
+        <f t="shared" si="116"/>
         <v>3820.3</v>
       </c>
-      <c r="N88" s="35"/>
-      <c r="O88" s="35">
-        <f t="shared" si="103"/>
+      <c r="N88" s="32"/>
+      <c r="O88" s="32">
+        <f t="shared" si="116"/>
         <v>8820.2999999999993</v>
       </c>
-      <c r="P88" s="35">
-        <f t="shared" si="103"/>
+      <c r="P88" s="32">
+        <f t="shared" si="116"/>
         <v>59575.900000000009</v>
       </c>
-      <c r="Q88" s="35">
-        <f t="shared" si="103"/>
+      <c r="Q88" s="32">
+        <f t="shared" si="116"/>
         <v>800</v>
       </c>
-      <c r="R88" s="35">
-        <f t="shared" si="103"/>
+      <c r="R88" s="32">
+        <f t="shared" si="116"/>
         <v>8682</v>
       </c>
-      <c r="S88" s="35">
-        <f t="shared" si="103"/>
-        <v>5000</v>
-      </c>
-      <c r="T88" s="35"/>
-      <c r="U88" s="35">
-        <f t="shared" si="103"/>
+      <c r="S88" s="32">
+        <f t="shared" si="116"/>
+        <v>5000</v>
+      </c>
+      <c r="T88" s="32"/>
+      <c r="U88" s="32">
+        <f t="shared" si="116"/>
         <v>5209.2</v>
       </c>
-      <c r="V88" s="35"/>
-      <c r="W88" s="35">
-        <f t="shared" si="103"/>
+      <c r="V88" s="32"/>
+      <c r="W88" s="32">
+        <f t="shared" si="116"/>
         <v>19691.2</v>
       </c>
-      <c r="X88" s="35">
-        <f t="shared" si="103"/>
+      <c r="X88" s="32">
+        <f t="shared" si="116"/>
         <v>45093.9</v>
       </c>
-      <c r="Y88" s="35">
-        <f t="shared" si="103"/>
+      <c r="Y88" s="32">
+        <f t="shared" si="116"/>
         <v>39884.700000000012</v>
       </c>
-      <c r="Z88" s="35"/>
-      <c r="AA88" s="35">
-        <f t="shared" si="103"/>
+      <c r="Z88" s="32"/>
+      <c r="AA88" s="32">
+        <f t="shared" si="116"/>
         <v>39884.700000000012</v>
       </c>
       <c r="AB88" s="2"/>
       <c r="AC88" s="2"/>
     </row>
-    <row r="89" spans="1:29" s="21" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A89" s="19"/>
-      <c r="B89" s="19"/>
-      <c r="C89" s="37" t="s">
+    <row r="89" spans="1:29" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A89" s="16"/>
+      <c r="B89" s="16"/>
+      <c r="C89" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="D89" s="20">
+      <c r="D89" s="17">
         <f>D88-E85</f>
         <v>37045</v>
       </c>
-      <c r="E89" s="20">
+      <c r="E89" s="17">
         <v>5092</v>
       </c>
-      <c r="F89" s="20"/>
-      <c r="G89" s="38">
-        <f t="shared" ref="G89" si="104">SUM(D89:F89)</f>
+      <c r="F89" s="17"/>
+      <c r="G89" s="35">
+        <f t="shared" ref="G89" si="117">SUM(D89:F89)</f>
         <v>42137</v>
       </c>
-      <c r="H89" s="19">
-        <f t="shared" ref="H89" si="105">10%*G89</f>
+      <c r="H89" s="16">
+        <f t="shared" ref="H89" si="118">10%*G89</f>
         <v>4213.7</v>
       </c>
-      <c r="I89" s="19">
+      <c r="I89" s="16">
         <v>400</v>
       </c>
-      <c r="J89" s="39">
-        <f t="shared" ref="J89" si="106">6%*G89</f>
+      <c r="J89" s="36">
+        <f t="shared" ref="J89" si="119">6%*G89</f>
         <v>2528.2199999999998</v>
       </c>
-      <c r="K89" s="22">
-        <f t="shared" ref="K89" si="107">SUM(G89:J89)</f>
+      <c r="K89" s="19">
+        <f t="shared" ref="K89" si="120">SUM(G89:J89)</f>
         <v>49278.92</v>
       </c>
-      <c r="L89" s="19">
-        <f t="shared" si="73"/>
-        <v>5000</v>
-      </c>
-      <c r="M89" s="19">
+      <c r="L89" s="16">
+        <f t="shared" si="85"/>
+        <v>5000</v>
+      </c>
+      <c r="M89" s="16">
         <f>10%*D89</f>
         <v>3704.5</v>
       </c>
-      <c r="N89" s="19"/>
-      <c r="O89" s="20">
-        <f t="shared" ref="O89" si="108">SUM(L89:M89)</f>
+      <c r="N89" s="16"/>
+      <c r="O89" s="17">
+        <f t="shared" ref="O89" si="121">SUM(L89:M89)</f>
         <v>8704.5</v>
       </c>
-      <c r="P89" s="22">
-        <f t="shared" ref="P89" si="109">K89+O89</f>
+      <c r="P89" s="19">
+        <f t="shared" ref="P89" si="122">K89+O89</f>
         <v>57983.42</v>
       </c>
-      <c r="Q89" s="19">
+      <c r="Q89" s="16">
         <v>800</v>
       </c>
-      <c r="R89" s="19">
-        <f t="shared" ref="R89" si="110">H89*2</f>
+      <c r="R89" s="16">
+        <f t="shared" ref="R89" si="123">H89*2</f>
         <v>8427.4</v>
       </c>
-      <c r="S89" s="19">
-        <v>5000</v>
-      </c>
-      <c r="T89" s="19"/>
-      <c r="U89" s="19">
-        <f t="shared" ref="U89" si="111">J89*2</f>
+      <c r="S89" s="16">
+        <v>5000</v>
+      </c>
+      <c r="T89" s="16"/>
+      <c r="U89" s="16">
+        <f t="shared" ref="U89" si="124">J89*2</f>
         <v>5056.4399999999996</v>
       </c>
-      <c r="V89" s="19"/>
-      <c r="W89" s="20">
-        <f t="shared" ref="W89" si="112">SUM(Q89:U89)</f>
+      <c r="V89" s="16"/>
+      <c r="W89" s="17">
+        <f t="shared" ref="W89" si="125">SUM(Q89:U89)</f>
         <v>19283.84</v>
       </c>
-      <c r="X89" s="19">
+      <c r="X89" s="16">
         <f>Y89+U89</f>
         <v>43756.020000000004</v>
       </c>
-      <c r="Y89" s="23">
+      <c r="Y89" s="20">
         <f>P89-W89</f>
         <v>38699.58</v>
       </c>
-      <c r="Z89" s="19"/>
-      <c r="AA89" s="19">
-        <f t="shared" ref="AA89" si="113">Y89-Z89</f>
+      <c r="Z89" s="16"/>
+      <c r="AA89" s="16">
+        <f t="shared" ref="AA89" si="126">Y89-Z89</f>
         <v>38699.58</v>
       </c>
-      <c r="AB89" s="19"/>
-      <c r="AC89" s="19"/>
+      <c r="AB89" s="16"/>
+      <c r="AC89" s="16"/>
     </row>
     <row r="90" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
@@ -10970,32 +11201,32 @@
         <f>34730*1.1</f>
         <v>38203</v>
       </c>
-      <c r="E90" s="18">
+      <c r="E90" s="15">
         <f>ROUNDDOWN(D90/30,0)*5</f>
         <v>6365</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="8">
-        <f t="shared" ref="G90" si="114">SUM(D90:F90)</f>
+        <f t="shared" ref="G90" si="127">SUM(D90:F90)</f>
         <v>44568</v>
       </c>
       <c r="H90" s="2">
-        <f t="shared" ref="H90" si="115">10%*G90</f>
+        <f t="shared" ref="H90" si="128">10%*G90</f>
         <v>4456.8</v>
       </c>
       <c r="I90" s="2">
         <v>400</v>
       </c>
       <c r="J90" s="13">
-        <f t="shared" ref="J90" si="116">6%*G90</f>
+        <f t="shared" ref="J90" si="129">6%*G90</f>
         <v>2674.08</v>
       </c>
       <c r="K90" s="14">
-        <f t="shared" ref="K90" si="117">SUM(G90:J90)</f>
+        <f t="shared" ref="K90" si="130">SUM(G90:J90)</f>
         <v>52098.880000000005</v>
       </c>
       <c r="L90" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="85"/>
         <v>5000</v>
       </c>
       <c r="M90" s="2">
@@ -11004,18 +11235,18 @@
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="4">
-        <f t="shared" ref="O90" si="118">SUM(L90:M90)</f>
+        <f t="shared" ref="O90" si="131">SUM(L90:M90)</f>
         <v>8820.2999999999993</v>
       </c>
       <c r="P90" s="8">
-        <f t="shared" ref="P90" si="119">K90+O90</f>
+        <f t="shared" ref="P90" si="132">K90+O90</f>
         <v>60919.180000000008</v>
       </c>
       <c r="Q90" s="2">
         <v>800</v>
       </c>
       <c r="R90" s="2">
-        <f t="shared" ref="R90" si="120">H90*2</f>
+        <f t="shared" ref="R90" si="133">H90*2</f>
         <v>8913.6</v>
       </c>
       <c r="S90" s="2">
@@ -11023,7 +11254,7 @@
       </c>
       <c r="T90" s="2"/>
       <c r="U90" s="2">
-        <f t="shared" ref="U90" si="121">J90*2</f>
+        <f t="shared" ref="U90" si="134">J90*2</f>
         <v>5348.16</v>
       </c>
       <c r="V90" s="12">
@@ -11044,7 +11275,7 @@
       </c>
       <c r="Z90" s="2"/>
       <c r="AA90" s="2">
-        <f t="shared" ref="AA90" si="122">Y90-Z90</f>
+        <f t="shared" ref="AA90" si="135">Y90-Z90</f>
         <v>34490.420000000006</v>
       </c>
       <c r="AB90" s="2"/>
@@ -11163,95 +11394,95 @@
       <c r="AB92" s="2"/>
       <c r="AC92" s="2"/>
     </row>
-    <row r="93" spans="1:29" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="24"/>
-      <c r="B93" s="24"/>
-      <c r="C93" s="36" t="s">
+    <row r="93" spans="1:29" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="21"/>
+      <c r="B93" s="21"/>
+      <c r="C93" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="D93" s="25">
+      <c r="D93" s="22">
         <f>D89-D88</f>
         <v>-1158</v>
       </c>
-      <c r="E93" s="25">
-        <f t="shared" ref="E93:AA93" si="123">E89-E88</f>
+      <c r="E93" s="22">
+        <f t="shared" ref="E93:AA93" si="136">E89-E88</f>
         <v>-115</v>
       </c>
-      <c r="F93" s="25"/>
-      <c r="G93" s="26">
-        <f t="shared" si="123"/>
+      <c r="F93" s="22"/>
+      <c r="G93" s="23">
+        <f t="shared" si="136"/>
         <v>-1273</v>
       </c>
-      <c r="H93" s="25">
-        <f t="shared" si="123"/>
+      <c r="H93" s="22">
+        <f t="shared" si="136"/>
         <v>-127.30000000000018</v>
       </c>
-      <c r="I93" s="25">
-        <f t="shared" si="123"/>
-        <v>0</v>
-      </c>
-      <c r="J93" s="25">
-        <f t="shared" si="123"/>
+      <c r="I93" s="22">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="J93" s="22">
+        <f t="shared" si="136"/>
         <v>-76.380000000000109</v>
       </c>
-      <c r="K93" s="25">
-        <f t="shared" si="123"/>
+      <c r="K93" s="22">
+        <f t="shared" si="136"/>
         <v>-1476.6800000000076</v>
       </c>
-      <c r="L93" s="25">
-        <f t="shared" si="123"/>
-        <v>0</v>
-      </c>
-      <c r="M93" s="25">
-        <f t="shared" si="123"/>
+      <c r="L93" s="22">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="M93" s="22">
+        <f t="shared" si="136"/>
         <v>-115.80000000000018</v>
       </c>
-      <c r="N93" s="25"/>
-      <c r="O93" s="25">
-        <f t="shared" si="123"/>
+      <c r="N93" s="22"/>
+      <c r="O93" s="22">
+        <f t="shared" si="136"/>
         <v>-115.79999999999927</v>
       </c>
-      <c r="P93" s="25">
-        <f t="shared" si="123"/>
+      <c r="P93" s="22">
+        <f t="shared" si="136"/>
         <v>-1592.4800000000105</v>
       </c>
-      <c r="Q93" s="25">
-        <f t="shared" si="123"/>
-        <v>0</v>
-      </c>
-      <c r="R93" s="25">
-        <f t="shared" si="123"/>
+      <c r="Q93" s="22">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="R93" s="22">
+        <f t="shared" si="136"/>
         <v>-254.60000000000036</v>
       </c>
-      <c r="S93" s="25">
-        <f t="shared" si="123"/>
-        <v>0</v>
-      </c>
-      <c r="T93" s="25"/>
-      <c r="U93" s="25">
-        <f t="shared" si="123"/>
+      <c r="S93" s="22">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="T93" s="22"/>
+      <c r="U93" s="22">
+        <f t="shared" si="136"/>
         <v>-152.76000000000022</v>
       </c>
-      <c r="V93" s="25"/>
-      <c r="W93" s="25">
-        <f t="shared" si="123"/>
+      <c r="V93" s="22"/>
+      <c r="W93" s="22">
+        <f t="shared" si="136"/>
         <v>-407.36000000000058</v>
       </c>
-      <c r="X93" s="25">
-        <f t="shared" si="123"/>
+      <c r="X93" s="22">
+        <f t="shared" si="136"/>
         <v>-1337.8799999999974</v>
       </c>
-      <c r="Y93" s="25">
-        <f t="shared" si="123"/>
+      <c r="Y93" s="22">
+        <f t="shared" si="136"/>
         <v>-1185.1200000000099</v>
       </c>
-      <c r="Z93" s="25"/>
-      <c r="AA93" s="25">
-        <f t="shared" si="123"/>
+      <c r="Z93" s="22"/>
+      <c r="AA93" s="22">
+        <f t="shared" si="136"/>
         <v>-1185.1200000000099</v>
       </c>
-      <c r="AB93" s="25"/>
-      <c r="AC93" s="24"/>
+      <c r="AB93" s="22"/>
+      <c r="AC93" s="21"/>
     </row>
     <row r="94" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
@@ -11506,6 +11737,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:K1"/>
     <mergeCell ref="AB1:AB2"/>
     <mergeCell ref="AC1:AC2"/>
     <mergeCell ref="P1:P2"/>
@@ -11514,12 +11751,6 @@
     <mergeCell ref="Y1:Y2"/>
     <mergeCell ref="Z1:Z2"/>
     <mergeCell ref="AA1:AA2"/>
-    <mergeCell ref="L1:O1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="H1:K1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="59" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
